--- a/Proteccion.xlsx
+++ b/Proteccion.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="398">
   <si>
     <t>Asignado a</t>
   </si>
@@ -963,7 +963,8 @@
   </si>
   <si>
     <t>23/02/2026 Se identifica que hay una cola de casos para soporte que se deben de gestionar. Se recibe documnetación para la atención en la plataforma
-25/02/2026 Hasta el momento se han gestionado alrededor de 40 - 50 casos</t>
+25/02/2026 Hasta el momento se han gestionado alrededor de 40 - 50 casos
+27/02/2026 solo quedá a lo mucho 3 casos, pero es una tarea que será necesario trabajarle al mismo ritmo que llegan casos</t>
   </si>
   <si>
     <t>REQ-25</t>
@@ -976,6 +977,41 @@
   </si>
   <si>
     <t>25/02/2026 Se realiza la gestión para todos los casos asociados</t>
+  </si>
+  <si>
+    <t>REQ-26</t>
+  </si>
+  <si>
+    <t>Se debe de cargar servicios y actualizar aplicativo para el servidor de migraciones</t>
+  </si>
+  <si>
+    <t>Cargue de servicios y afinación de servidor para migración</t>
+  </si>
+  <si>
+    <t>26/02/2026 Se necesita poner en punta de nuevo el servidor que dejó de estar actualizada desde diciembre, por lo que es necesario cargar los servicios de validación fileNet
+02/03/2026 Con los servicios ya cargados se cambia un proceso que no se había actualizado. Además se actualiza el repositorio para tener los datos tal cuál en producción
+03/03/2026 Se termina de configurar, actualizar y cargar el repositorio. Además, se pasa el servidor de migraci´n a producción de 7 a 9 de la noche</t>
+  </si>
+  <si>
+    <t>REQ-27</t>
+  </si>
+  <si>
+    <t>Se debe de agregar una función que permita que si se valida mesa, se debe de identificar si se marco bonos para abrir dicha tarea</t>
+  </si>
+  <si>
+    <t>Corrección lógica de mesa unificada</t>
+  </si>
+  <si>
+    <t>03/03/2026 Se termina de construir la lógica para que el evento de mesa unificada ok pueda evaluar e identificar si el trámite necesita abrir bonos</t>
+  </si>
+  <si>
+    <t>REQ-28</t>
+  </si>
+  <si>
+    <t>Identificación y mantenimiento a cada una de las dificultades presentadas en el servidor nuevo</t>
+  </si>
+  <si>
+    <t>Soporte a inconsistencias en la migración</t>
   </si>
   <si>
     <t>dias estimados</t>
@@ -1314,10 +1350,10 @@
     <t>Internal Server Error</t>
   </si>
   <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>True</t>
+    <t>False</t>
+  </si>
+  <si>
+    <t>true</t>
   </si>
 </sst>
 </file>
@@ -2808,7 +2844,7 @@
   <sheetPr>
     <tabColor rgb="FF93C47D"/>
   </sheetPr>
-  <dimension ref="A1:AN79"/>
+  <dimension ref="A1:AN82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.21875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2962,7 +2998,7 @@
         <v>23</v>
       </c>
       <c r="R2" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="3" spans="1:40" ht="29.25" customHeight="1">
@@ -3017,7 +3053,7 @@
         <v>26</v>
       </c>
       <c r="R3" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:40" ht="29.25" customHeight="1">
@@ -3076,7 +3112,7 @@
         <v>30</v>
       </c>
       <c r="R4" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" spans="1:40" ht="29.25" customHeight="1">
@@ -3135,7 +3171,7 @@
         <v>33</v>
       </c>
       <c r="R5" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" spans="1:40" ht="29.25" customHeight="1">
@@ -3194,7 +3230,7 @@
         <v>36</v>
       </c>
       <c r="R6" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="7" spans="1:40" ht="29.25" customHeight="1">
@@ -3253,7 +3289,7 @@
         <v>39</v>
       </c>
       <c r="R7" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8" spans="1:40" ht="29.25" customHeight="1">
@@ -3308,7 +3344,7 @@
         <v>43</v>
       </c>
       <c r="R8" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9" spans="1:40" ht="29.25" customHeight="1">
@@ -3363,7 +3399,7 @@
         <v>46</v>
       </c>
       <c r="R9" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="S9" s="57"/>
       <c r="T9" s="57"/>
@@ -3438,7 +3474,7 @@
         <v>49</v>
       </c>
       <c r="R10" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="S10" s="61"/>
       <c r="T10" s="61"/>
@@ -3517,7 +3553,7 @@
         <v>52</v>
       </c>
       <c r="R11" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="S11" s="57"/>
       <c r="T11" s="57"/>
@@ -3596,7 +3632,7 @@
         <v>56</v>
       </c>
       <c r="R12" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="S12" s="61"/>
       <c r="T12" s="61"/>
@@ -3673,7 +3709,7 @@
         <v>60</v>
       </c>
       <c r="R13" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="S13" s="57"/>
       <c r="T13" s="57"/>
@@ -3748,7 +3784,7 @@
         <v>63</v>
       </c>
       <c r="R14" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="S14" s="61"/>
       <c r="T14" s="61"/>
@@ -3825,7 +3861,7 @@
         <v>66</v>
       </c>
       <c r="R15" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:40" ht="40.5" customHeight="1">
@@ -3880,7 +3916,7 @@
         <v>69</v>
       </c>
       <c r="R16" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="48" customHeight="1">
@@ -3935,7 +3971,7 @@
         <v>72</v>
       </c>
       <c r="R17" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="42" customHeight="1">
@@ -3990,7 +4026,7 @@
         <v>75</v>
       </c>
       <c r="R18" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="29.25" customHeight="1">
@@ -4045,7 +4081,7 @@
         <v>78</v>
       </c>
       <c r="R19" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="29.25" customHeight="1">
@@ -4087,7 +4123,7 @@
       NETWORKDAYS(J20,L20,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="N20" s="53"/>
       <c r="O20" s="53"/>
@@ -4096,7 +4132,7 @@
         <v>81</v>
       </c>
       <c r="R20" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="39" customHeight="1">
@@ -4141,7 +4177,7 @@
         <v>85</v>
       </c>
       <c r="R21" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="129.75" customHeight="1">
@@ -4198,7 +4234,7 @@
         <v>88</v>
       </c>
       <c r="R22" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="69" customHeight="1">
@@ -4255,7 +4291,7 @@
         <v>92</v>
       </c>
       <c r="R23" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="78.75" customHeight="1">
@@ -4310,7 +4346,7 @@
         <v>95</v>
       </c>
       <c r="R24" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="63" customHeight="1">
@@ -4369,7 +4405,7 @@
         <v>99</v>
       </c>
       <c r="R25" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="67.5" customHeight="1">
@@ -4424,7 +4460,7 @@
         <v>103</v>
       </c>
       <c r="R26" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="55.5" customHeight="1">
@@ -4469,7 +4505,7 @@
       <c r="P27" s="56"/>
       <c r="Q27" s="77"/>
       <c r="R27" s="44" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="138" customHeight="1">
@@ -4524,7 +4560,7 @@
         <v>109</v>
       </c>
       <c r="R28" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="67.5" customHeight="1">
@@ -4579,7 +4615,7 @@
       <c r="P29" s="56"/>
       <c r="Q29" s="43"/>
       <c r="R29" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="85.5">
@@ -4632,7 +4668,7 @@
       <c r="P30" s="53"/>
       <c r="Q30" s="78"/>
       <c r="R30" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="71.25">
@@ -4685,7 +4721,7 @@
       <c r="P31" s="56"/>
       <c r="Q31" s="79"/>
       <c r="R31" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="42.75">
@@ -4736,7 +4772,7 @@
       <c r="P32" s="53"/>
       <c r="Q32" s="78"/>
       <c r="R32" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="76.5" customHeight="1">
@@ -4791,7 +4827,7 @@
         <v>120</v>
       </c>
       <c r="R33" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="38.25">
@@ -4848,7 +4884,7 @@
         <v>124</v>
       </c>
       <c r="R34" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="42.75">
@@ -4905,7 +4941,7 @@
         <v>124</v>
       </c>
       <c r="R35" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="93" customHeight="1">
@@ -4962,7 +4998,7 @@
         <v>130</v>
       </c>
       <c r="R36" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="76.5" customHeight="1">
@@ -5019,7 +5055,7 @@
         <v>134</v>
       </c>
       <c r="R37" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="120.75" customHeight="1">
@@ -5063,7 +5099,7 @@
       NETWORKDAYS(J38,L38,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="N38" s="24"/>
       <c r="O38" s="24"/>
@@ -5072,7 +5108,7 @@
         <v>139</v>
       </c>
       <c r="R38" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="162" customHeight="1">
@@ -5129,7 +5165,7 @@
         <v>142</v>
       </c>
       <c r="R39" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="93" customHeight="1">
@@ -5188,7 +5224,7 @@
         <v>146</v>
       </c>
       <c r="R40" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="93" customHeight="1">
@@ -5245,7 +5281,7 @@
         <v>151</v>
       </c>
       <c r="R41" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="67.5" customHeight="1">
@@ -5304,7 +5340,7 @@
         <v>154</v>
       </c>
       <c r="R42" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="93" customHeight="1">
@@ -5363,7 +5399,7 @@
         <v>158</v>
       </c>
       <c r="R43" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="93" customHeight="1">
@@ -5422,7 +5458,7 @@
         <v>162</v>
       </c>
       <c r="R44" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="93" customHeight="1">
@@ -5481,7 +5517,7 @@
         <v>166</v>
       </c>
       <c r="R45" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="162" customHeight="1">
@@ -5540,7 +5576,7 @@
         <v>170</v>
       </c>
       <c r="R46" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="162" customHeight="1">
@@ -5599,7 +5635,7 @@
         <v>173</v>
       </c>
       <c r="R47" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="162" customHeight="1">
@@ -5658,7 +5694,7 @@
         <v>176</v>
       </c>
       <c r="R48" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="162" customHeight="1">
@@ -5717,7 +5753,7 @@
         <v>179</v>
       </c>
       <c r="R49" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="162" customHeight="1">
@@ -5776,7 +5812,7 @@
         <v>182</v>
       </c>
       <c r="R50" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="51" spans="1:18" ht="162" customHeight="1">
@@ -5835,7 +5871,7 @@
         <v>185</v>
       </c>
       <c r="R51" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="162" customHeight="1">
@@ -5892,7 +5928,7 @@
         <v>188</v>
       </c>
       <c r="R52" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="53" spans="1:18" ht="101.25" customHeight="1">
@@ -5949,7 +5985,7 @@
         <v>192</v>
       </c>
       <c r="R53" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="54" spans="1:18" ht="110.25" customHeight="1">
@@ -6006,7 +6042,7 @@
         <v>196</v>
       </c>
       <c r="R54" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="162" customHeight="1">
@@ -6063,7 +6099,7 @@
         <v>200</v>
       </c>
       <c r="R55" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="56" spans="1:18" ht="162" customHeight="1">
@@ -6120,7 +6156,7 @@
         <v>203</v>
       </c>
       <c r="R56" s="80" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="57" spans="1:18" ht="110.25" customHeight="1">
@@ -6179,7 +6215,7 @@
         <v>207</v>
       </c>
       <c r="R57" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="162" customHeight="1">
@@ -6236,7 +6272,7 @@
         <v>210</v>
       </c>
       <c r="R58" s="80" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="59" spans="1:18" ht="110.25" customHeight="1">
@@ -6295,7 +6331,7 @@
         <v>214</v>
       </c>
       <c r="R59" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="60" spans="1:18" ht="162" customHeight="1">
@@ -6352,7 +6388,7 @@
         <v>217</v>
       </c>
       <c r="R60" s="80" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="61" spans="1:18" ht="162" customHeight="1">
@@ -6411,7 +6447,7 @@
         <v>220</v>
       </c>
       <c r="R61" s="81" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="110.25" customHeight="1">
@@ -6470,7 +6506,7 @@
         <v>223</v>
       </c>
       <c r="R62" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="63" spans="1:18" ht="162" customHeight="1">
@@ -6514,14 +6550,14 @@
       NETWORKDAYS(J63,L63,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="N63" s="39"/>
       <c r="O63" s="39"/>
       <c r="P63" s="39"/>
       <c r="Q63" s="79"/>
       <c r="R63" s="81" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="64" spans="1:18" ht="132.75" customHeight="1">
@@ -6580,7 +6616,7 @@
         <v>229</v>
       </c>
       <c r="R64" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="65" spans="1:18" ht="132.75" customHeight="1">
@@ -6639,7 +6675,7 @@
         <v>233</v>
       </c>
       <c r="R65" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="66" spans="1:18" ht="162" customHeight="1">
@@ -6696,7 +6732,7 @@
         <v>236</v>
       </c>
       <c r="R66" s="80" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="67" spans="1:18" ht="162" customHeight="1">
@@ -6753,7 +6789,7 @@
         <v>239</v>
       </c>
       <c r="R67" s="81" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="68" spans="1:18" ht="162" customHeight="1">
@@ -6810,7 +6846,7 @@
         <v>239</v>
       </c>
       <c r="R68" s="80" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="69" spans="1:18" ht="132.75" customHeight="1">
@@ -6868,7 +6904,7 @@
         <v>245</v>
       </c>
       <c r="R69" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="70" spans="1:18" ht="162" customHeight="1">
@@ -6925,7 +6961,7 @@
         <v>248</v>
       </c>
       <c r="R70" s="80" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="71" spans="1:18" ht="162" customHeight="1">
@@ -6983,7 +7019,7 @@
         <v>251</v>
       </c>
       <c r="R71" s="81" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="72" spans="1:18" ht="162" customHeight="1">
@@ -7042,7 +7078,7 @@
         <v>254</v>
       </c>
       <c r="R72" s="80" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="162" customHeight="1">
@@ -7101,7 +7137,7 @@
         <v>257</v>
       </c>
       <c r="R73" s="81" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="74" spans="1:18" ht="144" customHeight="1">
@@ -7160,7 +7196,7 @@
         <v>261</v>
       </c>
       <c r="R74" s="80" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="75" spans="1:18" ht="162" customHeight="1">
@@ -7219,7 +7255,7 @@
         <v>265</v>
       </c>
       <c r="R75" s="81" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="76" spans="1:18" ht="132.75" customHeight="1">
@@ -7278,7 +7314,7 @@
         <v>269</v>
       </c>
       <c r="R76" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="77" spans="1:18" ht="176.25" customHeight="1">
@@ -7337,7 +7373,7 @@
         <v>272</v>
       </c>
       <c r="R77" s="81" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="78" spans="1:18" ht="132.75" customHeight="1">
@@ -7355,10 +7391,10 @@
       </c>
       <c r="E78" s="19"/>
       <c r="F78" s="54" t="s">
-        <v>138</v>
+        <v>22</v>
       </c>
       <c r="G78" s="66">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="H78" s="22">
         <f>IF(OR(J78="",K78="",K78&lt;J78),0,NETWORKDAYS(J78,K78,Hoja2!$A$2:$A$53))</f>
@@ -7373,7 +7409,9 @@
       <c r="K78" s="24">
         <v>46079</v>
       </c>
-      <c r="L78" s="24"/>
+      <c r="L78" s="24">
+        <v>46080</v>
+      </c>
       <c r="M78" s="25">
         <f ca="1">IF(OR(J78="",AND(L78="",TODAY()&lt;J78),AND(L78&lt;&gt;"",L78&lt;J78)),0,
    IF(L78="",
@@ -7381,16 +7419,20 @@
       NETWORKDAYS(J78,L78,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N78" s="24"/>
-      <c r="O78" s="24"/>
-      <c r="P78" s="24"/>
+      <c r="O78" s="24">
+        <v>46080</v>
+      </c>
+      <c r="P78" s="24">
+        <v>46080</v>
+      </c>
       <c r="Q78" s="78" t="s">
         <v>276</v>
       </c>
       <c r="R78" s="29" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="79" spans="1:18" ht="132.75" customHeight="1">
@@ -7449,21 +7491,188 @@
         <v>280</v>
       </c>
       <c r="R79" s="44" t="s">
-        <v>386</v>
+        <v>397</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="153" customHeight="1">
+      <c r="A80" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B80" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="D80" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="E80" s="19"/>
+      <c r="F80" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="G80" s="66">
+        <v>100</v>
+      </c>
+      <c r="H80" s="22">
+        <f>IF(OR(J80="",K80="",K80&lt;J80),0,NETWORKDAYS(J80,K80,Hoja2!$A$2:$A$53))</f>
+        <v>4</v>
+      </c>
+      <c r="I80" s="45">
+        <v>46078</v>
+      </c>
+      <c r="J80" s="45">
+        <v>46079</v>
+      </c>
+      <c r="K80" s="24">
+        <v>46084</v>
+      </c>
+      <c r="L80" s="24">
+        <v>46084</v>
+      </c>
+      <c r="M80" s="25">
+        <f ca="1">IF(OR(J80="",AND(L80="",TODAY()&lt;J80),AND(L80&lt;&gt;"",L80&lt;J80)),0,
+   IF(L80="",
+      NETWORKDAYS(J80,TODAY(),Hoja2!$A$2:$A$53),
+      NETWORKDAYS(J80,L80,Hoja2!$A$2:$A$53)
+   )
+)</f>
+        <v>4</v>
+      </c>
+      <c r="N80" s="24">
+        <v>46084</v>
+      </c>
+      <c r="O80" s="24">
+        <v>46084</v>
+      </c>
+      <c r="P80" s="24">
+        <v>46084</v>
+      </c>
+      <c r="Q80" s="78" t="s">
+        <v>284</v>
+      </c>
+      <c r="R80" s="29" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="132.75" customHeight="1">
+      <c r="A81" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B81" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="C81" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="D81" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="E81" s="33"/>
+      <c r="F81" s="72" t="s">
+        <v>199</v>
+      </c>
+      <c r="G81" s="76">
+        <v>80</v>
+      </c>
+      <c r="H81" s="36">
+        <f>IF(OR(J81="",K81="",K81&lt;J81),0,NETWORKDAYS(J81,K81,Hoja2!$A$2:$A$53))</f>
+        <v>3</v>
+      </c>
+      <c r="I81" s="38">
+        <v>46083</v>
+      </c>
+      <c r="J81" s="38">
+        <v>46083</v>
+      </c>
+      <c r="K81" s="39">
+        <v>46085</v>
+      </c>
+      <c r="L81" s="39"/>
+      <c r="M81" s="40">
+        <f ca="1">IF(OR(J81="",AND(L81="",TODAY()&lt;J81),AND(L81&lt;&gt;"",L81&lt;J81)),0,
+   IF(L81="",
+      NETWORKDAYS(J81,TODAY(),Hoja2!$A$2:$A$53),
+      NETWORKDAYS(J81,L81,Hoja2!$A$2:$A$53)
+   )
+)</f>
+        <v>3</v>
+      </c>
+      <c r="N81" s="39"/>
+      <c r="O81" s="39">
+        <v>46084</v>
+      </c>
+      <c r="P81" s="39"/>
+      <c r="Q81" s="79" t="s">
+        <v>288</v>
+      </c>
+      <c r="R81" s="44" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="153" customHeight="1">
+      <c r="A82" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B82" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="C82" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="D82" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="E82" s="19"/>
+      <c r="F82" s="54" t="s">
+        <v>138</v>
+      </c>
+      <c r="G82" s="66">
+        <v>50</v>
+      </c>
+      <c r="H82" s="22">
+        <f>IF(OR(J82="",K82="",K82&lt;J82),0,NETWORKDAYS(J82,K82,Hoja2!$A$2:$A$53))</f>
+        <v>3</v>
+      </c>
+      <c r="I82" s="45">
+        <v>46085</v>
+      </c>
+      <c r="J82" s="45">
+        <v>46085</v>
+      </c>
+      <c r="K82" s="24">
+        <v>46087</v>
+      </c>
+      <c r="L82" s="24"/>
+      <c r="M82" s="25">
+        <f ca="1">IF(OR(J82="",AND(L82="",TODAY()&lt;J82),AND(L82&lt;&gt;"",L82&lt;J82)),0,
+   IF(L82="",
+      NETWORKDAYS(J82,TODAY(),Hoja2!$A$2:$A$53),
+      NETWORKDAYS(J82,L82,Hoja2!$A$2:$A$53)
+   )
+)</f>
+        <v>1</v>
+      </c>
+      <c r="N82" s="24"/>
+      <c r="O82" s="24"/>
+      <c r="P82" s="24"/>
+      <c r="Q82" s="78"/>
+      <c r="R82" s="29" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R30"/>
-  <conditionalFormatting sqref="B1:B79">
+  <conditionalFormatting sqref="B1:B82">
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>COUNTIF(B$1:B$79, B1)&gt;1</formula>
+      <formula>COUNTIF(B$1:B$82, B1)&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I2:L20 I21 K21:L21 I22:L79 N2:P79">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I2:L20 I21 K21:L21 I22:L82 N2:P82">
       <formula1>OR(NOT(ISERROR(DATEVALUE(I2))), AND(ISNUMBER(I2), LEFT(CELL("format", I2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F79">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F82">
       <formula1>"FINALIZADO,EN PROCESO,PAUSADO,EN TEST,PENDIENTE,PRUEBAS CLIENTE,PRUEBAS IMAGINE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7506,7 +7715,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="84" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="I1" s="85" t="s">
         <v>8</v>
@@ -7521,7 +7730,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="85" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="N1" s="87" t="s">
         <v>14</v>
@@ -7557,19 +7766,19 @@
     </row>
     <row r="2" spans="1:39" ht="29.25" customHeight="1">
       <c r="A2" s="88" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B2" s="89" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="90" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="D2" s="89" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="89" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="F2" s="91" t="s">
         <v>22</v>
@@ -7604,19 +7813,19 @@
     </row>
     <row r="3" spans="1:39" ht="29.25" customHeight="1">
       <c r="A3" s="88" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B3" s="89" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="90" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="D3" s="89" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="89" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F3" s="91" t="s">
         <v>22</v>
@@ -7651,19 +7860,19 @@
     </row>
     <row r="4" spans="1:39" ht="39" customHeight="1">
       <c r="A4" s="88" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B4" s="89" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="90" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="D4" s="89" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="89" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="F4" s="91" t="s">
         <v>22</v>
@@ -7702,19 +7911,19 @@
     </row>
     <row r="5" spans="1:39" ht="127.5">
       <c r="A5" s="88" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B5" s="89" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="90" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="D5" s="89" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="105" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="F5" s="91" t="s">
         <v>22</v>
@@ -7753,19 +7962,19 @@
     </row>
     <row r="6" spans="1:39" ht="29.25" customHeight="1">
       <c r="A6" s="88" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B6" s="89" t="s">
         <v>34</v>
       </c>
       <c r="C6" s="90" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="D6" s="89" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="107" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="F6" s="108" t="s">
         <v>22</v>
@@ -7804,19 +8013,19 @@
     </row>
     <row r="7" spans="1:39" ht="29.25" customHeight="1">
       <c r="A7" s="88" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B7" s="89" t="s">
         <v>37</v>
       </c>
       <c r="C7" s="90" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="D7" s="89" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="89" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="F7" s="110" t="s">
         <v>22</v>
@@ -7855,19 +8064,19 @@
     </row>
     <row r="8" spans="1:39" ht="29.25" customHeight="1">
       <c r="A8" s="88" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B8" s="89" t="s">
         <v>40</v>
       </c>
       <c r="C8" s="90" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="D8" s="89" t="s">
         <v>42</v>
       </c>
       <c r="E8" s="112" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="F8" s="91" t="s">
         <v>22</v>
@@ -7902,17 +8111,17 @@
     </row>
     <row r="9" spans="1:39" ht="29.25" customHeight="1">
       <c r="A9" s="88" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B9" s="89" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="116" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="D9" s="117"/>
       <c r="E9" s="89" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="F9" s="110" t="s">
         <v>22</v>
@@ -7949,17 +8158,17 @@
     </row>
     <row r="10" spans="1:39" ht="93" customHeight="1">
       <c r="A10" s="88" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B10" s="89" t="s">
         <v>47</v>
       </c>
       <c r="C10" s="116" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="D10" s="117"/>
       <c r="E10" s="89" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="F10" s="110" t="s">
         <v>22</v>
@@ -7994,19 +8203,19 @@
     </row>
     <row r="11" spans="1:39" ht="409.5">
       <c r="A11" s="88" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B11" s="89" t="s">
         <v>50</v>
       </c>
       <c r="C11" s="90" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="D11" s="89" t="s">
         <v>42</v>
       </c>
       <c r="E11" s="119" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="F11" s="110" t="s">
         <v>22</v>
@@ -8043,19 +8252,19 @@
     </row>
     <row r="12" spans="1:39" ht="29.25" customHeight="1">
       <c r="A12" s="88" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B12" s="89" t="s">
         <v>53</v>
       </c>
       <c r="C12" s="120" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="D12" s="89" t="s">
         <v>55</v>
       </c>
       <c r="E12" s="89" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="F12" s="110" t="s">
         <v>22</v>
@@ -8092,19 +8301,19 @@
     </row>
     <row r="13" spans="1:39" ht="29.25" customHeight="1">
       <c r="A13" s="88" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B13" s="89" t="s">
         <v>57</v>
       </c>
       <c r="C13" s="116" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="D13" s="89" t="s">
         <v>59</v>
       </c>
       <c r="E13" s="89" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="F13" s="110" t="s">
         <v>22</v>
@@ -8139,7 +8348,7 @@
     </row>
     <row r="14" spans="1:39" ht="29.25" customHeight="1">
       <c r="A14" s="88" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B14" s="89" t="s">
         <v>61</v>
@@ -8149,7 +8358,7 @@
       </c>
       <c r="D14" s="121"/>
       <c r="E14" s="107" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="F14" s="115" t="s">
         <v>22</v>
@@ -8212,7 +8421,7 @@
         <v>45292</v>
       </c>
       <c r="B1" s="123" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17.25" customHeight="1">
@@ -8220,7 +8429,7 @@
         <v>45299</v>
       </c>
       <c r="B2" s="123" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.25" customHeight="1">
@@ -8228,7 +8437,7 @@
         <v>45376</v>
       </c>
       <c r="B3" s="123" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17.25" customHeight="1">
@@ -8236,7 +8445,7 @@
         <v>45379</v>
       </c>
       <c r="B4" s="123" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17.25" customHeight="1">
@@ -8244,7 +8453,7 @@
         <v>45380</v>
       </c>
       <c r="B5" s="123" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17.25" customHeight="1">
@@ -8252,7 +8461,7 @@
         <v>45413</v>
       </c>
       <c r="B6" s="123" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.25" customHeight="1">
@@ -8260,7 +8469,7 @@
         <v>45425</v>
       </c>
       <c r="B7" s="123" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17.25" customHeight="1">
@@ -8268,7 +8477,7 @@
         <v>45446</v>
       </c>
       <c r="B8" s="123" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17.25" customHeight="1">
@@ -8276,7 +8485,7 @@
         <v>45453</v>
       </c>
       <c r="B9" s="123" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17.25" customHeight="1">
@@ -8284,7 +8493,7 @@
         <v>45474</v>
       </c>
       <c r="B10" s="123" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17.25" customHeight="1">
@@ -8292,7 +8501,7 @@
         <v>45493</v>
       </c>
       <c r="B11" s="123" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17.25" customHeight="1">
@@ -8300,7 +8509,7 @@
         <v>45511</v>
       </c>
       <c r="B12" s="123" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17.25" customHeight="1">
@@ -8308,7 +8517,7 @@
         <v>45523</v>
       </c>
       <c r="B13" s="123" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17.25" customHeight="1">
@@ -8316,7 +8525,7 @@
         <v>45579</v>
       </c>
       <c r="B14" s="123" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17.25" customHeight="1">
@@ -8324,7 +8533,7 @@
         <v>45600</v>
       </c>
       <c r="B15" s="123" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17.25" customHeight="1">
@@ -8332,7 +8541,7 @@
         <v>45607</v>
       </c>
       <c r="B16" s="123" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17.25" customHeight="1">
@@ -8340,7 +8549,7 @@
         <v>45634</v>
       </c>
       <c r="B17" s="123" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17.25" customHeight="1">
@@ -8348,7 +8557,7 @@
         <v>45651</v>
       </c>
       <c r="B18" s="123" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25" customHeight="1">
@@ -8356,7 +8565,7 @@
         <v>45658</v>
       </c>
       <c r="B19" s="124" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25" customHeight="1">
@@ -8364,7 +8573,7 @@
         <v>45663</v>
       </c>
       <c r="B20" s="124" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17.25" customHeight="1">
@@ -8372,7 +8581,7 @@
         <v>45740</v>
       </c>
       <c r="B21" s="124" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17.25" customHeight="1">
@@ -8380,7 +8589,7 @@
         <v>45764</v>
       </c>
       <c r="B22" s="124" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17.25" customHeight="1">
@@ -8388,7 +8597,7 @@
         <v>45765</v>
       </c>
       <c r="B23" s="124" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17.25" customHeight="1">
@@ -8396,7 +8605,7 @@
         <v>45778</v>
       </c>
       <c r="B24" s="124" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17.25" customHeight="1">
@@ -8404,7 +8613,7 @@
         <v>45810</v>
       </c>
       <c r="B25" s="124" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17.25" customHeight="1">
@@ -8412,7 +8621,7 @@
         <v>45831</v>
       </c>
       <c r="B26" s="124" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17.25" customHeight="1">
@@ -8420,7 +8629,7 @@
         <v>45838</v>
       </c>
       <c r="B27" s="124" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17.25" customHeight="1">
@@ -8428,7 +8637,7 @@
         <v>45858</v>
       </c>
       <c r="B28" s="124" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17.25" customHeight="1">
@@ -8436,7 +8645,7 @@
         <v>45876</v>
       </c>
       <c r="B29" s="124" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17.25" customHeight="1">
@@ -8444,7 +8653,7 @@
         <v>45887</v>
       </c>
       <c r="B30" s="124" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="17.25" customHeight="1">
@@ -8452,7 +8661,7 @@
         <v>45943</v>
       </c>
       <c r="B31" s="124" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="17.25" customHeight="1">
@@ -8460,7 +8669,7 @@
         <v>45964</v>
       </c>
       <c r="B32" s="124" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="17.25" customHeight="1">
@@ -8468,7 +8677,7 @@
         <v>45978</v>
       </c>
       <c r="B33" s="124" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="17.25" customHeight="1">
@@ -8476,7 +8685,7 @@
         <v>45999</v>
       </c>
       <c r="B34" s="124" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17.25" customHeight="1">
@@ -8484,7 +8693,7 @@
         <v>46016</v>
       </c>
       <c r="B35" s="124" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17.25" customHeight="1">
@@ -8492,7 +8701,7 @@
         <v>46023</v>
       </c>
       <c r="B36" s="124" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="17.25" customHeight="1">
@@ -8500,7 +8709,7 @@
         <v>46034</v>
       </c>
       <c r="B37" s="124" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17.25" customHeight="1">
@@ -8508,7 +8717,7 @@
         <v>46104</v>
       </c>
       <c r="B38" s="124" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17.25" customHeight="1">
@@ -8516,7 +8725,7 @@
         <v>46114</v>
       </c>
       <c r="B39" s="124" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="17.25" customHeight="1">
@@ -8524,7 +8733,7 @@
         <v>46115</v>
       </c>
       <c r="B40" s="124" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17.25" customHeight="1">
@@ -8532,7 +8741,7 @@
         <v>46143</v>
       </c>
       <c r="B41" s="124" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="17.25" customHeight="1">
@@ -8540,7 +8749,7 @@
         <v>46160</v>
       </c>
       <c r="B42" s="124" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="17.25" customHeight="1">
@@ -8548,7 +8757,7 @@
         <v>46181</v>
       </c>
       <c r="B43" s="124" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="17.25" customHeight="1">
@@ -8556,7 +8765,7 @@
         <v>46188</v>
       </c>
       <c r="B44" s="124" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="17.25" customHeight="1">
@@ -8564,7 +8773,7 @@
         <v>46202</v>
       </c>
       <c r="B45" s="124" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="17.25" customHeight="1">
@@ -8572,7 +8781,7 @@
         <v>46223</v>
       </c>
       <c r="B46" s="124" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="17.25" customHeight="1">
@@ -8580,7 +8789,7 @@
         <v>46241</v>
       </c>
       <c r="B47" s="124" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="17.25" customHeight="1">
@@ -8588,7 +8797,7 @@
         <v>46251</v>
       </c>
       <c r="B48" s="124" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="17.25" customHeight="1">
@@ -8596,7 +8805,7 @@
         <v>46307</v>
       </c>
       <c r="B49" s="124" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="17.25" customHeight="1">
@@ -8604,7 +8813,7 @@
         <v>46328</v>
       </c>
       <c r="B50" s="124" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="17.25" customHeight="1">
@@ -8612,7 +8821,7 @@
         <v>46342</v>
       </c>
       <c r="B51" s="124" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="17.25" customHeight="1">
@@ -8620,7 +8829,7 @@
         <v>46364</v>
       </c>
       <c r="B52" s="124" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="17.25" customHeight="1">
@@ -8628,7 +8837,7 @@
         <v>46381</v>
       </c>
       <c r="B53" s="124" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="17.25" customHeight="1"/>
@@ -9597,7 +9806,7 @@
   <sheetData>
     <row r="1" spans="1:97" ht="15.75">
       <c r="A1" s="125" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B1" s="126"/>
       <c r="C1" s="126"/>
@@ -9655,7 +9864,7 @@
     </row>
     <row r="3" spans="1:97" ht="32.25" customHeight="1">
       <c r="A3" s="127" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="B3" s="128">
         <v>45596</v>
@@ -9948,261 +10157,261 @@
     </row>
     <row r="4" spans="1:97" ht="30.75" customHeight="1">
       <c r="A4" s="131" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="B4" s="132" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="C4" s="133" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="D4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="E4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="G4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="H4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="I4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="J4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="K4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="L4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="M4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="N4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="O4" s="134" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="P4" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Q4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="R4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="S4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="T4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="U4" s="135" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="V4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="W4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="X4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Y4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Z4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AA4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AB4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AC4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AD4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AE4" s="160" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="AF4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AG4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AH4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AI4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AJ4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AK4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AL4" s="160" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="AM4" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AN4" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AO4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AP4" s="160" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="AQ4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AR4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AS4" s="160" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="AT4" s="136" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AU4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AV4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AW4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AX4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AY4" s="160" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="AZ4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BA4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BB4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BC4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BD4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BE4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BF4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BG4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BH4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BI4" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BJ4" s="160" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="BK4" s="135" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="BL4" s="135" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="BM4" s="135" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="BN4" s="135" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="BO4" s="135" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="BP4" s="135" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="BQ4" s="135" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="BR4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BS4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BT4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BU4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BV4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BW4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BX4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BY4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BZ4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CA4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CB4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CC4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CD4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CE4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CF4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CG4" s="134"/>
       <c r="CH4" s="134"/>
       <c r="CI4" s="160" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="CJ4" s="134"/>
       <c r="CK4" s="134"/>
@@ -10214,249 +10423,249 @@
       <c r="CQ4" s="134"/>
       <c r="CR4" s="134"/>
       <c r="CS4" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:97" ht="15.75" customHeight="1">
       <c r="A5" s="131" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="B5" s="132" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="C5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="D5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="E5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="G5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="H5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="I5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="J5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="K5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="L5" s="134" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="M5" s="134" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="N5" s="134" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="O5" s="134" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="P5" s="135" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="Q5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="R5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="S5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="T5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="U5" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="V5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="W5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="X5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Y5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Z5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AA5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AB5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AC5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AD5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AE5" s="161"/>
       <c r="AF5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AG5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AH5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AI5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AJ5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AK5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AL5" s="161"/>
       <c r="AM5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AN5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AO5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AP5" s="161"/>
       <c r="AQ5" s="134" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="AR5" s="134" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="AS5" s="161"/>
       <c r="AT5" s="134" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="AU5" s="134" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="AV5" s="134" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="AW5" s="134" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="AX5" s="134" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="AY5" s="161"/>
       <c r="AZ5" s="134" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="BA5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BB5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BC5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BD5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BE5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BF5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BG5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BH5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BI5" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BJ5" s="161"/>
       <c r="BK5" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BL5" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BM5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BN5" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BO5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BP5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BQ5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BR5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BS5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BT5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BU5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BV5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BW5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BX5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BY5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BZ5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CA5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CB5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CC5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CD5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CE5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CF5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CG5" s="134"/>
       <c r="CH5" s="134"/>
@@ -10471,249 +10680,249 @@
       <c r="CQ5" s="134"/>
       <c r="CR5" s="134"/>
       <c r="CS5" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:97" ht="15.75">
       <c r="A6" s="131" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B6" s="132" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="C6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="D6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="E6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="G6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="H6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="I6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="J6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="K6" s="137" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="L6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="M6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="N6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="O6" s="134" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="P6" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Q6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="R6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="S6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="T6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="U6" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="V6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="W6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="X6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Y6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Z6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AA6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AB6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AC6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AD6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AE6" s="161"/>
       <c r="AF6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AG6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AH6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AI6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AJ6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AK6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AL6" s="161"/>
       <c r="AM6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AN6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AO6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AP6" s="161"/>
       <c r="AQ6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AR6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AS6" s="161"/>
       <c r="AT6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AU6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AV6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AW6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AX6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AY6" s="161"/>
       <c r="AZ6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BA6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BB6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BC6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BD6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BE6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BF6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BG6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BH6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BI6" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BJ6" s="161"/>
       <c r="BK6" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BL6" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BM6" s="134" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="BN6" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BO6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BP6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BQ6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BR6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BS6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BT6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BU6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BV6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BW6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BX6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BY6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BZ6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CA6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CB6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CC6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CD6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CE6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CF6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CG6" s="134"/>
       <c r="CH6" s="134"/>
@@ -10728,198 +10937,198 @@
       <c r="CQ6" s="134"/>
       <c r="CR6" s="134"/>
       <c r="CS6" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:97" ht="15.75" hidden="1" customHeight="1">
       <c r="A7" s="131" t="s">
+        <v>368</v>
+      </c>
+      <c r="B7" s="132" t="s">
+        <v>355</v>
+      </c>
+      <c r="C7" s="134" t="s">
+        <v>355</v>
+      </c>
+      <c r="D7" s="134" t="s">
+        <v>355</v>
+      </c>
+      <c r="E7" s="134" t="s">
+        <v>355</v>
+      </c>
+      <c r="F7" s="134" t="s">
+        <v>355</v>
+      </c>
+      <c r="G7" s="134" t="s">
+        <v>355</v>
+      </c>
+      <c r="H7" s="134" t="s">
+        <v>355</v>
+      </c>
+      <c r="I7" s="134" t="s">
+        <v>355</v>
+      </c>
+      <c r="J7" s="134" t="s">
+        <v>355</v>
+      </c>
+      <c r="K7" s="134" t="s">
+        <v>355</v>
+      </c>
+      <c r="L7" s="137" t="s">
+        <v>366</v>
+      </c>
+      <c r="M7" s="134" t="s">
+        <v>355</v>
+      </c>
+      <c r="N7" s="134" t="s">
+        <v>355</v>
+      </c>
+      <c r="O7" s="134" t="s">
         <v>357</v>
       </c>
-      <c r="B7" s="132" t="s">
-        <v>344</v>
-      </c>
-      <c r="C7" s="134" t="s">
-        <v>344</v>
-      </c>
-      <c r="D7" s="134" t="s">
-        <v>344</v>
-      </c>
-      <c r="E7" s="134" t="s">
-        <v>344</v>
-      </c>
-      <c r="F7" s="134" t="s">
-        <v>344</v>
-      </c>
-      <c r="G7" s="134" t="s">
-        <v>344</v>
-      </c>
-      <c r="H7" s="134" t="s">
-        <v>344</v>
-      </c>
-      <c r="I7" s="134" t="s">
-        <v>344</v>
-      </c>
-      <c r="J7" s="134" t="s">
-        <v>344</v>
-      </c>
-      <c r="K7" s="134" t="s">
-        <v>344</v>
-      </c>
-      <c r="L7" s="137" t="s">
-        <v>355</v>
-      </c>
-      <c r="M7" s="134" t="s">
-        <v>344</v>
-      </c>
-      <c r="N7" s="134" t="s">
-        <v>344</v>
-      </c>
-      <c r="O7" s="134" t="s">
-        <v>346</v>
-      </c>
       <c r="P7" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Q7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="R7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="S7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="T7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="U7" s="135" t="s">
+        <v>369</v>
+      </c>
+      <c r="V7" s="134" t="s">
+        <v>355</v>
+      </c>
+      <c r="W7" s="134" t="s">
+        <v>355</v>
+      </c>
+      <c r="X7" s="134" t="s">
+        <v>355</v>
+      </c>
+      <c r="Y7" s="134" t="s">
+        <v>355</v>
+      </c>
+      <c r="Z7" s="134" t="s">
         <v>358</v>
       </c>
-      <c r="V7" s="134" t="s">
-        <v>344</v>
-      </c>
-      <c r="W7" s="134" t="s">
-        <v>344</v>
-      </c>
-      <c r="X7" s="134" t="s">
-        <v>344</v>
-      </c>
-      <c r="Y7" s="134" t="s">
-        <v>344</v>
-      </c>
-      <c r="Z7" s="134" t="s">
-        <v>347</v>
-      </c>
       <c r="AA7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AB7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AC7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AD7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AE7" s="161"/>
       <c r="AF7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AG7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AH7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AI7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AJ7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AK7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AL7" s="161"/>
       <c r="AM7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AN7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AO7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AP7" s="161"/>
       <c r="AQ7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AR7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AS7" s="161"/>
       <c r="AT7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AU7" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AV7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AW7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AX7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AY7" s="161"/>
       <c r="AZ7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BA7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BB7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BC7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BD7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BE7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BF7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BG7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BH7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BI7" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BJ7" s="161"/>
       <c r="BK7" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BL7" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BM7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BN7" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BO7" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BP7" s="134"/>
       <c r="BQ7" s="134"/>
@@ -10927,16 +11136,16 @@
       <c r="BS7" s="134"/>
       <c r="BT7" s="134"/>
       <c r="BU7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BV7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BW7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BX7" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BY7" s="134"/>
       <c r="BZ7" s="134"/>
@@ -10962,220 +11171,220 @@
     </row>
     <row r="8" spans="1:97" ht="15.75" hidden="1" customHeight="1">
       <c r="A8" s="131" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B8" s="132" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="C8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="D8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="E8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="G8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="H8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="I8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="J8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="K8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="L8" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="M8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="N8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="O8" s="134" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="P8" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Q8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="R8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="S8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="T8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="U8" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="V8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="W8" s="134" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="X8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Y8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Z8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AA8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AB8" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AC8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AD8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AE8" s="161"/>
       <c r="AF8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AG8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AH8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AI8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AJ8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AK8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AL8" s="161"/>
       <c r="AM8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AN8" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AO8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AP8" s="161"/>
       <c r="AQ8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AR8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AS8" s="161"/>
       <c r="AT8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AU8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AV8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AW8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AX8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AY8" s="161"/>
       <c r="AZ8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BA8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BB8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BC8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BD8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BE8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BF8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BG8" s="134" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="BH8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BI8" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BJ8" s="161"/>
       <c r="BK8" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BL8" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BM8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BN8" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BO8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BP8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BQ8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BR8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BS8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BT8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BU8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BV8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BW8" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BX8" s="134" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="BY8" s="134"/>
       <c r="BZ8" s="134"/>
@@ -11201,244 +11410,244 @@
     </row>
     <row r="9" spans="1:97" ht="15.75">
       <c r="A9" s="131" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B9" s="132" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="C9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="D9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="E9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="G9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="H9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="I9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="J9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="K9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="L9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="M9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="N9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="O9" s="137" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="P9" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Q9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="R9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="S9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="T9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="U9" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="V9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="W9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="X9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Y9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Z9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AA9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AB9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AC9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AD9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AE9" s="161"/>
       <c r="AF9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AG9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AH9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AI9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AJ9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AK9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AL9" s="161"/>
       <c r="AM9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AN9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AO9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AP9" s="161"/>
       <c r="AQ9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AR9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AS9" s="161"/>
       <c r="AT9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AU9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AV9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AW9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AX9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AY9" s="161"/>
       <c r="AZ9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BA9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BB9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BC9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BD9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BE9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BF9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BG9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BH9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BI9" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BJ9" s="161"/>
       <c r="BK9" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BL9" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BM9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BN9" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BO9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BP9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BQ9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BR9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BS9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BT9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BU9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BV9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BW9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BX9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BY9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BZ9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CA9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CB9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CC9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CD9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CE9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CF9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CG9" s="134"/>
       <c r="CH9" s="134"/>
@@ -11453,249 +11662,249 @@
       <c r="CQ9" s="134"/>
       <c r="CR9" s="134"/>
       <c r="CS9" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10" spans="1:97" ht="15.75">
       <c r="A10" s="131" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B10" s="132" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="D10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="E10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="G10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="H10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="I10" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="J10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="K10" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="L10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="M10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="N10" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="O10" s="134" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="P10" s="135" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="Q10" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="R10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="S10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="T10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="U10" s="135" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="V10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="W10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="X10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Y10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Z10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AA10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AB10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AC10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AD10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AE10" s="161"/>
       <c r="AF10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AG10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AH10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AI10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AJ10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AK10" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AL10" s="161"/>
       <c r="AM10" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AN10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AO10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AP10" s="161"/>
       <c r="AQ10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AR10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AS10" s="161"/>
       <c r="AT10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AU10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AV10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AW10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AX10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AY10" s="161"/>
       <c r="AZ10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BA10" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BB10" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BC10" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BD10" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BE10" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BF10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BG10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BH10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BI10" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BJ10" s="161"/>
       <c r="BK10" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BL10" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BM10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BN10" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BO10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BP10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BQ10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BR10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BS10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BT10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BU10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BV10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BW10" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BX10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BY10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BZ10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CA10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CB10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CC10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CD10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CE10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CF10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CG10" s="134"/>
       <c r="CH10" s="134"/>
@@ -11710,249 +11919,249 @@
       <c r="CQ10" s="134"/>
       <c r="CR10" s="134"/>
       <c r="CS10" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" spans="1:97" ht="15.75">
       <c r="A11" s="131" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B11" s="132" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="D11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="E11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="G11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="H11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="I11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="J11" s="134" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="K11" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="L11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="M11" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="N11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="O11" s="134" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="P11" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Q11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="R11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="S11" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="T11" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="U11" s="135" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="V11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="W11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="X11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Y11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Z11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AA11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AB11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AC11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AD11" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AE11" s="161"/>
       <c r="AF11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AG11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AH11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AI11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AJ11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AK11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AL11" s="161"/>
       <c r="AM11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AN11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AO11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AP11" s="161"/>
       <c r="AQ11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AR11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AS11" s="161"/>
       <c r="AT11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AU11" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AV11" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AW11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AX11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AY11" s="161"/>
       <c r="AZ11" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BA11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BB11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BC11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BD11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BE11" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BF11" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BG11" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BH11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BI11" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BJ11" s="161"/>
       <c r="BK11" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BL11" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BM11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BN11" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BO11" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BP11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BQ11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BR11" s="134" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="BS11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BT11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BU11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BV11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BW11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BX11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BY11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BZ11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CA11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CB11" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="CC11" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="CD11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CE11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CF11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CG11" s="134"/>
       <c r="CH11" s="134"/>
@@ -11967,249 +12176,249 @@
       <c r="CQ11" s="134"/>
       <c r="CR11" s="134"/>
       <c r="CS11" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" spans="1:97" ht="15.75">
       <c r="A12" s="131" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="B12" s="132" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="D12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="E12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="G12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="H12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="I12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="J12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="K12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="L12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="M12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="N12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="O12" s="134" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="P12" s="135" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="Q12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="R12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="S12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="T12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="U12" s="135" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="V12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="W12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="X12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="Y12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="Z12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AA12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AB12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AC12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AD12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AE12" s="161"/>
       <c r="AF12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AG12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AH12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AI12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AJ12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AK12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AL12" s="161"/>
       <c r="AM12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AN12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AO12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AP12" s="161"/>
       <c r="AQ12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AR12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AS12" s="161"/>
       <c r="AT12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AU12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AV12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AW12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AX12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AY12" s="161"/>
       <c r="AZ12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BA12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BB12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BC12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BD12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BE12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BF12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BG12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BH12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BI12" s="135" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BJ12" s="161"/>
       <c r="BK12" s="135" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BL12" s="135" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BM12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BN12" s="135" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BO12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BP12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BQ12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BR12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BS12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BT12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BU12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BV12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BW12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BX12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BY12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="BZ12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="CA12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="CB12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CC12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="CD12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="CE12" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CF12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="CG12" s="134"/>
       <c r="CH12" s="134"/>
@@ -12224,249 +12433,249 @@
       <c r="CQ12" s="134"/>
       <c r="CR12" s="134"/>
       <c r="CS12" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
     </row>
     <row r="13" spans="1:97" ht="15.75">
       <c r="A13" s="131" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="B13" s="132" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="D13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="E13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="F13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="G13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="H13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="I13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="J13" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="K13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="L13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="M13" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="N13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="O13" s="134" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="P13" s="135" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="Q13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="R13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="S13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="T13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="U13" s="135" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="V13" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="W13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="X13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="Y13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="Z13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AA13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AB13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AC13" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AD13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AE13" s="162"/>
       <c r="AF13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AG13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AH13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AI13" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AJ13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AK13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AL13" s="162"/>
       <c r="AM13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AN13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AO13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AP13" s="162"/>
       <c r="AQ13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AR13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AS13" s="162"/>
       <c r="AT13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AU13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AV13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AW13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AX13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="AY13" s="162"/>
       <c r="AZ13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BA13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BB13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BC13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BD13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BE13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BF13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BG13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BH13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BI13" s="135" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BJ13" s="162"/>
       <c r="BK13" s="135" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BL13" s="135" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BM13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BN13" s="135" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BO13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BP13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BQ13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BR13" s="134" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="BS13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BT13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BU13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BV13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BW13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BX13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BY13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="BZ13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="CA13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="CB13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="CC13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="CD13" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CE13" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CF13" s="134" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="CG13" s="134"/>
       <c r="CH13" s="134"/>
@@ -12481,7 +12690,7 @@
       <c r="CQ13" s="134"/>
       <c r="CR13" s="134"/>
       <c r="CS13" s="134" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -13500,7 +13709,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="25.5">
       <c r="A1" s="138" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="B1" s="138" t="s">
         <v>2</v>
@@ -13524,16 +13733,16 @@
         <v>11</v>
       </c>
       <c r="I1" s="141" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="J1" s="142" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="K1" s="143" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="L1" s="141" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="M1" s="144"/>
       <c r="N1" s="144"/>
@@ -13552,10 +13761,10 @@
     </row>
     <row r="2" spans="1:26" ht="38.25">
       <c r="A2" s="145" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="B2" s="146" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="C2" s="147"/>
       <c r="D2" s="147" t="s">
@@ -13582,7 +13791,7 @@
       </c>
       <c r="K2" s="150"/>
       <c r="L2" s="151" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="M2" s="144"/>
       <c r="N2" s="144"/>
@@ -13601,16 +13810,16 @@
     </row>
     <row r="3" spans="1:26" ht="51">
       <c r="A3" s="145" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B3" s="163" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="C3" s="152" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="D3" s="147" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="E3" s="148">
         <v>45575</v>
@@ -13629,7 +13838,7 @@
       </c>
       <c r="K3" s="148"/>
       <c r="L3" s="151" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="M3" s="153"/>
       <c r="N3" s="144"/>
@@ -13648,14 +13857,14 @@
     </row>
     <row r="4" spans="1:26" ht="51">
       <c r="A4" s="145" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B4" s="161"/>
       <c r="C4" s="154" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="D4" s="147" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="E4" s="148">
         <v>45575</v>
@@ -13674,7 +13883,7 @@
       </c>
       <c r="K4" s="155"/>
       <c r="L4" s="158" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="M4" s="153"/>
       <c r="N4" s="144"/>
@@ -13693,16 +13902,16 @@
     </row>
     <row r="5" spans="1:26" ht="51">
       <c r="A5" s="145" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B5" s="141" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C5" s="147" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="D5" s="147" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="E5" s="148">
         <v>45575</v>
@@ -13721,7 +13930,7 @@
       </c>
       <c r="K5" s="148"/>
       <c r="L5" s="151" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="M5" s="153"/>
       <c r="N5" s="144"/>

--- a/Proteccion.xlsx
+++ b/Proteccion.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="399">
   <si>
     <t>Asignado a</t>
   </si>
@@ -1022,9 +1022,6 @@
   </si>
   <si>
     <t>Soporte a inconsistencias en la migración</t>
-  </si>
-  <si>
-    <t>EN PROCESO</t>
   </si>
   <si>
     <t>06/03/2026 Se han hecho trabajos de soporte para distintos m[odulos que incurrieron en errores en el momento de la migraci[on. IOnluyendo reporter[ia, consumos, formularios, visores, etc&gt; no Se ha terminado el proceso de normalizaci[on del sistema y se siguen realizando correcciones</t>
@@ -1366,10 +1363,10 @@
     <t>Internal Server Error</t>
   </si>
   <si>
+    <t>False</t>
+  </si>
+  <si>
     <t>True</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
 </sst>
 </file>
@@ -4136,7 +4133,7 @@
       NETWORKDAYS(J20,L20,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N20" s="53"/>
       <c r="O20" s="53"/>
@@ -4190,7 +4187,7 @@
         <v>85</v>
       </c>
       <c r="R21" s="73" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="129.75" customHeight="1">
@@ -4520,7 +4517,7 @@
         <v>107</v>
       </c>
       <c r="R27" s="44" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="138" customHeight="1">
@@ -5114,7 +5111,7 @@
       NETWORKDAYS(J38,L38,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="N38" s="24"/>
       <c r="O38" s="24"/>
@@ -5123,7 +5120,7 @@
         <v>139</v>
       </c>
       <c r="R38" s="80" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="162" customHeight="1">
@@ -7591,10 +7588,10 @@
       </c>
       <c r="E81" s="33"/>
       <c r="F81" s="72" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="G81" s="77">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H81" s="36">
         <f>IF(OR(J81="",K81="",K81&lt;J81),0,NETWORKDAYS(J81,K81,Hoja2!$A$2:$A$53))</f>
@@ -7609,7 +7606,9 @@
       <c r="K81" s="39">
         <v>46085</v>
       </c>
-      <c r="L81" s="39"/>
+      <c r="L81" s="39">
+        <v>46090</v>
+      </c>
       <c r="M81" s="40">
         <f ca="1">IF(OR(J81="",AND(L81="",TODAY()&lt;J81),AND(L81&lt;&gt;"",L81&lt;J81)),0,
    IF(L81="",
@@ -7617,13 +7616,15 @@
       NETWORKDAYS(J81,L81,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N81" s="39"/>
       <c r="O81" s="39">
         <v>46084</v>
       </c>
-      <c r="P81" s="39"/>
+      <c r="P81" s="39">
+        <v>46090</v>
+      </c>
       <c r="Q81" s="79" t="s">
         <v>288</v>
       </c>
@@ -7646,10 +7647,10 @@
       </c>
       <c r="E82" s="19"/>
       <c r="F82" s="54" t="s">
-        <v>292</v>
+        <v>22</v>
       </c>
       <c r="G82" s="66">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H82" s="22">
         <f>IF(OR(J82="",K82="",K82&lt;J82),0,NETWORKDAYS(J82,K82,Hoja2!$A$2:$A$53))</f>
@@ -7664,7 +7665,9 @@
       <c r="K82" s="24">
         <v>46087</v>
       </c>
-      <c r="L82" s="24"/>
+      <c r="L82" s="24">
+        <v>46091</v>
+      </c>
       <c r="M82" s="25">
         <f ca="1">IF(OR(J82="",AND(L82="",TODAY()&lt;J82),AND(L82&lt;&gt;"",L82&lt;J82)),0,
    IF(L82="",
@@ -7672,13 +7675,17 @@
       NETWORKDAYS(J82,L82,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N82" s="24"/>
-      <c r="O82" s="24"/>
-      <c r="P82" s="24"/>
+      <c r="O82" s="24">
+        <v>46090</v>
+      </c>
+      <c r="P82" s="24">
+        <v>46091</v>
+      </c>
       <c r="Q82" s="78" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="R82" s="29" t="s">
         <v>398</v>
@@ -7688,6 +7695,8 @@
   <autoFilter ref="A1:AN82">
     <filterColumn colId="15">
       <filters blank="1">
+        <filter val="09/03/2026"/>
+        <filter val="10/03/2026"/>
         <filter val="16/02/2026"/>
       </filters>
     </filterColumn>
@@ -7744,7 +7753,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="83" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I1" s="84" t="s">
         <v>8</v>
@@ -7759,7 +7768,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="84" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N1" s="86" t="s">
         <v>14</v>
@@ -7795,19 +7804,19 @@
     </row>
     <row r="2" spans="1:39" ht="29.25" customHeight="1">
       <c r="A2" s="87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B2" s="88" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="89" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D2" s="88" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="88" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F2" s="90" t="s">
         <v>22</v>
@@ -7842,19 +7851,19 @@
     </row>
     <row r="3" spans="1:39" ht="29.25" customHeight="1">
       <c r="A3" s="87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B3" s="88" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="89" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D3" s="88" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="88" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F3" s="90" t="s">
         <v>22</v>
@@ -7889,19 +7898,19 @@
     </row>
     <row r="4" spans="1:39" ht="39" customHeight="1">
       <c r="A4" s="87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B4" s="88" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="89" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D4" s="88" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="88" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F4" s="90" t="s">
         <v>22</v>
@@ -7940,19 +7949,19 @@
     </row>
     <row r="5" spans="1:39" ht="127.5">
       <c r="A5" s="87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B5" s="88" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="89" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D5" s="88" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="104" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F5" s="90" t="s">
         <v>22</v>
@@ -7991,19 +8000,19 @@
     </row>
     <row r="6" spans="1:39" ht="29.25" customHeight="1">
       <c r="A6" s="87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B6" s="88" t="s">
         <v>34</v>
       </c>
       <c r="C6" s="89" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D6" s="88" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="106" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F6" s="107" t="s">
         <v>22</v>
@@ -8042,19 +8051,19 @@
     </row>
     <row r="7" spans="1:39" ht="29.25" customHeight="1">
       <c r="A7" s="87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B7" s="88" t="s">
         <v>37</v>
       </c>
       <c r="C7" s="89" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D7" s="88" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="88" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F7" s="109" t="s">
         <v>22</v>
@@ -8093,19 +8102,19 @@
     </row>
     <row r="8" spans="1:39" ht="29.25" customHeight="1">
       <c r="A8" s="87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B8" s="88" t="s">
         <v>40</v>
       </c>
       <c r="C8" s="89" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D8" s="88" t="s">
         <v>42</v>
       </c>
       <c r="E8" s="111" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F8" s="90" t="s">
         <v>22</v>
@@ -8140,17 +8149,17 @@
     </row>
     <row r="9" spans="1:39" ht="29.25" customHeight="1">
       <c r="A9" s="87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B9" s="88" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="115" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D9" s="116"/>
       <c r="E9" s="88" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F9" s="109" t="s">
         <v>22</v>
@@ -8187,17 +8196,17 @@
     </row>
     <row r="10" spans="1:39" ht="93" customHeight="1">
       <c r="A10" s="87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B10" s="88" t="s">
         <v>47</v>
       </c>
       <c r="C10" s="115" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D10" s="116"/>
       <c r="E10" s="88" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F10" s="109" t="s">
         <v>22</v>
@@ -8232,19 +8241,19 @@
     </row>
     <row r="11" spans="1:39" ht="409.5">
       <c r="A11" s="87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B11" s="88" t="s">
         <v>50</v>
       </c>
       <c r="C11" s="89" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D11" s="88" t="s">
         <v>42</v>
       </c>
       <c r="E11" s="118" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F11" s="109" t="s">
         <v>22</v>
@@ -8281,19 +8290,19 @@
     </row>
     <row r="12" spans="1:39" ht="29.25" customHeight="1">
       <c r="A12" s="87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B12" s="88" t="s">
         <v>53</v>
       </c>
       <c r="C12" s="119" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D12" s="88" t="s">
         <v>55</v>
       </c>
       <c r="E12" s="88" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F12" s="109" t="s">
         <v>22</v>
@@ -8330,19 +8339,19 @@
     </row>
     <row r="13" spans="1:39" ht="29.25" customHeight="1">
       <c r="A13" s="87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B13" s="88" t="s">
         <v>57</v>
       </c>
       <c r="C13" s="115" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D13" s="88" t="s">
         <v>59</v>
       </c>
       <c r="E13" s="88" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F13" s="109" t="s">
         <v>22</v>
@@ -8377,7 +8386,7 @@
     </row>
     <row r="14" spans="1:39" ht="29.25" customHeight="1">
       <c r="A14" s="87" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B14" s="88" t="s">
         <v>61</v>
@@ -8387,7 +8396,7 @@
       </c>
       <c r="D14" s="120"/>
       <c r="E14" s="106" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F14" s="114" t="s">
         <v>22</v>
@@ -8450,7 +8459,7 @@
         <v>45292</v>
       </c>
       <c r="B1" s="122" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17.25" customHeight="1">
@@ -8458,7 +8467,7 @@
         <v>45299</v>
       </c>
       <c r="B2" s="122" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.25" customHeight="1">
@@ -8466,7 +8475,7 @@
         <v>45376</v>
       </c>
       <c r="B3" s="122" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17.25" customHeight="1">
@@ -8474,7 +8483,7 @@
         <v>45379</v>
       </c>
       <c r="B4" s="122" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17.25" customHeight="1">
@@ -8482,7 +8491,7 @@
         <v>45380</v>
       </c>
       <c r="B5" s="122" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17.25" customHeight="1">
@@ -8490,7 +8499,7 @@
         <v>45413</v>
       </c>
       <c r="B6" s="122" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.25" customHeight="1">
@@ -8498,7 +8507,7 @@
         <v>45425</v>
       </c>
       <c r="B7" s="122" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17.25" customHeight="1">
@@ -8506,7 +8515,7 @@
         <v>45446</v>
       </c>
       <c r="B8" s="122" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17.25" customHeight="1">
@@ -8514,7 +8523,7 @@
         <v>45453</v>
       </c>
       <c r="B9" s="122" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17.25" customHeight="1">
@@ -8522,7 +8531,7 @@
         <v>45474</v>
       </c>
       <c r="B10" s="122" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17.25" customHeight="1">
@@ -8530,7 +8539,7 @@
         <v>45493</v>
       </c>
       <c r="B11" s="122" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17.25" customHeight="1">
@@ -8538,7 +8547,7 @@
         <v>45511</v>
       </c>
       <c r="B12" s="122" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17.25" customHeight="1">
@@ -8546,7 +8555,7 @@
         <v>45523</v>
       </c>
       <c r="B13" s="122" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17.25" customHeight="1">
@@ -8554,7 +8563,7 @@
         <v>45579</v>
       </c>
       <c r="B14" s="122" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17.25" customHeight="1">
@@ -8562,7 +8571,7 @@
         <v>45600</v>
       </c>
       <c r="B15" s="122" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17.25" customHeight="1">
@@ -8570,7 +8579,7 @@
         <v>45607</v>
       </c>
       <c r="B16" s="122" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17.25" customHeight="1">
@@ -8578,7 +8587,7 @@
         <v>45634</v>
       </c>
       <c r="B17" s="122" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17.25" customHeight="1">
@@ -8586,7 +8595,7 @@
         <v>45651</v>
       </c>
       <c r="B18" s="122" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25" customHeight="1">
@@ -8594,7 +8603,7 @@
         <v>45658</v>
       </c>
       <c r="B19" s="123" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25" customHeight="1">
@@ -8602,7 +8611,7 @@
         <v>45663</v>
       </c>
       <c r="B20" s="123" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17.25" customHeight="1">
@@ -8610,7 +8619,7 @@
         <v>45740</v>
       </c>
       <c r="B21" s="123" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17.25" customHeight="1">
@@ -8618,7 +8627,7 @@
         <v>45764</v>
       </c>
       <c r="B22" s="123" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17.25" customHeight="1">
@@ -8626,7 +8635,7 @@
         <v>45765</v>
       </c>
       <c r="B23" s="123" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17.25" customHeight="1">
@@ -8634,7 +8643,7 @@
         <v>45778</v>
       </c>
       <c r="B24" s="123" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17.25" customHeight="1">
@@ -8642,7 +8651,7 @@
         <v>45810</v>
       </c>
       <c r="B25" s="123" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17.25" customHeight="1">
@@ -8650,7 +8659,7 @@
         <v>45831</v>
       </c>
       <c r="B26" s="123" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17.25" customHeight="1">
@@ -8658,7 +8667,7 @@
         <v>45838</v>
       </c>
       <c r="B27" s="123" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17.25" customHeight="1">
@@ -8666,7 +8675,7 @@
         <v>45858</v>
       </c>
       <c r="B28" s="123" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17.25" customHeight="1">
@@ -8674,7 +8683,7 @@
         <v>45876</v>
       </c>
       <c r="B29" s="123" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17.25" customHeight="1">
@@ -8682,7 +8691,7 @@
         <v>45887</v>
       </c>
       <c r="B30" s="123" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="17.25" customHeight="1">
@@ -8690,7 +8699,7 @@
         <v>45943</v>
       </c>
       <c r="B31" s="123" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="17.25" customHeight="1">
@@ -8698,7 +8707,7 @@
         <v>45964</v>
       </c>
       <c r="B32" s="123" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="17.25" customHeight="1">
@@ -8706,7 +8715,7 @@
         <v>45978</v>
       </c>
       <c r="B33" s="123" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="17.25" customHeight="1">
@@ -8714,7 +8723,7 @@
         <v>45999</v>
       </c>
       <c r="B34" s="123" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17.25" customHeight="1">
@@ -8722,7 +8731,7 @@
         <v>46016</v>
       </c>
       <c r="B35" s="123" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17.25" customHeight="1">
@@ -8730,7 +8739,7 @@
         <v>46023</v>
       </c>
       <c r="B36" s="123" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="17.25" customHeight="1">
@@ -8738,7 +8747,7 @@
         <v>46034</v>
       </c>
       <c r="B37" s="123" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17.25" customHeight="1">
@@ -8746,7 +8755,7 @@
         <v>46104</v>
       </c>
       <c r="B38" s="123" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17.25" customHeight="1">
@@ -8754,7 +8763,7 @@
         <v>46114</v>
       </c>
       <c r="B39" s="123" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="17.25" customHeight="1">
@@ -8762,7 +8771,7 @@
         <v>46115</v>
       </c>
       <c r="B40" s="123" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17.25" customHeight="1">
@@ -8770,7 +8779,7 @@
         <v>46143</v>
       </c>
       <c r="B41" s="123" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="17.25" customHeight="1">
@@ -8778,7 +8787,7 @@
         <v>46160</v>
       </c>
       <c r="B42" s="123" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="17.25" customHeight="1">
@@ -8786,7 +8795,7 @@
         <v>46181</v>
       </c>
       <c r="B43" s="123" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="17.25" customHeight="1">
@@ -8794,7 +8803,7 @@
         <v>46188</v>
       </c>
       <c r="B44" s="123" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="17.25" customHeight="1">
@@ -8802,7 +8811,7 @@
         <v>46202</v>
       </c>
       <c r="B45" s="123" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="17.25" customHeight="1">
@@ -8810,7 +8819,7 @@
         <v>46223</v>
       </c>
       <c r="B46" s="123" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="17.25" customHeight="1">
@@ -8818,7 +8827,7 @@
         <v>46241</v>
       </c>
       <c r="B47" s="123" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="17.25" customHeight="1">
@@ -8826,7 +8835,7 @@
         <v>46251</v>
       </c>
       <c r="B48" s="123" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="17.25" customHeight="1">
@@ -8834,7 +8843,7 @@
         <v>46307</v>
       </c>
       <c r="B49" s="123" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="17.25" customHeight="1">
@@ -8842,7 +8851,7 @@
         <v>46328</v>
       </c>
       <c r="B50" s="123" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="17.25" customHeight="1">
@@ -8850,7 +8859,7 @@
         <v>46342</v>
       </c>
       <c r="B51" s="123" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="17.25" customHeight="1">
@@ -8858,7 +8867,7 @@
         <v>46364</v>
       </c>
       <c r="B52" s="123" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="17.25" customHeight="1">
@@ -8866,7 +8875,7 @@
         <v>46381</v>
       </c>
       <c r="B53" s="123" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="17.25" customHeight="1"/>
@@ -9835,7 +9844,7 @@
   <sheetData>
     <row r="1" spans="1:97" ht="15.75">
       <c r="A1" s="124" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
@@ -9893,7 +9902,7 @@
     </row>
     <row r="3" spans="1:97" ht="32.25" customHeight="1">
       <c r="A3" s="126" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B3" s="127">
         <v>45596</v>
@@ -10186,261 +10195,261 @@
     </row>
     <row r="4" spans="1:97" ht="30.75" customHeight="1">
       <c r="A4" s="130" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B4" s="131" t="s">
+        <v>356</v>
+      </c>
+      <c r="C4" s="132" t="s">
         <v>357</v>
       </c>
-      <c r="C4" s="132" t="s">
+      <c r="D4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="E4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="F4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="G4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="H4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="I4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="J4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="K4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="L4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="M4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="N4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="O4" s="133" t="s">
         <v>358</v>
       </c>
-      <c r="D4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="E4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="F4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="G4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="H4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="I4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="J4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="K4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="L4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="M4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="N4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="O4" s="133" t="s">
+      <c r="P4" s="134" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="R4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="S4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="T4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="U4" s="134" t="s">
         <v>359</v>
       </c>
-      <c r="P4" s="134" t="s">
-        <v>357</v>
-      </c>
-      <c r="Q4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="R4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="S4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="T4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="U4" s="134" t="s">
+      <c r="V4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="W4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="X4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="Y4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="Z4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AA4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AB4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AC4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AD4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AE4" s="159" t="s">
         <v>360</v>
       </c>
-      <c r="V4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="W4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="X4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="Y4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="Z4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AA4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AB4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AC4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AD4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AE4" s="159" t="s">
+      <c r="AF4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AG4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AH4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AI4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AJ4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AK4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AL4" s="159" t="s">
         <v>361</v>
       </c>
-      <c r="AF4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AG4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AH4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AI4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AJ4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AK4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AL4" s="159" t="s">
+      <c r="AM4" s="133" t="s">
+        <v>359</v>
+      </c>
+      <c r="AN4" s="133" t="s">
+        <v>359</v>
+      </c>
+      <c r="AO4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AP4" s="159" t="s">
         <v>362</v>
       </c>
-      <c r="AM4" s="133" t="s">
-        <v>360</v>
-      </c>
-      <c r="AN4" s="133" t="s">
-        <v>360</v>
-      </c>
-      <c r="AO4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AP4" s="159" t="s">
+      <c r="AQ4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AR4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AS4" s="159" t="s">
+        <v>362</v>
+      </c>
+      <c r="AT4" s="135" t="s">
+        <v>356</v>
+      </c>
+      <c r="AU4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AV4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AW4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AX4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AY4" s="159" t="s">
+        <v>362</v>
+      </c>
+      <c r="AZ4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="BA4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="BB4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="BC4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="BD4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="BE4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="BF4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="BG4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="BH4" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="BI4" s="134" t="s">
+        <v>356</v>
+      </c>
+      <c r="BJ4" s="159" t="s">
+        <v>362</v>
+      </c>
+      <c r="BK4" s="134" t="s">
         <v>363</v>
       </c>
-      <c r="AQ4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AR4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AS4" s="159" t="s">
+      <c r="BL4" s="134" t="s">
         <v>363</v>
       </c>
-      <c r="AT4" s="135" t="s">
-        <v>357</v>
-      </c>
-      <c r="AU4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AV4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AW4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AX4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AY4" s="159" t="s">
+      <c r="BM4" s="134" t="s">
         <v>363</v>
       </c>
-      <c r="AZ4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="BA4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="BB4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="BC4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="BD4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="BE4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="BF4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="BG4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="BH4" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="BI4" s="134" t="s">
-        <v>357</v>
-      </c>
-      <c r="BJ4" s="159" t="s">
+      <c r="BN4" s="134" t="s">
         <v>363</v>
       </c>
-      <c r="BK4" s="134" t="s">
-        <v>364</v>
-      </c>
-      <c r="BL4" s="134" t="s">
-        <v>364</v>
-      </c>
-      <c r="BM4" s="134" t="s">
-        <v>364</v>
-      </c>
-      <c r="BN4" s="134" t="s">
-        <v>364</v>
-      </c>
       <c r="BO4" s="134" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="BP4" s="134" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="BQ4" s="134" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="BR4" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BS4" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BT4" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BU4" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BV4" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BW4" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BX4" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BY4" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BZ4" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CA4" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CB4" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CC4" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CD4" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CE4" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CF4" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CG4" s="133"/>
       <c r="CH4" s="133"/>
       <c r="CI4" s="159" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="CJ4" s="133"/>
       <c r="CK4" s="133"/>
@@ -10452,249 +10461,249 @@
       <c r="CQ4" s="133"/>
       <c r="CR4" s="133"/>
       <c r="CS4" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:97" ht="15.75" customHeight="1">
       <c r="A5" s="130" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B5" s="131" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L5" s="133" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M5" s="133" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="N5" s="133" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O5" s="133" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="P5" s="134" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="R5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="S5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="T5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="U5" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="V5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="W5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="X5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Y5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Z5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AA5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AC5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AE5" s="160"/>
       <c r="AF5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AH5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AI5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AJ5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AK5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AL5" s="160"/>
       <c r="AM5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AN5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AO5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AP5" s="160"/>
       <c r="AQ5" s="133" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AR5" s="133" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AS5" s="160"/>
       <c r="AT5" s="133" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AU5" s="133" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AV5" s="133" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AW5" s="133" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AX5" s="133" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AY5" s="160"/>
       <c r="AZ5" s="133" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="BA5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BB5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BC5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BD5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BE5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BF5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BG5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BH5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BI5" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BJ5" s="160"/>
       <c r="BK5" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BL5" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BM5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BN5" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BO5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BP5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BQ5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BR5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BS5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BT5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BU5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BV5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BW5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BX5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BY5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BZ5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CA5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CB5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CC5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CD5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CE5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CF5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CG5" s="133"/>
       <c r="CH5" s="133"/>
@@ -10709,249 +10718,249 @@
       <c r="CQ5" s="133"/>
       <c r="CR5" s="133"/>
       <c r="CS5" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:97" ht="15.75">
       <c r="A6" s="130" t="s">
+        <v>366</v>
+      </c>
+      <c r="B6" s="131" t="s">
+        <v>356</v>
+      </c>
+      <c r="C6" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="D6" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="E6" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="F6" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="G6" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="H6" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="I6" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="K6" s="136" t="s">
         <v>367</v>
       </c>
-      <c r="B6" s="131" t="s">
-        <v>357</v>
-      </c>
-      <c r="C6" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="D6" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="E6" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="F6" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="G6" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="H6" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="I6" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="J6" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="K6" s="136" t="s">
-        <v>368</v>
-      </c>
       <c r="L6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O6" s="133" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P6" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="R6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="S6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="T6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="U6" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="V6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="W6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="X6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Y6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Z6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AA6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AC6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AE6" s="160"/>
       <c r="AF6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AH6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AI6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AJ6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AK6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AL6" s="160"/>
       <c r="AM6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AN6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AO6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AP6" s="160"/>
       <c r="AQ6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AR6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AS6" s="160"/>
       <c r="AT6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AU6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AV6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AW6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AX6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AY6" s="160"/>
       <c r="AZ6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BA6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BB6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BC6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BD6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BE6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BF6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BG6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BH6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BI6" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BJ6" s="160"/>
       <c r="BK6" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BL6" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BM6" s="133" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="BN6" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BO6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BP6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BQ6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BR6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BS6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BT6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BU6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BV6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BW6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BX6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BY6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BZ6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CA6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CB6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CC6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CD6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CE6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CF6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CG6" s="133"/>
       <c r="CH6" s="133"/>
@@ -10966,198 +10975,198 @@
       <c r="CQ6" s="133"/>
       <c r="CR6" s="133"/>
       <c r="CS6" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="7" spans="1:97" ht="15.75" hidden="1" customHeight="1">
       <c r="A7" s="130" t="s">
+        <v>369</v>
+      </c>
+      <c r="B7" s="131" t="s">
+        <v>356</v>
+      </c>
+      <c r="C7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="D7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="E7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="F7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="G7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="H7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="I7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="J7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="K7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="L7" s="136" t="s">
+        <v>367</v>
+      </c>
+      <c r="M7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="N7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="O7" s="133" t="s">
+        <v>358</v>
+      </c>
+      <c r="P7" s="134" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="R7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="S7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="T7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="U7" s="134" t="s">
         <v>370</v>
       </c>
-      <c r="B7" s="131" t="s">
-        <v>357</v>
-      </c>
-      <c r="C7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="D7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="E7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="F7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="G7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="H7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="I7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="J7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="K7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="L7" s="136" t="s">
-        <v>368</v>
-      </c>
-      <c r="M7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="N7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="O7" s="133" t="s">
+      <c r="V7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="W7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="X7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="Y7" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="Z7" s="133" t="s">
         <v>359</v>
       </c>
-      <c r="P7" s="134" t="s">
-        <v>357</v>
-      </c>
-      <c r="Q7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="R7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="S7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="T7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="U7" s="134" t="s">
-        <v>371</v>
-      </c>
-      <c r="V7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="W7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="X7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="Y7" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="Z7" s="133" t="s">
-        <v>360</v>
-      </c>
       <c r="AA7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AC7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AE7" s="160"/>
       <c r="AF7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AH7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AI7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AJ7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AK7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AL7" s="160"/>
       <c r="AM7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AN7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AO7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AP7" s="160"/>
       <c r="AQ7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AR7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AS7" s="160"/>
       <c r="AT7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AU7" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AV7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AW7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AX7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AY7" s="160"/>
       <c r="AZ7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BA7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BB7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BC7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BD7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BE7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BF7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BG7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BH7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BI7" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BJ7" s="160"/>
       <c r="BK7" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BL7" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BM7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BN7" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BO7" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BP7" s="133"/>
       <c r="BQ7" s="133"/>
@@ -11165,16 +11174,16 @@
       <c r="BS7" s="133"/>
       <c r="BT7" s="133"/>
       <c r="BU7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BV7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BW7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BX7" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BY7" s="133"/>
       <c r="BZ7" s="133"/>
@@ -11200,220 +11209,220 @@
     </row>
     <row r="8" spans="1:97" ht="15.75" hidden="1" customHeight="1">
       <c r="A8" s="130" t="s">
+        <v>371</v>
+      </c>
+      <c r="B8" s="131" t="s">
+        <v>356</v>
+      </c>
+      <c r="C8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="D8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="E8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="F8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="G8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="H8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="I8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="J8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="K8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="L8" s="133" t="s">
+        <v>359</v>
+      </c>
+      <c r="M8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="N8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="O8" s="133" t="s">
+        <v>358</v>
+      </c>
+      <c r="P8" s="134" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="R8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="S8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="T8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="U8" s="134" t="s">
+        <v>356</v>
+      </c>
+      <c r="V8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="W8" s="133" t="s">
         <v>372</v>
       </c>
-      <c r="B8" s="131" t="s">
-        <v>357</v>
-      </c>
-      <c r="C8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="D8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="E8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="F8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="G8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="H8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="I8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="J8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="K8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="L8" s="133" t="s">
-        <v>360</v>
-      </c>
-      <c r="M8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="N8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="O8" s="133" t="s">
+      <c r="X8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="Y8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="Z8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AA8" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="AB8" s="133" t="s">
         <v>359</v>
       </c>
-      <c r="P8" s="134" t="s">
-        <v>357</v>
-      </c>
-      <c r="Q8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="R8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="S8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="T8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="U8" s="134" t="s">
-        <v>357</v>
-      </c>
-      <c r="V8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="W8" s="133" t="s">
-        <v>373</v>
-      </c>
-      <c r="X8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="Y8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="Z8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AA8" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="AB8" s="133" t="s">
-        <v>360</v>
-      </c>
       <c r="AC8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AE8" s="160"/>
       <c r="AF8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AH8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AI8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AJ8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AK8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AL8" s="160"/>
       <c r="AM8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AN8" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AO8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AP8" s="160"/>
       <c r="AQ8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AR8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AS8" s="160"/>
       <c r="AT8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AU8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AV8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AW8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AX8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AY8" s="160"/>
       <c r="AZ8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BA8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BB8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BC8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BD8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BE8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BF8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BG8" s="133" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="BH8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BI8" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BJ8" s="160"/>
       <c r="BK8" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BL8" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BM8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BN8" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BO8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BP8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BQ8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BR8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BS8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BT8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BU8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BV8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BW8" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BX8" s="133" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="BY8" s="133"/>
       <c r="BZ8" s="133"/>
@@ -11439,244 +11448,244 @@
     </row>
     <row r="9" spans="1:97" ht="15.75">
       <c r="A9" s="130" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B9" s="131" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O9" s="136" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P9" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="R9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="S9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="T9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="U9" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="V9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="W9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="X9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Y9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Z9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AA9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AC9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AE9" s="160"/>
       <c r="AF9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AH9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AI9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AJ9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AK9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AL9" s="160"/>
       <c r="AM9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AN9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AO9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AP9" s="160"/>
       <c r="AQ9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AR9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AS9" s="160"/>
       <c r="AT9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AU9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AV9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AW9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AX9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AY9" s="160"/>
       <c r="AZ9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BA9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BB9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BC9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BD9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BE9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BF9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BG9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BH9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BI9" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BJ9" s="160"/>
       <c r="BK9" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BL9" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BM9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BN9" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BO9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BP9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BQ9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BR9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BS9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BT9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BU9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BV9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BW9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BX9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BY9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BZ9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CA9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CB9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CC9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CD9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CE9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CF9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CG9" s="133"/>
       <c r="CH9" s="133"/>
@@ -11691,249 +11700,249 @@
       <c r="CQ9" s="133"/>
       <c r="CR9" s="133"/>
       <c r="CS9" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:97" ht="15.75">
       <c r="A10" s="130" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B10" s="131" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I10" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K10" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N10" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="O10" s="133" t="s">
+        <v>358</v>
+      </c>
+      <c r="P10" s="134" t="s">
         <v>359</v>
       </c>
-      <c r="P10" s="134" t="s">
-        <v>360</v>
-      </c>
       <c r="Q10" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="R10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="S10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="T10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="U10" s="134" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="V10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="W10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="X10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Y10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Z10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AA10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AC10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AE10" s="160"/>
       <c r="AF10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AH10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AI10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AJ10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AK10" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AL10" s="160"/>
       <c r="AM10" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AN10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AO10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AP10" s="160"/>
       <c r="AQ10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AR10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AS10" s="160"/>
       <c r="AT10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AU10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AV10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AW10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AX10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AY10" s="160"/>
       <c r="AZ10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BA10" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BB10" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BC10" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BD10" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BE10" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BF10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BG10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BH10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BI10" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BJ10" s="160"/>
       <c r="BK10" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BL10" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BM10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BN10" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BO10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BP10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BQ10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BR10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BS10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BT10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BU10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BV10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BW10" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BX10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BY10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BZ10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CA10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CB10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CC10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CD10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CE10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CF10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CG10" s="133"/>
       <c r="CH10" s="133"/>
@@ -11948,249 +11957,249 @@
       <c r="CQ10" s="133"/>
       <c r="CR10" s="133"/>
       <c r="CS10" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="1:97" ht="15.75">
       <c r="A11" s="130" t="s">
+        <v>377</v>
+      </c>
+      <c r="B11" s="131" t="s">
+        <v>356</v>
+      </c>
+      <c r="C11" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="D11" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="E11" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="F11" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="G11" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="H11" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="I11" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="J11" s="133" t="s">
         <v>378</v>
       </c>
-      <c r="B11" s="131" t="s">
-        <v>357</v>
-      </c>
-      <c r="C11" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="D11" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="E11" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="F11" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="G11" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="H11" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="I11" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="J11" s="133" t="s">
-        <v>379</v>
-      </c>
       <c r="K11" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M11" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="N11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O11" s="133" t="s">
+        <v>358</v>
+      </c>
+      <c r="P11" s="134" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q11" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="R11" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="S11" s="133" t="s">
         <v>359</v>
       </c>
-      <c r="P11" s="134" t="s">
-        <v>357</v>
-      </c>
-      <c r="Q11" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="R11" s="133" t="s">
-        <v>357</v>
-      </c>
-      <c r="S11" s="133" t="s">
-        <v>360</v>
-      </c>
       <c r="T11" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="U11" s="134" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="V11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="W11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="X11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Y11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Z11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AA11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AC11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD11" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AE11" s="160"/>
       <c r="AF11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AH11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AI11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AJ11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AK11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AL11" s="160"/>
       <c r="AM11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AN11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AO11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AP11" s="160"/>
       <c r="AQ11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AR11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AS11" s="160"/>
       <c r="AT11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AU11" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AV11" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AW11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AX11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AY11" s="160"/>
       <c r="AZ11" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BA11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BB11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BC11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BD11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BE11" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BF11" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BG11" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BH11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BI11" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BJ11" s="160"/>
       <c r="BK11" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BL11" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BM11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BN11" s="134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BO11" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BP11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BQ11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BR11" s="133" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="BS11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BT11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BU11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BV11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BW11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BX11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BY11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BZ11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CA11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CB11" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="CC11" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="CD11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CE11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CF11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CG11" s="133"/>
       <c r="CH11" s="133"/>
@@ -12205,249 +12214,249 @@
       <c r="CQ11" s="133"/>
       <c r="CR11" s="133"/>
       <c r="CS11" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" spans="1:97" ht="15.75">
       <c r="A12" s="130" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B12" s="131" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="N12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="O12" s="133" t="s">
+        <v>358</v>
+      </c>
+      <c r="P12" s="134" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q12" s="133" t="s">
         <v>359</v>
       </c>
-      <c r="P12" s="134" t="s">
-        <v>357</v>
-      </c>
-      <c r="Q12" s="133" t="s">
-        <v>360</v>
-      </c>
       <c r="R12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="S12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="T12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="U12" s="134" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="V12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="W12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="X12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Y12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Z12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AA12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AB12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AC12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AE12" s="160"/>
       <c r="AF12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AH12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AI12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AJ12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AK12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AL12" s="160"/>
       <c r="AM12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AN12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AO12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AP12" s="160"/>
       <c r="AQ12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AR12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AS12" s="160"/>
       <c r="AT12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AU12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AV12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AW12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AX12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AY12" s="160"/>
       <c r="AZ12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BA12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BB12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BC12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BD12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BE12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BF12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BG12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BH12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BI12" s="134" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BJ12" s="160"/>
       <c r="BK12" s="134" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BL12" s="134" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BM12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BN12" s="134" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BO12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BP12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BQ12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BR12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BS12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BT12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BU12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BV12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BW12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BX12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BY12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BZ12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="CA12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="CB12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CC12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="CD12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="CE12" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CF12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="CG12" s="133"/>
       <c r="CH12" s="133"/>
@@ -12462,249 +12471,249 @@
       <c r="CQ12" s="133"/>
       <c r="CR12" s="133"/>
       <c r="CS12" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="13" spans="1:97" ht="15.75">
       <c r="A13" s="130" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B13" s="131" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J13" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M13" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="N13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="O13" s="133" t="s">
+        <v>358</v>
+      </c>
+      <c r="P13" s="134" t="s">
         <v>359</v>
       </c>
-      <c r="P13" s="134" t="s">
-        <v>360</v>
-      </c>
       <c r="Q13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="R13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="S13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="T13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="U13" s="134" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="V13" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="W13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="X13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Y13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Z13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AA13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AB13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AC13" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AD13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AE13" s="161"/>
       <c r="AF13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AH13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AI13" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AJ13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AK13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AL13" s="161"/>
       <c r="AM13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AN13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AO13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AP13" s="161"/>
       <c r="AQ13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AR13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AS13" s="161"/>
       <c r="AT13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AU13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AV13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AW13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AX13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AY13" s="161"/>
       <c r="AZ13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BA13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BB13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BC13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BD13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BE13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BF13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BG13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BH13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BI13" s="134" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BJ13" s="161"/>
       <c r="BK13" s="134" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BL13" s="134" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BM13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BN13" s="134" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BO13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BP13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BQ13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BR13" s="133" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="BS13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BT13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BU13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BV13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BW13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BX13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BY13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BZ13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="CA13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="CB13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="CC13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="CD13" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CE13" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CF13" s="133" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="CG13" s="133"/>
       <c r="CH13" s="133"/>
@@ -12719,7 +12728,7 @@
       <c r="CQ13" s="133"/>
       <c r="CR13" s="133"/>
       <c r="CS13" s="133" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -13738,7 +13747,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="25.5">
       <c r="A1" s="137" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B1" s="137" t="s">
         <v>2</v>
@@ -13762,16 +13771,16 @@
         <v>11</v>
       </c>
       <c r="I1" s="140" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J1" s="141" t="s">
+        <v>383</v>
+      </c>
+      <c r="K1" s="142" t="s">
         <v>384</v>
       </c>
-      <c r="K1" s="142" t="s">
+      <c r="L1" s="140" t="s">
         <v>385</v>
-      </c>
-      <c r="L1" s="140" t="s">
-        <v>386</v>
       </c>
       <c r="M1" s="143"/>
       <c r="N1" s="143"/>
@@ -13790,10 +13799,10 @@
     </row>
     <row r="2" spans="1:26" ht="38.25">
       <c r="A2" s="144" t="s">
+        <v>386</v>
+      </c>
+      <c r="B2" s="145" t="s">
         <v>387</v>
-      </c>
-      <c r="B2" s="145" t="s">
-        <v>388</v>
       </c>
       <c r="C2" s="146"/>
       <c r="D2" s="146" t="s">
@@ -13820,7 +13829,7 @@
       </c>
       <c r="K2" s="149"/>
       <c r="L2" s="150" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="M2" s="143"/>
       <c r="N2" s="143"/>
@@ -13839,16 +13848,16 @@
     </row>
     <row r="3" spans="1:26" ht="51">
       <c r="A3" s="144" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B3" s="162" t="s">
+        <v>389</v>
+      </c>
+      <c r="C3" s="151" t="s">
         <v>390</v>
       </c>
-      <c r="C3" s="151" t="s">
+      <c r="D3" s="146" t="s">
         <v>391</v>
-      </c>
-      <c r="D3" s="146" t="s">
-        <v>392</v>
       </c>
       <c r="E3" s="147">
         <v>45575</v>
@@ -13867,7 +13876,7 @@
       </c>
       <c r="K3" s="147"/>
       <c r="L3" s="150" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="M3" s="152"/>
       <c r="N3" s="143"/>
@@ -13886,14 +13895,14 @@
     </row>
     <row r="4" spans="1:26" ht="51">
       <c r="A4" s="144" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B4" s="160"/>
       <c r="C4" s="153" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D4" s="146" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E4" s="147">
         <v>45575</v>
@@ -13912,7 +13921,7 @@
       </c>
       <c r="K4" s="154"/>
       <c r="L4" s="157" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="M4" s="152"/>
       <c r="N4" s="143"/>
@@ -13931,16 +13940,16 @@
     </row>
     <row r="5" spans="1:26" ht="51">
       <c r="A5" s="144" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B5" s="140" t="s">
+        <v>395</v>
+      </c>
+      <c r="C5" s="146" t="s">
         <v>396</v>
       </c>
-      <c r="C5" s="146" t="s">
-        <v>397</v>
-      </c>
       <c r="D5" s="146" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E5" s="147">
         <v>45575</v>
@@ -13959,7 +13968,7 @@
       </c>
       <c r="K5" s="147"/>
       <c r="L5" s="150" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="M5" s="152"/>
       <c r="N5" s="143"/>

--- a/Proteccion.xlsx
+++ b/Proteccion.xlsx
@@ -19,7 +19,7 @@
     <sheet name="pruebas i" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'EN PROCESO (Proteccíon)'!$A$1:$AN$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'EN PROCESO (Proteccíon)'!$A$1:$AN$85</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="408">
   <si>
     <t>Asignado a</t>
   </si>
@@ -719,11 +719,9 @@
     <t>Creación de la base del proyecto para la extrrasión de datos de filenet</t>
   </si>
   <si>
-    <t>EN TEST</t>
-  </si>
-  <si>
     <t>29/12/2025 Se habia aplazado en muchos momentos durante diciembre y debido a permisos en la bandeja se dificultó el acceso
-06/03/2026 Hace parte de un grupo de funcionalidades que ya están probadas y son funcionales, pero el módulo aún le hace falta y todavía nada se ha pasado a producción. Esto último se debe a que se han priorizado otras tareas incluyendo el tema de migración el cual debía realizarse antes de pasar todo el proyecto y pedir los permisos de conexión al portal de BPO</t>
+06/03/2026 Hace parte de un grupo de funcionalidades que ya están probadas y son funcionales, pero el módulo aún le hace falta y todavía nada se ha pasado a producción. Esto último se debe a que se han priorizado otras tareas incluyendo el tema de migración el cual debía realizarse antes de pasar todo el proyecto y pedir los permisos de conexión al portal de BPO
+11/03/2026 Se migra la lógica y los servicios del local a producción</t>
   </si>
   <si>
     <t>Interno-H16-3</t>
@@ -734,7 +732,8 @@
   <si>
     <t>05/01/2026 Se crea servicio que se comunica con la extracción de filente y que además captura el inicio de sesión de la plataforma para empezar a trabajar automatizadamente con esta 
 13/01/2026 se completa el servicio, se se divide la lógica en tareas ejecutables y se desarrolla la persistencia 
-06/03/2026 Hace parte de un grupo de funcionalidades que ya están probadas y son funcionales, pero el módulo aún le hace falta y todavía nada se ha pasado a producción. Esto último se debe a que se han priorizado otras tareas incluyendo el tema de migración el cual debía realizarse antes de pasar todo el proyecto y pedir los permisos de conexión al portal de BPO</t>
+06/03/2026 Hace parte de un grupo de funcionalidades que ya están probadas y son funcionales, pero el módulo aún le hace falta y todavía nada se ha pasado a producción. Esto último se debe a que se han priorizado otras tareas incluyendo el tema de migración el cual debía realizarse antes de pasar todo el proyecto y pedir los permisos de conexión al portal de BPO
+11/03/2026 Se migra la lógica y los servicios del local a producción</t>
   </si>
   <si>
     <t>REQ-21</t>
@@ -757,7 +756,8 @@
   <si>
     <t>14/01/2026 Se crea lógica de persistencia para activar servicio
 16/01/2026 Se completa la llógica del servicio, se construye la base y se da respuesta constante para luego poder realizar implementación
-06/03/2026 Hace parte de un grupo de funcionalidades que ya están probadas y son funcionales, pero el módulo aún le hace falta y todavía nada se ha pasado a producción. Esto último se debe a que se han priorizado otras tareas incluyendo el tema de migración el cual debía realizarse antes de pasar todo el proyecto y pedir los permisos de conexión al portal de BPO</t>
+06/03/2026 Hace parte de un grupo de funcionalidades que ya están probadas y son funcionales, pero el módulo aún le hace falta y todavía nada se ha pasado a producción. Esto último se debe a que se han priorizado otras tareas incluyendo el tema de migración el cual debía realizarse antes de pasar todo el proyecto y pedir los permisos de conexión al portal de BPO
+11/03/2026 Se migra la lógica y los servicios del local a producción</t>
   </si>
   <si>
     <t>REQ-17</t>
@@ -779,7 +779,8 @@
   </si>
   <si>
     <t>26/01/2026 Se retoma el trabajo después de identificar las correcciones y nuevos elementos por analizar en el back. Sin embargo, hace falta un escenario por parametrizar que no se pudo encontrar un ejemplo
-06/03/2026 Hace parte de un grupo de funcionalidades que ya están probadas y son funcionales, pero el módulo aún le hace falta y todavía nada se ha pasado a producción. Esto último se debe a que se han priorizado otras tareas incluyendo el tema de migración el cual debía realizarse antes de pasar todo el proyecto y pedir los permisos de conexión al portal de BPO</t>
+06/03/2026 Hace parte de un grupo de funcionalidades que ya están probadas y son funcionales, pero el módulo aún le hace falta y todavía nada se ha pasado a producción. Esto último se debe a que se han priorizado otras tareas incluyendo el tema de migración el cual debía realizarse antes de pasar todo el proyecto y pedir los permisos de conexión al portal de BPO
+11/03/2026 Se migra la lógica y los servicios del local a producción</t>
   </si>
   <si>
     <t>Interno-H16-6</t>
@@ -806,7 +807,8 @@
     <t>Corrección de datos para acoplar a las necesidades y todos los casos posibles del proceso</t>
   </si>
   <si>
-    <t>06/03/2026 Hace parte de un grupo de funcionalidades que ya están probadas y son funcionales, pero el módulo aún le hace falta y todavía nada se ha pasado a producción. Esto último se debe a que se han priorizado otras tareas incluyendo el tema de migración el cual debía realizarse antes de pasar todo el proyecto y pedir los permisos de conexión al portal de BPO</t>
+    <t>06/03/2026 Hace parte de un grupo de funcionalidades que ya están probadas y son funcionales, pero el módulo aún le hace falta y todavía nada se ha pasado a producción. Esto último se debe a que se han priorizado otras tareas incluyendo el tema de migración el cual debía realizarse antes de pasar todo el proyecto y pedir los permisos de conexión al portal de BPO
+11/03/2026 Se migra la lógica y los servicios del local a producción</t>
   </si>
   <si>
     <t>REQ-20</t>
@@ -841,7 +843,8 @@
   </si>
   <si>
     <t>28/01/2026 Se encontraron dificultades en el acomplamiento de los servicios sobre todo hacia filenet, pero se puedo implementar todo el flujo
-06/03/2026 Hace parte de un grupo de funcionalidades que ya están probadas y son funcionales, pero el módulo aún le hace falta y todavía nada se ha pasado a producción. Esto último se debe a que se han priorizado otras tareas incluyendo el tema de migración el cual debía realizarse antes de pasar todo el proyecto y pedir los permisos de conexión al portal de BPO</t>
+06/03/2026 Hace parte de un grupo de funcionalidades que ya están probadas y son funcionales, pero el módulo aún le hace falta y todavía nada se ha pasado a producción. Esto último se debe a que se han priorizado otras tareas incluyendo el tema de migración el cual debía realizarse antes de pasar todo el proyecto y pedir los permisos de conexión al portal de BPO
+11/03/2026 Se migra la lógica y los servicios del local a producción</t>
   </si>
   <si>
     <t>Interno-H16-9</t>
@@ -852,7 +855,8 @@
   <si>
     <t>29/01/2026 Se termina la implementación y me encuentro en pruebas de funcionamiento
 03/02/2026 Se pudo lograr realizar una prueba depunto a punto exitosa
-06/03/2026 Hace parte de un grupo de funcionalidades que ya están probadas y son funcionales, pero el módulo aún le hace falta y todavía nada se ha pasado a producción. Esto último se debe a que se han priorizado otras tareas incluyendo el tema de migración el cual debía realizarse antes de pasar todo el proyecto y pedir los permisos de conexión al portal de BPO</t>
+06/03/2026 Hace parte de un grupo de funcionalidades que ya están probadas y son funcionales, pero el módulo aún le hace falta y todavía nada se ha pasado a producción. Esto último se debe a que se han priorizado otras tareas incluyendo el tema de migración el cual debía realizarse antes de pasar todo el proyecto y pedir los permisos de conexión al portal de BPO
+11/03/2026 Se migra la lógica y los servicios del local a producción</t>
   </si>
   <si>
     <t>Interno-H16-10</t>
@@ -880,7 +884,8 @@
   </si>
   <si>
     <t>04/02/2026 Se cambia la lógica actual que estaba presentando lentitud en la gestión del operador por una asyncrona que se renueva todos los días
-06/03/2026 Hace parte de un grupo de funcionalidades que ya están probadas y son funcionales, pero el módulo aún le hace falta y todavía nada se ha pasado a producción. Esto último se debe a que se han priorizado otras tareas incluyendo el tema de migración el cual debía realizarse antes de pasar todo el proyecto y pedir los permisos de conexión al portal de BPO</t>
+06/03/2026 Hace parte de un grupo de funcionalidades que ya están probadas y son funcionales, pero el módulo aún le hace falta y todavía nada se ha pasado a producción. Esto último se debe a que se han priorizado otras tareas incluyendo el tema de migración el cual debía realizarse antes de pasar todo el proyecto y pedir los permisos de conexión al portal de BPO
+11/03/2026 Se migra la lógica y los servicios del local a producción</t>
   </si>
   <si>
     <t>Interno-H16-12</t>
@@ -1025,6 +1030,34 @@
   </si>
   <si>
     <t>06/03/2026 Se han hecho trabajos de soporte para distintos m[odulos que incurrieron en errores en el momento de la migraci[on. IOnluyendo reporter[ia, consumos, formularios, visores, etc&gt; no Se ha terminado el proceso de normalizaci[on del sistema y se siguen realizando correcciones</t>
+  </si>
+  <si>
+    <t>Interno-H16-16</t>
+  </si>
+  <si>
+    <t>Pruebas y acople del desarrollo al ambiente nuevo en producción</t>
+  </si>
+  <si>
+    <t>EN PROCESO</t>
+  </si>
+  <si>
+    <t>Interno-H16-17</t>
+  </si>
+  <si>
+    <t>Identificación y validación del código proporcionado por Don Hernan</t>
+  </si>
+  <si>
+    <t>Migración de módulo de auxilios a tecnologías más modernas</t>
+  </si>
+  <si>
+    <t>12/03/2026 Se termina de realizar la validacion del código y su funcionamiento. Se encuentra que el código fuie prepadrado para otra unidada y se le indica a Don Hernan</t>
+  </si>
+  <si>
+    <t>REQ-28-2</t>
+  </si>
+  <si>
+    <t>13/03/2026 Se encontraron errores en el proceso que estaba presentando problemas problemas delicacdos en el flujo, tanto para las trámites abiertos en investigación como los trámites gestionados en glosas. Se realizan todas las validaciones, cambios y verificaciones y se consigue solventar los problemas
+16/03/2026 Se terminan de validar unos casos asociados al problema y se corrigen</t>
   </si>
   <si>
     <t>dias estimados</t>
@@ -1364,6 +1397,9 @@
   </si>
   <si>
     <t>False</t>
+  </si>
+  <si>
+    <t>true</t>
   </si>
   <si>
     <t>True</t>
@@ -2028,7 +2064,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2478,6 +2514,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2851,10 +2889,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FF93C47D"/>
   </sheetPr>
-  <dimension ref="A1:AN82"/>
+  <dimension ref="A1:AN85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.21875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3007,8 +3045,8 @@
       <c r="Q2" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="29" t="s">
-        <v>398</v>
+      <c r="R2" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:40" ht="29.25" customHeight="1">
@@ -3062,11 +3100,11 @@
       <c r="Q3" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="R3" s="44" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="4" spans="1:40" ht="29.25" hidden="1" customHeight="1">
+      <c r="R3" s="164" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40" ht="29.25" customHeight="1">
       <c r="A4" s="16" t="s">
         <v>18</v>
       </c>
@@ -3121,11 +3159,11 @@
       <c r="Q4" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="R4" s="29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:40" ht="29.25" hidden="1" customHeight="1">
+      <c r="R4" s="29" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" ht="29.25" customHeight="1">
       <c r="A5" s="30" t="s">
         <v>18</v>
       </c>
@@ -3180,11 +3218,11 @@
       <c r="Q5" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="R5" s="44" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:40" ht="29.25" hidden="1" customHeight="1">
+      <c r="R5" s="44" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40" ht="29.25" customHeight="1">
       <c r="A6" s="16" t="s">
         <v>18</v>
       </c>
@@ -3239,11 +3277,11 @@
       <c r="Q6" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="R6" s="29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:40" ht="29.25" hidden="1" customHeight="1">
+      <c r="R6" s="29" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="7" spans="1:40" ht="29.25" customHeight="1">
       <c r="A7" s="30" t="s">
         <v>18</v>
       </c>
@@ -3298,8 +3336,8 @@
       <c r="Q7" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="R7" s="44" t="b">
-        <v>1</v>
+      <c r="R7" s="44" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="8" spans="1:40" ht="29.25" customHeight="1">
@@ -3353,8 +3391,8 @@
       <c r="Q8" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="R8" s="29" t="s">
-        <v>398</v>
+      <c r="R8" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="9" spans="1:40" ht="29.25" customHeight="1">
@@ -3408,8 +3446,8 @@
       <c r="Q9" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="R9" s="44" t="s">
-        <v>398</v>
+      <c r="R9" s="164" t="s">
+        <v>406</v>
       </c>
       <c r="S9" s="57"/>
       <c r="T9" s="57"/>
@@ -3483,8 +3521,8 @@
       <c r="Q10" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="R10" s="29" t="s">
-        <v>398</v>
+      <c r="R10" s="164" t="s">
+        <v>406</v>
       </c>
       <c r="S10" s="61"/>
       <c r="T10" s="61"/>
@@ -3562,8 +3600,8 @@
       <c r="Q11" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="R11" s="44" t="s">
-        <v>398</v>
+      <c r="R11" s="164" t="s">
+        <v>406</v>
       </c>
       <c r="S11" s="57"/>
       <c r="T11" s="57"/>
@@ -3641,8 +3679,8 @@
       <c r="Q12" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="R12" s="29" t="s">
-        <v>398</v>
+      <c r="R12" s="164" t="s">
+        <v>406</v>
       </c>
       <c r="S12" s="61"/>
       <c r="T12" s="61"/>
@@ -3718,8 +3756,8 @@
       <c r="Q13" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="R13" s="44" t="s">
-        <v>398</v>
+      <c r="R13" s="164" t="s">
+        <v>406</v>
       </c>
       <c r="S13" s="57"/>
       <c r="T13" s="57"/>
@@ -3793,8 +3831,8 @@
       <c r="Q14" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="R14" s="29" t="s">
-        <v>398</v>
+      <c r="R14" s="164" t="s">
+        <v>406</v>
       </c>
       <c r="S14" s="61"/>
       <c r="T14" s="61"/>
@@ -3870,8 +3908,8 @@
       <c r="Q15" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="R15" s="44" t="s">
-        <v>398</v>
+      <c r="R15" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="16" spans="1:40" ht="40.5" customHeight="1">
@@ -3925,8 +3963,8 @@
       <c r="Q16" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="R16" s="29" t="s">
-        <v>398</v>
+      <c r="R16" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="48" customHeight="1">
@@ -3980,8 +4018,8 @@
       <c r="Q17" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="R17" s="44" t="s">
-        <v>398</v>
+      <c r="R17" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="42" customHeight="1">
@@ -4035,8 +4073,8 @@
       <c r="Q18" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="R18" s="29" t="s">
-        <v>398</v>
+      <c r="R18" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="29.25" customHeight="1">
@@ -4090,8 +4128,8 @@
       <c r="Q19" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="R19" s="44" t="s">
-        <v>398</v>
+      <c r="R19" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="52.5" customHeight="1">
@@ -4133,7 +4171,7 @@
       NETWORKDAYS(J20,L20,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="N20" s="53"/>
       <c r="O20" s="53"/>
@@ -4141,8 +4179,8 @@
       <c r="Q20" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="R20" s="29" t="s">
-        <v>398</v>
+      <c r="R20" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="67.5" customHeight="1">
@@ -4186,8 +4224,8 @@
       <c r="Q21" s="72" t="s">
         <v>85</v>
       </c>
-      <c r="R21" s="73" t="s">
-        <v>397</v>
+      <c r="R21" s="163" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="129.75" customHeight="1">
@@ -4243,8 +4281,8 @@
       <c r="Q22" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="R22" s="29" t="s">
-        <v>398</v>
+      <c r="R22" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="69" customHeight="1">
@@ -4300,8 +4338,8 @@
       <c r="Q23" s="72" t="s">
         <v>92</v>
       </c>
-      <c r="R23" s="44" t="s">
-        <v>398</v>
+      <c r="R23" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="78.75" customHeight="1">
@@ -4355,11 +4393,11 @@
       <c r="Q24" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="R24" s="29" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="63" hidden="1" customHeight="1">
+      <c r="R24" s="164" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="63" customHeight="1">
       <c r="A25" s="30" t="s">
         <v>18</v>
       </c>
@@ -4414,8 +4452,8 @@
       <c r="Q25" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="R25" s="44" t="b">
-        <v>1</v>
+      <c r="R25" s="44" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="67.5" customHeight="1">
@@ -4469,8 +4507,8 @@
       <c r="Q26" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="R26" s="29" t="s">
-        <v>398</v>
+      <c r="R26" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="55.5" customHeight="1">
@@ -4516,8 +4554,8 @@
       <c r="Q27" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="R27" s="44" t="s">
-        <v>397</v>
+      <c r="R27" s="163" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="138" customHeight="1">
@@ -4571,8 +4609,8 @@
       <c r="Q28" s="78" t="s">
         <v>110</v>
       </c>
-      <c r="R28" s="29" t="s">
-        <v>398</v>
+      <c r="R28" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="67.5" customHeight="1">
@@ -4626,8 +4664,8 @@
       </c>
       <c r="P29" s="56"/>
       <c r="Q29" s="43"/>
-      <c r="R29" s="44" t="s">
-        <v>398</v>
+      <c r="R29" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="85.5">
@@ -4679,8 +4717,8 @@
       </c>
       <c r="P30" s="53"/>
       <c r="Q30" s="78"/>
-      <c r="R30" s="29" t="s">
-        <v>398</v>
+      <c r="R30" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="71.25">
@@ -4732,8 +4770,8 @@
       </c>
       <c r="P31" s="56"/>
       <c r="Q31" s="79"/>
-      <c r="R31" s="44" t="s">
-        <v>398</v>
+      <c r="R31" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="42.75">
@@ -4783,8 +4821,8 @@
       <c r="O32" s="24"/>
       <c r="P32" s="53"/>
       <c r="Q32" s="78"/>
-      <c r="R32" s="29" t="s">
-        <v>398</v>
+      <c r="R32" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="76.5" customHeight="1">
@@ -4838,8 +4876,8 @@
       <c r="Q33" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="R33" s="44" t="s">
-        <v>398</v>
+      <c r="R33" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="38.25">
@@ -4895,8 +4933,8 @@
       <c r="Q34" s="78" t="s">
         <v>125</v>
       </c>
-      <c r="R34" s="29" t="s">
-        <v>398</v>
+      <c r="R34" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="42.75">
@@ -4952,8 +4990,8 @@
       <c r="Q35" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="R35" s="44" t="s">
-        <v>398</v>
+      <c r="R35" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="93" customHeight="1">
@@ -5009,8 +5047,8 @@
       <c r="Q36" s="78" t="s">
         <v>131</v>
       </c>
-      <c r="R36" s="29" t="s">
-        <v>398</v>
+      <c r="R36" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="76.5" customHeight="1">
@@ -5066,8 +5104,8 @@
       <c r="Q37" s="79" t="s">
         <v>135</v>
       </c>
-      <c r="R37" s="44" t="s">
-        <v>398</v>
+      <c r="R37" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="235.5" customHeight="1">
@@ -5111,7 +5149,7 @@
       NETWORKDAYS(J38,L38,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="N38" s="24"/>
       <c r="O38" s="24"/>
@@ -5119,8 +5157,8 @@
       <c r="Q38" s="78" t="s">
         <v>139</v>
       </c>
-      <c r="R38" s="80" t="s">
-        <v>397</v>
+      <c r="R38" s="163" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="162" customHeight="1">
@@ -5176,11 +5214,11 @@
       <c r="Q39" s="79" t="s">
         <v>142</v>
       </c>
-      <c r="R39" s="44" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="93" hidden="1" customHeight="1">
+      <c r="R39" s="164" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="93" customHeight="1">
       <c r="A40" s="16" t="s">
         <v>18</v>
       </c>
@@ -5235,8 +5273,8 @@
       <c r="Q40" s="78" t="s">
         <v>146</v>
       </c>
-      <c r="R40" s="29" t="b">
-        <v>1</v>
+      <c r="R40" s="29" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="93" customHeight="1">
@@ -5292,11 +5330,11 @@
       <c r="Q41" s="79" t="s">
         <v>151</v>
       </c>
-      <c r="R41" s="44" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="67.5" hidden="1" customHeight="1">
+      <c r="R41" s="164" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="67.5" customHeight="1">
       <c r="A42" s="16" t="s">
         <v>18</v>
       </c>
@@ -5351,11 +5389,11 @@
       <c r="Q42" s="50" t="s">
         <v>154</v>
       </c>
-      <c r="R42" s="29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="93" hidden="1" customHeight="1">
+      <c r="R42" s="29" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="93" customHeight="1">
       <c r="A43" s="30" t="s">
         <v>18</v>
       </c>
@@ -5410,11 +5448,11 @@
       <c r="Q43" s="79" t="s">
         <v>158</v>
       </c>
-      <c r="R43" s="44" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" ht="93" hidden="1" customHeight="1">
+      <c r="R43" s="44" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="93" customHeight="1">
       <c r="A44" s="16" t="s">
         <v>18</v>
       </c>
@@ -5469,11 +5507,11 @@
       <c r="Q44" s="78" t="s">
         <v>162</v>
       </c>
-      <c r="R44" s="29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" ht="93" hidden="1" customHeight="1">
+      <c r="R44" s="29" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="93" customHeight="1">
       <c r="A45" s="30" t="s">
         <v>18</v>
       </c>
@@ -5528,11 +5566,11 @@
       <c r="Q45" s="79" t="s">
         <v>166</v>
       </c>
-      <c r="R45" s="44" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" ht="162" hidden="1" customHeight="1">
+      <c r="R45" s="44" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="162" customHeight="1">
       <c r="A46" s="16" t="s">
         <v>18</v>
       </c>
@@ -5587,11 +5625,11 @@
       <c r="Q46" s="78" t="s">
         <v>170</v>
       </c>
-      <c r="R46" s="29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" ht="162" hidden="1" customHeight="1">
+      <c r="R46" s="29" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="162" customHeight="1">
       <c r="A47" s="30" t="s">
         <v>18</v>
       </c>
@@ -5646,11 +5684,11 @@
       <c r="Q47" s="79" t="s">
         <v>173</v>
       </c>
-      <c r="R47" s="44" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="162" hidden="1" customHeight="1">
+      <c r="R47" s="44" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="162" customHeight="1">
       <c r="A48" s="16" t="s">
         <v>18</v>
       </c>
@@ -5705,11 +5743,11 @@
       <c r="Q48" s="78" t="s">
         <v>176</v>
       </c>
-      <c r="R48" s="29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" ht="162" hidden="1" customHeight="1">
+      <c r="R48" s="29" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="162" customHeight="1">
       <c r="A49" s="30" t="s">
         <v>18</v>
       </c>
@@ -5764,11 +5802,11 @@
       <c r="Q49" s="79" t="s">
         <v>179</v>
       </c>
-      <c r="R49" s="44" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" ht="162" hidden="1" customHeight="1">
+      <c r="R49" s="44" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="162" customHeight="1">
       <c r="A50" s="16" t="s">
         <v>18</v>
       </c>
@@ -5823,11 +5861,11 @@
       <c r="Q50" s="78" t="s">
         <v>182</v>
       </c>
-      <c r="R50" s="29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" ht="162" hidden="1" customHeight="1">
+      <c r="R50" s="29" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="162" customHeight="1">
       <c r="A51" s="30" t="s">
         <v>18</v>
       </c>
@@ -5882,8 +5920,8 @@
       <c r="Q51" s="79" t="s">
         <v>185</v>
       </c>
-      <c r="R51" s="44" t="b">
-        <v>1</v>
+      <c r="R51" s="44" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="162" customHeight="1">
@@ -5939,8 +5977,8 @@
       <c r="Q52" s="78" t="s">
         <v>188</v>
       </c>
-      <c r="R52" s="29" t="s">
-        <v>398</v>
+      <c r="R52" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="53" spans="1:18" ht="101.25" customHeight="1">
@@ -5996,8 +6034,8 @@
       <c r="Q53" s="79" t="s">
         <v>192</v>
       </c>
-      <c r="R53" s="44" t="s">
-        <v>398</v>
+      <c r="R53" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="54" spans="1:18" ht="110.25" customHeight="1">
@@ -6053,8 +6091,8 @@
       <c r="Q54" s="78" t="s">
         <v>196</v>
       </c>
-      <c r="R54" s="29" t="s">
-        <v>398</v>
+      <c r="R54" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="162" customHeight="1">
@@ -6072,7 +6110,7 @@
       </c>
       <c r="E55" s="33"/>
       <c r="F55" s="72" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="G55" s="35">
         <v>100</v>
@@ -6106,12 +6144,14 @@
       <c r="O55" s="39">
         <v>46020</v>
       </c>
-      <c r="P55" s="39"/>
+      <c r="P55" s="39">
+        <v>46092</v>
+      </c>
       <c r="Q55" s="79" t="s">
-        <v>200</v>
-      </c>
-      <c r="R55" s="44" t="s">
-        <v>398</v>
+        <v>199</v>
+      </c>
+      <c r="R55" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="56" spans="1:18" ht="162" customHeight="1">
@@ -6119,17 +6159,17 @@
         <v>18</v>
       </c>
       <c r="B56" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="C56" s="18" t="s">
         <v>201</v>
-      </c>
-      <c r="C56" s="18" t="s">
-        <v>202</v>
       </c>
       <c r="D56" s="19" t="s">
         <v>191</v>
       </c>
       <c r="E56" s="19"/>
       <c r="F56" s="54" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="G56" s="21">
         <v>100</v>
@@ -6163,26 +6203,28 @@
       <c r="O56" s="24">
         <v>46035</v>
       </c>
-      <c r="P56" s="24"/>
+      <c r="P56" s="24">
+        <v>46092</v>
+      </c>
       <c r="Q56" s="78" t="s">
-        <v>203</v>
-      </c>
-      <c r="R56" s="80" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" ht="110.25" hidden="1" customHeight="1">
+        <v>202</v>
+      </c>
+      <c r="R56" s="164" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="110.25" customHeight="1">
       <c r="A57" s="30" t="s">
         <v>18</v>
       </c>
       <c r="B57" s="31" t="s">
+        <v>203</v>
+      </c>
+      <c r="C57" s="32" t="s">
         <v>204</v>
       </c>
-      <c r="C57" s="32" t="s">
+      <c r="D57" s="33" t="s">
         <v>205</v>
-      </c>
-      <c r="D57" s="33" t="s">
-        <v>206</v>
       </c>
       <c r="E57" s="33"/>
       <c r="F57" s="72" t="s">
@@ -6224,10 +6266,10 @@
         <v>46029</v>
       </c>
       <c r="Q57" s="79" t="s">
-        <v>207</v>
-      </c>
-      <c r="R57" s="44" t="b">
-        <v>1</v>
+        <v>206</v>
+      </c>
+      <c r="R57" s="44" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="162" customHeight="1">
@@ -6235,17 +6277,17 @@
         <v>18</v>
       </c>
       <c r="B58" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="C58" s="18" t="s">
         <v>208</v>
-      </c>
-      <c r="C58" s="18" t="s">
-        <v>209</v>
       </c>
       <c r="D58" s="19" t="s">
         <v>191</v>
       </c>
       <c r="E58" s="19"/>
       <c r="F58" s="54" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="G58" s="21">
         <v>100</v>
@@ -6279,26 +6321,28 @@
       <c r="O58" s="24">
         <v>46038</v>
       </c>
-      <c r="P58" s="24"/>
+      <c r="P58" s="24">
+        <v>46092</v>
+      </c>
       <c r="Q58" s="78" t="s">
-        <v>210</v>
-      </c>
-      <c r="R58" s="80" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" ht="110.25" hidden="1" customHeight="1">
+        <v>209</v>
+      </c>
+      <c r="R58" s="164" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="110.25" customHeight="1">
       <c r="A59" s="30" t="s">
         <v>18</v>
       </c>
       <c r="B59" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="C59" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="C59" s="32" t="s">
+      <c r="D59" s="33" t="s">
         <v>212</v>
-      </c>
-      <c r="D59" s="33" t="s">
-        <v>213</v>
       </c>
       <c r="E59" s="33"/>
       <c r="F59" s="72" t="s">
@@ -6340,10 +6384,10 @@
         <v>46036</v>
       </c>
       <c r="Q59" s="79" t="s">
-        <v>214</v>
-      </c>
-      <c r="R59" s="44" t="b">
-        <v>1</v>
+        <v>213</v>
+      </c>
+      <c r="R59" s="44" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="60" spans="1:18" ht="162" customHeight="1">
@@ -6351,17 +6395,17 @@
         <v>18</v>
       </c>
       <c r="B60" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="C60" s="18" t="s">
         <v>215</v>
-      </c>
-      <c r="C60" s="18" t="s">
-        <v>216</v>
       </c>
       <c r="D60" s="19" t="s">
         <v>191</v>
       </c>
       <c r="E60" s="19"/>
       <c r="F60" s="54" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="G60" s="21">
         <v>100</v>
@@ -6395,23 +6439,25 @@
       <c r="O60" s="24">
         <v>46050</v>
       </c>
-      <c r="P60" s="24"/>
+      <c r="P60" s="24">
+        <v>46092</v>
+      </c>
       <c r="Q60" s="78" t="s">
-        <v>217</v>
-      </c>
-      <c r="R60" s="80" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" ht="162" hidden="1" customHeight="1">
+        <v>216</v>
+      </c>
+      <c r="R60" s="164" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="162" customHeight="1">
       <c r="A61" s="30" t="s">
         <v>18</v>
       </c>
       <c r="B61" s="31" t="s">
+        <v>217</v>
+      </c>
+      <c r="C61" s="32" t="s">
         <v>218</v>
-      </c>
-      <c r="C61" s="32" t="s">
-        <v>219</v>
       </c>
       <c r="D61" s="33" t="s">
         <v>191</v>
@@ -6456,24 +6502,24 @@
         <v>46042</v>
       </c>
       <c r="Q61" s="79" t="s">
-        <v>220</v>
-      </c>
-      <c r="R61" s="73" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="110.25" hidden="1" customHeight="1">
+        <v>219</v>
+      </c>
+      <c r="R61" s="73" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="110.25" customHeight="1">
       <c r="A62" s="16" t="s">
         <v>18</v>
       </c>
       <c r="B62" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="D62" s="19" t="s">
         <v>221</v>
-      </c>
-      <c r="C62" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="D62" s="19" t="s">
-        <v>222</v>
       </c>
       <c r="E62" s="19"/>
       <c r="F62" s="54" t="s">
@@ -6515,10 +6561,10 @@
         <v>46042</v>
       </c>
       <c r="Q62" s="78" t="s">
-        <v>223</v>
-      </c>
-      <c r="R62" s="29" t="b">
-        <v>1</v>
+        <v>222</v>
+      </c>
+      <c r="R62" s="29" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="63" spans="1:18" ht="162" customHeight="1">
@@ -6526,17 +6572,17 @@
         <v>18</v>
       </c>
       <c r="B63" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="C63" s="32" t="s">
         <v>224</v>
-      </c>
-      <c r="C63" s="32" t="s">
-        <v>225</v>
       </c>
       <c r="D63" s="33" t="s">
         <v>191</v>
       </c>
       <c r="E63" s="33"/>
       <c r="F63" s="72" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="G63" s="35">
         <v>100</v>
@@ -6570,26 +6616,28 @@
       <c r="O63" s="39">
         <v>46050</v>
       </c>
-      <c r="P63" s="39"/>
+      <c r="P63" s="39">
+        <v>46092</v>
+      </c>
       <c r="Q63" s="79" t="s">
-        <v>226</v>
-      </c>
-      <c r="R63" s="73" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" ht="132.75" hidden="1" customHeight="1">
+        <v>225</v>
+      </c>
+      <c r="R63" s="164" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="132.75" customHeight="1">
       <c r="A64" s="16" t="s">
         <v>18</v>
       </c>
       <c r="B64" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="C64" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="C64" s="18" t="s">
+      <c r="D64" s="19" t="s">
         <v>228</v>
-      </c>
-      <c r="D64" s="19" t="s">
-        <v>229</v>
       </c>
       <c r="E64" s="19"/>
       <c r="F64" s="54" t="s">
@@ -6631,24 +6679,24 @@
         <v>46045</v>
       </c>
       <c r="Q64" s="78" t="s">
-        <v>230</v>
-      </c>
-      <c r="R64" s="29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18" ht="132.75" hidden="1" customHeight="1">
+        <v>229</v>
+      </c>
+      <c r="R64" s="29" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="132.75" customHeight="1">
       <c r="A65" s="30" t="s">
         <v>18</v>
       </c>
       <c r="B65" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="C65" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="C65" s="32" t="s">
+      <c r="D65" s="33" t="s">
         <v>232</v>
-      </c>
-      <c r="D65" s="33" t="s">
-        <v>233</v>
       </c>
       <c r="E65" s="33"/>
       <c r="F65" s="72" t="s">
@@ -6690,10 +6738,10 @@
         <v>46044</v>
       </c>
       <c r="Q65" s="79" t="s">
-        <v>234</v>
-      </c>
-      <c r="R65" s="44" t="b">
-        <v>1</v>
+        <v>233</v>
+      </c>
+      <c r="R65" s="44" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="66" spans="1:18" ht="162" customHeight="1">
@@ -6701,17 +6749,17 @@
         <v>18</v>
       </c>
       <c r="B66" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="C66" s="18" t="s">
         <v>235</v>
-      </c>
-      <c r="C66" s="18" t="s">
-        <v>236</v>
       </c>
       <c r="D66" s="19" t="s">
         <v>191</v>
       </c>
       <c r="E66" s="19"/>
       <c r="F66" s="54" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="G66" s="21">
         <v>100</v>
@@ -6745,12 +6793,14 @@
       <c r="O66" s="24">
         <v>46050</v>
       </c>
-      <c r="P66" s="24"/>
+      <c r="P66" s="24">
+        <v>46092</v>
+      </c>
       <c r="Q66" s="78" t="s">
-        <v>237</v>
-      </c>
-      <c r="R66" s="80" t="s">
-        <v>398</v>
+        <v>236</v>
+      </c>
+      <c r="R66" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="67" spans="1:18" ht="162" customHeight="1">
@@ -6758,17 +6808,17 @@
         <v>18</v>
       </c>
       <c r="B67" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="C67" s="32" t="s">
         <v>238</v>
-      </c>
-      <c r="C67" s="32" t="s">
-        <v>239</v>
       </c>
       <c r="D67" s="33" t="s">
         <v>191</v>
       </c>
       <c r="E67" s="33"/>
       <c r="F67" s="72" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="G67" s="35">
         <v>100</v>
@@ -6802,12 +6852,14 @@
       <c r="O67" s="39">
         <v>46051</v>
       </c>
-      <c r="P67" s="39"/>
+      <c r="P67" s="39">
+        <v>46092</v>
+      </c>
       <c r="Q67" s="79" t="s">
-        <v>240</v>
-      </c>
-      <c r="R67" s="73" t="s">
-        <v>398</v>
+        <v>239</v>
+      </c>
+      <c r="R67" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="68" spans="1:18" ht="162" customHeight="1">
@@ -6815,17 +6867,17 @@
         <v>18</v>
       </c>
       <c r="B68" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="C68" s="18" t="s">
         <v>241</v>
-      </c>
-      <c r="C68" s="18" t="s">
-        <v>242</v>
       </c>
       <c r="D68" s="19" t="s">
         <v>191</v>
       </c>
       <c r="E68" s="19"/>
       <c r="F68" s="54" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="G68" s="21">
         <v>100</v>
@@ -6859,26 +6911,28 @@
       <c r="O68" s="24">
         <v>46051</v>
       </c>
-      <c r="P68" s="24"/>
+      <c r="P68" s="24">
+        <v>46092</v>
+      </c>
       <c r="Q68" s="78" t="s">
-        <v>240</v>
-      </c>
-      <c r="R68" s="80" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18" ht="132.75" hidden="1" customHeight="1">
+        <v>239</v>
+      </c>
+      <c r="R68" s="164" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="132.75" customHeight="1">
       <c r="A69" s="30" t="s">
         <v>18</v>
       </c>
       <c r="B69" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="C69" s="32" t="s">
         <v>243</v>
       </c>
-      <c r="C69" s="32" t="s">
+      <c r="D69" s="33" t="s">
         <v>244</v>
-      </c>
-      <c r="D69" s="33" t="s">
-        <v>245</v>
       </c>
       <c r="E69" s="33"/>
       <c r="F69" s="72" t="s">
@@ -6919,10 +6973,10 @@
         <v>46048</v>
       </c>
       <c r="Q69" s="79" t="s">
-        <v>246</v>
-      </c>
-      <c r="R69" s="44" t="b">
-        <v>1</v>
+        <v>245</v>
+      </c>
+      <c r="R69" s="44" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="70" spans="1:18" ht="162" customHeight="1">
@@ -6930,17 +6984,17 @@
         <v>18</v>
       </c>
       <c r="B70" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="C70" s="18" t="s">
         <v>247</v>
-      </c>
-      <c r="C70" s="18" t="s">
-        <v>248</v>
       </c>
       <c r="D70" s="19" t="s">
         <v>191</v>
       </c>
       <c r="E70" s="19"/>
       <c r="F70" s="54" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="G70" s="21">
         <v>100</v>
@@ -6974,26 +7028,28 @@
       <c r="O70" s="24">
         <v>46057</v>
       </c>
-      <c r="P70" s="24"/>
+      <c r="P70" s="24">
+        <v>46092</v>
+      </c>
       <c r="Q70" s="78" t="s">
-        <v>249</v>
-      </c>
-      <c r="R70" s="80" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18" ht="162" hidden="1" customHeight="1">
+        <v>248</v>
+      </c>
+      <c r="R70" s="164" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="162" customHeight="1">
       <c r="A71" s="30" t="s">
         <v>18</v>
       </c>
       <c r="B71" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="C71" s="32" t="s">
         <v>250</v>
       </c>
-      <c r="C71" s="32" t="s">
-        <v>251</v>
-      </c>
       <c r="D71" s="33" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E71" s="33"/>
       <c r="F71" s="72" t="s">
@@ -7034,24 +7090,24 @@
         <v>46070</v>
       </c>
       <c r="Q71" s="79" t="s">
-        <v>252</v>
-      </c>
-      <c r="R71" s="73" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18" ht="162" hidden="1" customHeight="1">
+        <v>251</v>
+      </c>
+      <c r="R71" s="73" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="162" customHeight="1">
       <c r="A72" s="16" t="s">
         <v>18</v>
       </c>
       <c r="B72" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="C72" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="C72" s="18" t="s">
-        <v>254</v>
-      </c>
       <c r="D72" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E72" s="19"/>
       <c r="F72" s="54" t="s">
@@ -7093,21 +7149,21 @@
         <v>46058</v>
       </c>
       <c r="Q72" s="78" t="s">
-        <v>255</v>
-      </c>
-      <c r="R72" s="80" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18" ht="162" hidden="1" customHeight="1">
+        <v>254</v>
+      </c>
+      <c r="R72" s="80" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="162" customHeight="1">
       <c r="A73" s="30" t="s">
         <v>18</v>
       </c>
       <c r="B73" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="C73" s="32" t="s">
         <v>256</v>
-      </c>
-      <c r="C73" s="32" t="s">
-        <v>257</v>
       </c>
       <c r="D73" s="33" t="s">
         <v>134</v>
@@ -7152,24 +7208,24 @@
         <v>46062</v>
       </c>
       <c r="Q73" s="79" t="s">
-        <v>258</v>
-      </c>
-      <c r="R73" s="73" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18" ht="144" hidden="1" customHeight="1">
+        <v>257</v>
+      </c>
+      <c r="R73" s="73" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="144" customHeight="1">
       <c r="A74" s="16" t="s">
         <v>18</v>
       </c>
       <c r="B74" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="C74" s="18" t="s">
         <v>259</v>
       </c>
-      <c r="C74" s="18" t="s">
+      <c r="D74" s="19" t="s">
         <v>260</v>
-      </c>
-      <c r="D74" s="19" t="s">
-        <v>261</v>
       </c>
       <c r="E74" s="19"/>
       <c r="F74" s="54" t="s">
@@ -7211,10 +7267,10 @@
         <v>46070</v>
       </c>
       <c r="Q74" s="78" t="s">
-        <v>262</v>
-      </c>
-      <c r="R74" s="80" t="b">
-        <v>1</v>
+        <v>261</v>
+      </c>
+      <c r="R74" s="80" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="75" spans="1:18" ht="162" customHeight="1">
@@ -7222,10 +7278,10 @@
         <v>18</v>
       </c>
       <c r="B75" s="31" t="s">
+        <v>262</v>
+      </c>
+      <c r="C75" s="32" t="s">
         <v>263</v>
-      </c>
-      <c r="C75" s="32" t="s">
-        <v>264</v>
       </c>
       <c r="D75" s="33" t="s">
         <v>134</v>
@@ -7270,24 +7326,24 @@
         <v>46069</v>
       </c>
       <c r="Q75" s="79" t="s">
-        <v>265</v>
-      </c>
-      <c r="R75" s="73" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18" ht="132.75" hidden="1" customHeight="1">
+        <v>264</v>
+      </c>
+      <c r="R75" s="164" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="132.75" customHeight="1">
       <c r="A76" s="16" t="s">
         <v>18</v>
       </c>
       <c r="B76" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="C76" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="C76" s="18" t="s">
+      <c r="D76" s="19" t="s">
         <v>267</v>
-      </c>
-      <c r="D76" s="19" t="s">
-        <v>268</v>
       </c>
       <c r="E76" s="19"/>
       <c r="F76" s="54" t="s">
@@ -7329,24 +7385,24 @@
         <v>46072</v>
       </c>
       <c r="Q76" s="78" t="s">
-        <v>269</v>
-      </c>
-      <c r="R76" s="29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18" ht="176.25" hidden="1" customHeight="1">
+        <v>268</v>
+      </c>
+      <c r="R76" s="29" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="176.25" customHeight="1">
       <c r="A77" s="30" t="s">
         <v>18</v>
       </c>
       <c r="B77" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="C77" s="32" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="32" t="s">
-        <v>271</v>
-      </c>
       <c r="D77" s="33" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E77" s="33"/>
       <c r="F77" s="72" t="s">
@@ -7388,24 +7444,24 @@
         <v>46073</v>
       </c>
       <c r="Q77" s="79" t="s">
-        <v>272</v>
-      </c>
-      <c r="R77" s="73" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18" ht="132.75" hidden="1" customHeight="1">
+        <v>271</v>
+      </c>
+      <c r="R77" s="73" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="132.75" customHeight="1">
       <c r="A78" s="16" t="s">
         <v>18</v>
       </c>
       <c r="B78" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="C78" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="C78" s="18" t="s">
+      <c r="D78" s="19" t="s">
         <v>274</v>
-      </c>
-      <c r="D78" s="19" t="s">
-        <v>275</v>
       </c>
       <c r="E78" s="19"/>
       <c r="F78" s="54" t="s">
@@ -7447,24 +7503,24 @@
         <v>46080</v>
       </c>
       <c r="Q78" s="78" t="s">
-        <v>276</v>
-      </c>
-      <c r="R78" s="29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18" ht="132.75" hidden="1" customHeight="1">
+        <v>275</v>
+      </c>
+      <c r="R78" s="29" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="132.75" customHeight="1">
       <c r="A79" s="30" t="s">
         <v>18</v>
       </c>
       <c r="B79" s="31" t="s">
+        <v>276</v>
+      </c>
+      <c r="C79" s="32" t="s">
         <v>277</v>
       </c>
-      <c r="C79" s="32" t="s">
+      <c r="D79" s="33" t="s">
         <v>278</v>
-      </c>
-      <c r="D79" s="33" t="s">
-        <v>279</v>
       </c>
       <c r="E79" s="33"/>
       <c r="F79" s="72" t="s">
@@ -7506,24 +7562,24 @@
         <v>46077</v>
       </c>
       <c r="Q79" s="79" t="s">
-        <v>280</v>
-      </c>
-      <c r="R79" s="44" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18" ht="153" hidden="1" customHeight="1">
+        <v>279</v>
+      </c>
+      <c r="R79" s="44" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="153" customHeight="1">
       <c r="A80" s="16" t="s">
         <v>18</v>
       </c>
       <c r="B80" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="C80" s="18" t="s">
         <v>281</v>
       </c>
-      <c r="C80" s="18" t="s">
+      <c r="D80" s="19" t="s">
         <v>282</v>
-      </c>
-      <c r="D80" s="19" t="s">
-        <v>283</v>
       </c>
       <c r="E80" s="19"/>
       <c r="F80" s="54" t="s">
@@ -7567,10 +7623,10 @@
         <v>46084</v>
       </c>
       <c r="Q80" s="78" t="s">
-        <v>284</v>
-      </c>
-      <c r="R80" s="29" t="b">
-        <v>1</v>
+        <v>283</v>
+      </c>
+      <c r="R80" s="29" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="132.75" customHeight="1">
@@ -7578,13 +7634,13 @@
         <v>18</v>
       </c>
       <c r="B81" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="C81" s="32" t="s">
         <v>285</v>
       </c>
-      <c r="C81" s="32" t="s">
+      <c r="D81" s="33" t="s">
         <v>286</v>
-      </c>
-      <c r="D81" s="33" t="s">
-        <v>287</v>
       </c>
       <c r="E81" s="33"/>
       <c r="F81" s="72" t="s">
@@ -7626,10 +7682,10 @@
         <v>46090</v>
       </c>
       <c r="Q81" s="79" t="s">
-        <v>288</v>
-      </c>
-      <c r="R81" s="44" t="s">
-        <v>398</v>
+        <v>287</v>
+      </c>
+      <c r="R81" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="82" spans="1:18" ht="153" customHeight="1">
@@ -7637,13 +7693,13 @@
         <v>18</v>
       </c>
       <c r="B82" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="C82" s="18" t="s">
         <v>289</v>
       </c>
-      <c r="C82" s="18" t="s">
+      <c r="D82" s="19" t="s">
         <v>290</v>
-      </c>
-      <c r="D82" s="19" t="s">
-        <v>291</v>
       </c>
       <c r="E82" s="19"/>
       <c r="F82" s="54" t="s">
@@ -7685,32 +7741,189 @@
         <v>46091</v>
       </c>
       <c r="Q82" s="78" t="s">
+        <v>291</v>
+      </c>
+      <c r="R82" s="164" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="162" customHeight="1">
+      <c r="A83" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B83" s="31" t="s">
         <v>292</v>
       </c>
-      <c r="R82" s="29" t="s">
-        <v>398</v>
+      <c r="C83" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="D83" s="33" t="s">
+        <v>191</v>
+      </c>
+      <c r="E83" s="33"/>
+      <c r="F83" s="72" t="s">
+        <v>294</v>
+      </c>
+      <c r="G83" s="35">
+        <v>80</v>
+      </c>
+      <c r="H83" s="36">
+        <f>IF(OR(J83="",K83="",K83&lt;J83),0,NETWORKDAYS(J83,K83,Hoja2!$A$2:$A$53))</f>
+        <v>3</v>
+      </c>
+      <c r="I83" s="38">
+        <v>46091</v>
+      </c>
+      <c r="J83" s="38">
+        <v>46092</v>
+      </c>
+      <c r="K83" s="39">
+        <v>46094</v>
+      </c>
+      <c r="L83" s="39"/>
+      <c r="M83" s="40">
+        <f ca="1">IF(OR(J83="",AND(L83="",TODAY()&lt;J83),AND(L83&lt;&gt;"",L83&lt;J83)),0,
+   IF(L83="",
+      NETWORKDAYS(J83,TODAY(),Hoja2!$A$2:$A$53),
+      NETWORKDAYS(J83,L83,Hoja2!$A$2:$A$53)
+   )
+)</f>
+        <v>5</v>
+      </c>
+      <c r="N83" s="39"/>
+      <c r="O83" s="39"/>
+      <c r="P83" s="39"/>
+      <c r="Q83" s="79"/>
+      <c r="R83" s="164" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="162" customHeight="1">
+      <c r="A84" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B84" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="C84" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="D84" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="E84" s="19"/>
+      <c r="F84" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="G84" s="21">
+        <v>100</v>
+      </c>
+      <c r="H84" s="22">
+        <f>IF(OR(J84="",K84="",K84&lt;J84),0,NETWORKDAYS(J84,K84,Hoja2!$A$2:$A$53))</f>
+        <v>3</v>
+      </c>
+      <c r="I84" s="45">
+        <v>46091</v>
+      </c>
+      <c r="J84" s="45">
+        <v>46091</v>
+      </c>
+      <c r="K84" s="24">
+        <v>46093</v>
+      </c>
+      <c r="L84" s="24">
+        <v>46093</v>
+      </c>
+      <c r="M84" s="25">
+        <f ca="1">IF(OR(J84="",AND(L84="",TODAY()&lt;J84),AND(L84&lt;&gt;"",L84&lt;J84)),0,
+   IF(L84="",
+      NETWORKDAYS(J84,TODAY(),Hoja2!$A$2:$A$53),
+      NETWORKDAYS(J84,L84,Hoja2!$A$2:$A$53)
+   )
+)</f>
+        <v>3</v>
+      </c>
+      <c r="N84" s="24"/>
+      <c r="O84" s="24"/>
+      <c r="P84" s="24"/>
+      <c r="Q84" s="78" t="s">
+        <v>298</v>
+      </c>
+      <c r="R84" s="164" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="153" customHeight="1">
+      <c r="A85" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B85" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="C85" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="D85" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="E85" s="33"/>
+      <c r="F85" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="G85" s="77">
+        <v>100</v>
+      </c>
+      <c r="H85" s="36">
+        <f>IF(OR(J85="",K85="",K85&lt;J85),0,NETWORKDAYS(J85,K85,Hoja2!$A$2:$A$53))</f>
+        <v>1</v>
+      </c>
+      <c r="I85" s="38">
+        <v>46094</v>
+      </c>
+      <c r="J85" s="38">
+        <v>46094</v>
+      </c>
+      <c r="K85" s="39">
+        <v>46094</v>
+      </c>
+      <c r="L85" s="39">
+        <v>46097</v>
+      </c>
+      <c r="M85" s="40">
+        <f ca="1">IF(OR(J85="",AND(L85="",TODAY()&lt;J85),AND(L85&lt;&gt;"",L85&lt;J85)),0,
+   IF(L85="",
+      NETWORKDAYS(J85,TODAY(),Hoja2!$A$2:$A$53),
+      NETWORKDAYS(J85,L85,Hoja2!$A$2:$A$53)
+   )
+)</f>
+        <v>2</v>
+      </c>
+      <c r="N85" s="39"/>
+      <c r="O85" s="39">
+        <v>46094</v>
+      </c>
+      <c r="P85" s="39">
+        <v>46094</v>
+      </c>
+      <c r="Q85" s="79" t="s">
+        <v>300</v>
+      </c>
+      <c r="R85" s="164" t="s">
+        <v>406</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN82">
-    <filterColumn colId="15">
-      <filters blank="1">
-        <filter val="09/03/2026"/>
-        <filter val="10/03/2026"/>
-        <filter val="16/02/2026"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="B1:B82">
+  <autoFilter ref="A1:AN85"/>
+  <conditionalFormatting sqref="B1:B85">
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>COUNTIF(B$1:B$82, B1)&gt;1</formula>
+      <formula>COUNTIF(B$1:B$85, B1)&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I2:L20 I21 K21:L21 I22:L82 N2:P82">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I2:L20 I21 K21:L21 I22:L85 N2:P85">
       <formula1>OR(NOT(ISERROR(DATEVALUE(I2))), AND(ISNUMBER(I2), LEFT(CELL("format", I2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F82">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F85">
       <formula1>"FINALIZADO,EN PROCESO,PAUSADO,EN TEST,PENDIENTE,PRUEBAS CLIENTE,PRUEBAS IMAGINE,CANCELADO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7753,7 +7966,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="83" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="I1" s="84" t="s">
         <v>8</v>
@@ -7768,7 +7981,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="84" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="N1" s="86" t="s">
         <v>14</v>
@@ -7804,19 +8017,19 @@
     </row>
     <row r="2" spans="1:39" ht="29.25" customHeight="1">
       <c r="A2" s="87" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B2" s="88" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="89" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="D2" s="88" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="88" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F2" s="90" t="s">
         <v>22</v>
@@ -7851,19 +8064,19 @@
     </row>
     <row r="3" spans="1:39" ht="29.25" customHeight="1">
       <c r="A3" s="87" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B3" s="88" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="89" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="D3" s="88" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="88" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F3" s="90" t="s">
         <v>22</v>
@@ -7898,19 +8111,19 @@
     </row>
     <row r="4" spans="1:39" ht="39" customHeight="1">
       <c r="A4" s="87" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B4" s="88" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="89" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="D4" s="88" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="88" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="F4" s="90" t="s">
         <v>22</v>
@@ -7949,19 +8162,19 @@
     </row>
     <row r="5" spans="1:39" ht="127.5">
       <c r="A5" s="87" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B5" s="88" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="89" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="D5" s="88" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="104" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="F5" s="90" t="s">
         <v>22</v>
@@ -8000,19 +8213,19 @@
     </row>
     <row r="6" spans="1:39" ht="29.25" customHeight="1">
       <c r="A6" s="87" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B6" s="88" t="s">
         <v>34</v>
       </c>
       <c r="C6" s="89" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="D6" s="88" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="106" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="F6" s="107" t="s">
         <v>22</v>
@@ -8051,19 +8264,19 @@
     </row>
     <row r="7" spans="1:39" ht="29.25" customHeight="1">
       <c r="A7" s="87" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B7" s="88" t="s">
         <v>37</v>
       </c>
       <c r="C7" s="89" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="D7" s="88" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="88" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="F7" s="109" t="s">
         <v>22</v>
@@ -8102,19 +8315,19 @@
     </row>
     <row r="8" spans="1:39" ht="29.25" customHeight="1">
       <c r="A8" s="87" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B8" s="88" t="s">
         <v>40</v>
       </c>
       <c r="C8" s="89" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D8" s="88" t="s">
         <v>42</v>
       </c>
       <c r="E8" s="111" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="F8" s="90" t="s">
         <v>22</v>
@@ -8149,17 +8362,17 @@
     </row>
     <row r="9" spans="1:39" ht="29.25" customHeight="1">
       <c r="A9" s="87" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B9" s="88" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="115" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D9" s="116"/>
       <c r="E9" s="88" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="F9" s="109" t="s">
         <v>22</v>
@@ -8196,17 +8409,17 @@
     </row>
     <row r="10" spans="1:39" ht="93" customHeight="1">
       <c r="A10" s="87" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B10" s="88" t="s">
         <v>47</v>
       </c>
       <c r="C10" s="115" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D10" s="116"/>
       <c r="E10" s="88" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="F10" s="109" t="s">
         <v>22</v>
@@ -8241,19 +8454,19 @@
     </row>
     <row r="11" spans="1:39" ht="409.5">
       <c r="A11" s="87" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B11" s="88" t="s">
         <v>50</v>
       </c>
       <c r="C11" s="89" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D11" s="88" t="s">
         <v>42</v>
       </c>
       <c r="E11" s="118" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="F11" s="109" t="s">
         <v>22</v>
@@ -8290,19 +8503,19 @@
     </row>
     <row r="12" spans="1:39" ht="29.25" customHeight="1">
       <c r="A12" s="87" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B12" s="88" t="s">
         <v>53</v>
       </c>
       <c r="C12" s="119" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D12" s="88" t="s">
         <v>55</v>
       </c>
       <c r="E12" s="88" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="F12" s="109" t="s">
         <v>22</v>
@@ -8339,19 +8552,19 @@
     </row>
     <row r="13" spans="1:39" ht="29.25" customHeight="1">
       <c r="A13" s="87" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B13" s="88" t="s">
         <v>57</v>
       </c>
       <c r="C13" s="115" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="D13" s="88" t="s">
         <v>59</v>
       </c>
       <c r="E13" s="88" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="F13" s="109" t="s">
         <v>22</v>
@@ -8386,7 +8599,7 @@
     </row>
     <row r="14" spans="1:39" ht="29.25" customHeight="1">
       <c r="A14" s="87" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B14" s="88" t="s">
         <v>61</v>
@@ -8396,7 +8609,7 @@
       </c>
       <c r="D14" s="120"/>
       <c r="E14" s="106" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F14" s="114" t="s">
         <v>22</v>
@@ -8459,7 +8672,7 @@
         <v>45292</v>
       </c>
       <c r="B1" s="122" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17.25" customHeight="1">
@@ -8467,7 +8680,7 @@
         <v>45299</v>
       </c>
       <c r="B2" s="122" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.25" customHeight="1">
@@ -8475,7 +8688,7 @@
         <v>45376</v>
       </c>
       <c r="B3" s="122" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17.25" customHeight="1">
@@ -8483,7 +8696,7 @@
         <v>45379</v>
       </c>
       <c r="B4" s="122" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17.25" customHeight="1">
@@ -8491,7 +8704,7 @@
         <v>45380</v>
       </c>
       <c r="B5" s="122" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17.25" customHeight="1">
@@ -8499,7 +8712,7 @@
         <v>45413</v>
       </c>
       <c r="B6" s="122" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.25" customHeight="1">
@@ -8507,7 +8720,7 @@
         <v>45425</v>
       </c>
       <c r="B7" s="122" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17.25" customHeight="1">
@@ -8515,7 +8728,7 @@
         <v>45446</v>
       </c>
       <c r="B8" s="122" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17.25" customHeight="1">
@@ -8523,7 +8736,7 @@
         <v>45453</v>
       </c>
       <c r="B9" s="122" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17.25" customHeight="1">
@@ -8531,7 +8744,7 @@
         <v>45474</v>
       </c>
       <c r="B10" s="122" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17.25" customHeight="1">
@@ -8539,7 +8752,7 @@
         <v>45493</v>
       </c>
       <c r="B11" s="122" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17.25" customHeight="1">
@@ -8547,7 +8760,7 @@
         <v>45511</v>
       </c>
       <c r="B12" s="122" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17.25" customHeight="1">
@@ -8555,7 +8768,7 @@
         <v>45523</v>
       </c>
       <c r="B13" s="122" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17.25" customHeight="1">
@@ -8563,7 +8776,7 @@
         <v>45579</v>
       </c>
       <c r="B14" s="122" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17.25" customHeight="1">
@@ -8571,7 +8784,7 @@
         <v>45600</v>
       </c>
       <c r="B15" s="122" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17.25" customHeight="1">
@@ -8579,7 +8792,7 @@
         <v>45607</v>
       </c>
       <c r="B16" s="122" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17.25" customHeight="1">
@@ -8587,7 +8800,7 @@
         <v>45634</v>
       </c>
       <c r="B17" s="122" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17.25" customHeight="1">
@@ -8595,7 +8808,7 @@
         <v>45651</v>
       </c>
       <c r="B18" s="122" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25" customHeight="1">
@@ -8603,7 +8816,7 @@
         <v>45658</v>
       </c>
       <c r="B19" s="123" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25" customHeight="1">
@@ -8611,7 +8824,7 @@
         <v>45663</v>
       </c>
       <c r="B20" s="123" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17.25" customHeight="1">
@@ -8619,7 +8832,7 @@
         <v>45740</v>
       </c>
       <c r="B21" s="123" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17.25" customHeight="1">
@@ -8627,7 +8840,7 @@
         <v>45764</v>
       </c>
       <c r="B22" s="123" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17.25" customHeight="1">
@@ -8635,7 +8848,7 @@
         <v>45765</v>
       </c>
       <c r="B23" s="123" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17.25" customHeight="1">
@@ -8643,7 +8856,7 @@
         <v>45778</v>
       </c>
       <c r="B24" s="123" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17.25" customHeight="1">
@@ -8651,7 +8864,7 @@
         <v>45810</v>
       </c>
       <c r="B25" s="123" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17.25" customHeight="1">
@@ -8659,7 +8872,7 @@
         <v>45831</v>
       </c>
       <c r="B26" s="123" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17.25" customHeight="1">
@@ -8667,7 +8880,7 @@
         <v>45838</v>
       </c>
       <c r="B27" s="123" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17.25" customHeight="1">
@@ -8675,7 +8888,7 @@
         <v>45858</v>
       </c>
       <c r="B28" s="123" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17.25" customHeight="1">
@@ -8683,7 +8896,7 @@
         <v>45876</v>
       </c>
       <c r="B29" s="123" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17.25" customHeight="1">
@@ -8691,7 +8904,7 @@
         <v>45887</v>
       </c>
       <c r="B30" s="123" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="17.25" customHeight="1">
@@ -8699,7 +8912,7 @@
         <v>45943</v>
       </c>
       <c r="B31" s="123" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="17.25" customHeight="1">
@@ -8707,7 +8920,7 @@
         <v>45964</v>
       </c>
       <c r="B32" s="123" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="17.25" customHeight="1">
@@ -8715,7 +8928,7 @@
         <v>45978</v>
       </c>
       <c r="B33" s="123" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="17.25" customHeight="1">
@@ -8723,7 +8936,7 @@
         <v>45999</v>
       </c>
       <c r="B34" s="123" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17.25" customHeight="1">
@@ -8731,7 +8944,7 @@
         <v>46016</v>
       </c>
       <c r="B35" s="123" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17.25" customHeight="1">
@@ -8739,7 +8952,7 @@
         <v>46023</v>
       </c>
       <c r="B36" s="123" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="17.25" customHeight="1">
@@ -8747,7 +8960,7 @@
         <v>46034</v>
       </c>
       <c r="B37" s="123" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17.25" customHeight="1">
@@ -8755,7 +8968,7 @@
         <v>46104</v>
       </c>
       <c r="B38" s="123" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17.25" customHeight="1">
@@ -8763,7 +8976,7 @@
         <v>46114</v>
       </c>
       <c r="B39" s="123" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="17.25" customHeight="1">
@@ -8771,7 +8984,7 @@
         <v>46115</v>
       </c>
       <c r="B40" s="123" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17.25" customHeight="1">
@@ -8779,7 +8992,7 @@
         <v>46143</v>
       </c>
       <c r="B41" s="123" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="17.25" customHeight="1">
@@ -8787,7 +9000,7 @@
         <v>46160</v>
       </c>
       <c r="B42" s="123" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="17.25" customHeight="1">
@@ -8795,7 +9008,7 @@
         <v>46181</v>
       </c>
       <c r="B43" s="123" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="17.25" customHeight="1">
@@ -8803,7 +9016,7 @@
         <v>46188</v>
       </c>
       <c r="B44" s="123" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="17.25" customHeight="1">
@@ -8811,7 +9024,7 @@
         <v>46202</v>
       </c>
       <c r="B45" s="123" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="17.25" customHeight="1">
@@ -8819,7 +9032,7 @@
         <v>46223</v>
       </c>
       <c r="B46" s="123" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="17.25" customHeight="1">
@@ -8827,7 +9040,7 @@
         <v>46241</v>
       </c>
       <c r="B47" s="123" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="17.25" customHeight="1">
@@ -8835,7 +9048,7 @@
         <v>46251</v>
       </c>
       <c r="B48" s="123" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="17.25" customHeight="1">
@@ -8843,7 +9056,7 @@
         <v>46307</v>
       </c>
       <c r="B49" s="123" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="17.25" customHeight="1">
@@ -8851,7 +9064,7 @@
         <v>46328</v>
       </c>
       <c r="B50" s="123" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="17.25" customHeight="1">
@@ -8859,7 +9072,7 @@
         <v>46342</v>
       </c>
       <c r="B51" s="123" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="17.25" customHeight="1">
@@ -8867,7 +9080,7 @@
         <v>46364</v>
       </c>
       <c r="B52" s="123" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="17.25" customHeight="1">
@@ -8875,7 +9088,7 @@
         <v>46381</v>
       </c>
       <c r="B53" s="123" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="17.25" customHeight="1"/>
@@ -9844,7 +10057,7 @@
   <sheetData>
     <row r="1" spans="1:97" ht="15.75">
       <c r="A1" s="124" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
@@ -9902,7 +10115,7 @@
     </row>
     <row r="3" spans="1:97" ht="32.25" customHeight="1">
       <c r="A3" s="126" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B3" s="127">
         <v>45596</v>
@@ -10195,261 +10408,261 @@
     </row>
     <row r="4" spans="1:97" ht="30.75" customHeight="1">
       <c r="A4" s="130" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B4" s="131" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C4" s="132" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="D4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="E4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="G4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="H4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="I4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="J4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="K4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="L4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="M4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="N4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="O4" s="133" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="P4" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Q4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="R4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="S4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="T4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="U4" s="134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="V4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="W4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="X4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Y4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Z4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AA4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AB4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AC4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AD4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AE4" s="159" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="AF4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AG4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AH4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AI4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AJ4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AK4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AL4" s="159" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="AM4" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AN4" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AO4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AP4" s="159" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AQ4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AR4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AS4" s="159" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AT4" s="135" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AU4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AV4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AW4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AX4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AY4" s="159" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AZ4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BA4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BB4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BC4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BD4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BE4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BF4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BG4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BH4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BI4" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BJ4" s="159" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="BK4" s="134" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="BL4" s="134" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="BM4" s="134" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="BN4" s="134" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="BO4" s="134" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="BP4" s="134" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="BQ4" s="134" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="BR4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BS4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BT4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BU4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BV4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BW4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BX4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BY4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BZ4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CA4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CB4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CC4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CD4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CE4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CF4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CG4" s="133"/>
       <c r="CH4" s="133"/>
       <c r="CI4" s="159" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="CJ4" s="133"/>
       <c r="CK4" s="133"/>
@@ -10461,249 +10674,249 @@
       <c r="CQ4" s="133"/>
       <c r="CR4" s="133"/>
       <c r="CS4" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5" spans="1:97" ht="15.75" customHeight="1">
       <c r="A5" s="130" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B5" s="131" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="E5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="G5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="H5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="I5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="J5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="K5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="L5" s="133" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="M5" s="133" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="N5" s="133" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="O5" s="133" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="P5" s="134" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="Q5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="R5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="S5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="T5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="U5" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="V5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="W5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="X5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Y5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Z5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AA5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AB5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AC5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AD5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AE5" s="160"/>
       <c r="AF5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AG5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AH5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AI5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AJ5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AK5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AL5" s="160"/>
       <c r="AM5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AN5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AO5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AP5" s="160"/>
       <c r="AQ5" s="133" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AR5" s="133" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AS5" s="160"/>
       <c r="AT5" s="133" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AU5" s="133" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AV5" s="133" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AW5" s="133" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AX5" s="133" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AY5" s="160"/>
       <c r="AZ5" s="133" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="BA5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BB5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BC5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BD5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BE5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BF5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BG5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BH5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BI5" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BJ5" s="160"/>
       <c r="BK5" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BL5" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BM5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BN5" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BO5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BP5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BQ5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BR5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BS5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BT5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BU5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BV5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BW5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BX5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BY5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BZ5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CA5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CB5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CC5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CD5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CE5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CF5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CG5" s="133"/>
       <c r="CH5" s="133"/>
@@ -10718,249 +10931,249 @@
       <c r="CQ5" s="133"/>
       <c r="CR5" s="133"/>
       <c r="CS5" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" spans="1:97" ht="15.75">
       <c r="A6" s="130" t="s">
+        <v>374</v>
+      </c>
+      <c r="B6" s="131" t="s">
+        <v>364</v>
+      </c>
+      <c r="C6" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="D6" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="E6" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="F6" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="G6" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="H6" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="I6" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="J6" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="K6" s="136" t="s">
+        <v>375</v>
+      </c>
+      <c r="L6" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="M6" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="N6" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="O6" s="133" t="s">
         <v>366</v>
       </c>
-      <c r="B6" s="131" t="s">
-        <v>356</v>
-      </c>
-      <c r="C6" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="D6" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="E6" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="F6" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="G6" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="H6" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="I6" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="J6" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="K6" s="136" t="s">
-        <v>367</v>
-      </c>
-      <c r="L6" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="M6" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="N6" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="O6" s="133" t="s">
-        <v>358</v>
-      </c>
       <c r="P6" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Q6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="R6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="S6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="T6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="U6" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="V6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="W6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="X6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Y6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Z6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AA6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AB6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AC6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AD6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AE6" s="160"/>
       <c r="AF6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AG6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AH6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AI6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AJ6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AK6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AL6" s="160"/>
       <c r="AM6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AN6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AO6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AP6" s="160"/>
       <c r="AQ6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AR6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AS6" s="160"/>
       <c r="AT6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AU6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AV6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AW6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AX6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AY6" s="160"/>
       <c r="AZ6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BA6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BB6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BC6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BD6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BE6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BF6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BG6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BH6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BI6" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BJ6" s="160"/>
       <c r="BK6" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BL6" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BM6" s="133" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="BN6" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BO6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BP6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BQ6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BR6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BS6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BT6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BU6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BV6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BW6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BX6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BY6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BZ6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CA6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CB6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CC6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CD6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CE6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CF6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CG6" s="133"/>
       <c r="CH6" s="133"/>
@@ -10975,198 +11188,198 @@
       <c r="CQ6" s="133"/>
       <c r="CR6" s="133"/>
       <c r="CS6" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="7" spans="1:97" ht="15.75" hidden="1" customHeight="1">
       <c r="A7" s="130" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B7" s="131" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="E7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="G7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="H7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="I7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="J7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="K7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="L7" s="136" t="s">
+        <v>375</v>
+      </c>
+      <c r="M7" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="N7" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="O7" s="133" t="s">
+        <v>366</v>
+      </c>
+      <c r="P7" s="134" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q7" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="R7" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="S7" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="T7" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="U7" s="134" t="s">
+        <v>378</v>
+      </c>
+      <c r="V7" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="W7" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="X7" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y7" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="Z7" s="133" t="s">
         <v>367</v>
       </c>
-      <c r="M7" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="N7" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="O7" s="133" t="s">
-        <v>358</v>
-      </c>
-      <c r="P7" s="134" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q7" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="R7" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="S7" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="T7" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="U7" s="134" t="s">
-        <v>370</v>
-      </c>
-      <c r="V7" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="W7" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="X7" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="Y7" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="Z7" s="133" t="s">
-        <v>359</v>
-      </c>
       <c r="AA7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AB7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AC7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AD7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AE7" s="160"/>
       <c r="AF7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AG7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AH7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AI7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AJ7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AK7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AL7" s="160"/>
       <c r="AM7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AN7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AO7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AP7" s="160"/>
       <c r="AQ7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AR7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AS7" s="160"/>
       <c r="AT7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AU7" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AV7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AW7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AX7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AY7" s="160"/>
       <c r="AZ7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BA7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BB7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BC7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BD7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BE7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BF7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BG7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BH7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BI7" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BJ7" s="160"/>
       <c r="BK7" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BL7" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BM7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BN7" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BO7" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BP7" s="133"/>
       <c r="BQ7" s="133"/>
@@ -11174,16 +11387,16 @@
       <c r="BS7" s="133"/>
       <c r="BT7" s="133"/>
       <c r="BU7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BV7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BW7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BX7" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BY7" s="133"/>
       <c r="BZ7" s="133"/>
@@ -11209,220 +11422,220 @@
     </row>
     <row r="8" spans="1:97" ht="15.75" hidden="1" customHeight="1">
       <c r="A8" s="130" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B8" s="131" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="E8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="G8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="H8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="I8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="J8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="K8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="L8" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="M8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="N8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="O8" s="133" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="P8" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Q8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="R8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="S8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="T8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="U8" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="V8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="W8" s="133" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="X8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Y8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Z8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AA8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AB8" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AC8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AD8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AE8" s="160"/>
       <c r="AF8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AG8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AH8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AI8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AJ8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AK8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AL8" s="160"/>
       <c r="AM8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AN8" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AO8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AP8" s="160"/>
       <c r="AQ8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AR8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AS8" s="160"/>
       <c r="AT8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AU8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AV8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AW8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AX8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AY8" s="160"/>
       <c r="AZ8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BA8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BB8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BC8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BD8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BE8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BF8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BG8" s="133" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="BH8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BI8" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BJ8" s="160"/>
       <c r="BK8" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BL8" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BM8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BN8" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BO8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BP8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BQ8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BR8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BS8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BT8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BU8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BV8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BW8" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BX8" s="133" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="BY8" s="133"/>
       <c r="BZ8" s="133"/>
@@ -11448,244 +11661,244 @@
     </row>
     <row r="9" spans="1:97" ht="15.75">
       <c r="A9" s="130" t="s">
+        <v>383</v>
+      </c>
+      <c r="B9" s="131" t="s">
+        <v>364</v>
+      </c>
+      <c r="C9" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="D9" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="E9" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="F9" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="G9" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="H9" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="I9" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="J9" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="K9" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="L9" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="M9" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="N9" s="133" t="s">
+        <v>364</v>
+      </c>
+      <c r="O9" s="136" t="s">
         <v>375</v>
       </c>
-      <c r="B9" s="131" t="s">
-        <v>356</v>
-      </c>
-      <c r="C9" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="D9" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="E9" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="F9" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="G9" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="H9" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="I9" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="J9" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="K9" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="L9" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="M9" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="N9" s="133" t="s">
-        <v>356</v>
-      </c>
-      <c r="O9" s="136" t="s">
-        <v>367</v>
-      </c>
       <c r="P9" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Q9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="R9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="S9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="T9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="U9" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="V9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="W9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="X9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Y9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Z9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AA9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AB9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AC9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AD9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AE9" s="160"/>
       <c r="AF9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AG9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AH9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AI9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AJ9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AK9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AL9" s="160"/>
       <c r="AM9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AN9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AO9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AP9" s="160"/>
       <c r="AQ9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AR9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AS9" s="160"/>
       <c r="AT9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AU9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AV9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AW9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AX9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AY9" s="160"/>
       <c r="AZ9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BA9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BB9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BC9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BD9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BE9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BF9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BG9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BH9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BI9" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BJ9" s="160"/>
       <c r="BK9" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BL9" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BM9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BN9" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BO9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BP9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BQ9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BR9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BS9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BT9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BU9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BV9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BW9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BX9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BY9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BZ9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CA9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CB9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CC9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CD9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CE9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CF9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CG9" s="133"/>
       <c r="CH9" s="133"/>
@@ -11700,249 +11913,249 @@
       <c r="CQ9" s="133"/>
       <c r="CR9" s="133"/>
       <c r="CS9" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" spans="1:97" ht="15.75">
       <c r="A10" s="130" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B10" s="131" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="E10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="G10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="H10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="I10" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="J10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="K10" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="L10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="M10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="N10" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="O10" s="133" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="P10" s="134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="Q10" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="R10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="S10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="T10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="U10" s="134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="V10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="W10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="X10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Y10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Z10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AA10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AB10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AC10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AD10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AE10" s="160"/>
       <c r="AF10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AG10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AH10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AI10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AJ10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AK10" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AL10" s="160"/>
       <c r="AM10" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AN10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AO10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AP10" s="160"/>
       <c r="AQ10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AR10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AS10" s="160"/>
       <c r="AT10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AU10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AV10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AW10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AX10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AY10" s="160"/>
       <c r="AZ10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BA10" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BB10" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BC10" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BD10" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BE10" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BF10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BG10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BH10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BI10" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BJ10" s="160"/>
       <c r="BK10" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BL10" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BM10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BN10" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BO10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BP10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BQ10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BR10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BS10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BT10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BU10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BV10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BW10" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BX10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BY10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BZ10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CA10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CB10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CC10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CD10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CE10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CF10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CG10" s="133"/>
       <c r="CH10" s="133"/>
@@ -11957,249 +12170,249 @@
       <c r="CQ10" s="133"/>
       <c r="CR10" s="133"/>
       <c r="CS10" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11" spans="1:97" ht="15.75">
       <c r="A11" s="130" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B11" s="131" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="E11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="G11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="H11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="I11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="J11" s="133" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="K11" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="L11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="M11" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="N11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="O11" s="133" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="P11" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Q11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="R11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="S11" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="T11" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="U11" s="134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="V11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="W11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="X11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Y11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Z11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AA11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AB11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AC11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AD11" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AE11" s="160"/>
       <c r="AF11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AG11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AH11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AI11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AJ11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AK11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AL11" s="160"/>
       <c r="AM11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AN11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AO11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AP11" s="160"/>
       <c r="AQ11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AR11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AS11" s="160"/>
       <c r="AT11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AU11" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AV11" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AW11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AX11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AY11" s="160"/>
       <c r="AZ11" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BA11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BB11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BC11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BD11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BE11" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BF11" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BG11" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BH11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BI11" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BJ11" s="160"/>
       <c r="BK11" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BL11" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BM11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BN11" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BO11" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BP11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BQ11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BR11" s="133" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="BS11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BT11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BU11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BV11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BW11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BX11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BY11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BZ11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CA11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CB11" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="CC11" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="CD11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CE11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CF11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CG11" s="133"/>
       <c r="CH11" s="133"/>
@@ -12214,249 +12427,249 @@
       <c r="CQ11" s="133"/>
       <c r="CR11" s="133"/>
       <c r="CS11" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12" spans="1:97" ht="15.75">
       <c r="A12" s="130" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B12" s="131" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="E12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="G12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="H12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="I12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="J12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="K12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="L12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="M12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="N12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="O12" s="133" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="P12" s="134" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="Q12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="R12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="S12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="T12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="U12" s="134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="V12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="W12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="X12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="Y12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="Z12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AA12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AB12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AC12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AD12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AE12" s="160"/>
       <c r="AF12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AG12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AH12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AI12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AJ12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AK12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AL12" s="160"/>
       <c r="AM12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AN12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AO12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AP12" s="160"/>
       <c r="AQ12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AR12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AS12" s="160"/>
       <c r="AT12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AU12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AV12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AW12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AX12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AY12" s="160"/>
       <c r="AZ12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BA12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BB12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BC12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BD12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BE12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BF12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BG12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BH12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BI12" s="134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BJ12" s="160"/>
       <c r="BK12" s="134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BL12" s="134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BM12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BN12" s="134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BO12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BP12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BQ12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BR12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BS12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BT12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BU12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BV12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BW12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BX12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BY12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="BZ12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="CA12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="CB12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CC12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="CD12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="CE12" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CF12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="CG12" s="133"/>
       <c r="CH12" s="133"/>
@@ -12471,249 +12684,249 @@
       <c r="CQ12" s="133"/>
       <c r="CR12" s="133"/>
       <c r="CS12" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" spans="1:97" ht="15.75">
       <c r="A13" s="130" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="B13" s="131" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="E13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="F13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="G13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="H13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="I13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="J13" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="K13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="L13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="M13" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="N13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="O13" s="133" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="P13" s="134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="Q13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="R13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="S13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="T13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="U13" s="134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="V13" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="W13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="X13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="Y13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="Z13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AA13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AB13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AC13" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AD13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AE13" s="161"/>
       <c r="AF13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AG13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AH13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AI13" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AJ13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AK13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AL13" s="161"/>
       <c r="AM13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AN13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AO13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AP13" s="161"/>
       <c r="AQ13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AR13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AS13" s="161"/>
       <c r="AT13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AU13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AV13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AW13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AX13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="AY13" s="161"/>
       <c r="AZ13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BA13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BB13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BC13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BD13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BE13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BF13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BG13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BH13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BI13" s="134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BJ13" s="161"/>
       <c r="BK13" s="134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BL13" s="134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BM13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BN13" s="134" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BO13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BP13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BQ13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BR13" s="133" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="BS13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BT13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BU13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BV13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BW13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BX13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BY13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="BZ13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="CA13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="CB13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="CC13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="CD13" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CE13" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CF13" s="133" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="CG13" s="133"/>
       <c r="CH13" s="133"/>
@@ -12728,7 +12941,7 @@
       <c r="CQ13" s="133"/>
       <c r="CR13" s="133"/>
       <c r="CS13" s="133" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -13747,7 +13960,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="25.5">
       <c r="A1" s="137" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B1" s="137" t="s">
         <v>2</v>
@@ -13771,16 +13984,16 @@
         <v>11</v>
       </c>
       <c r="I1" s="140" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="J1" s="141" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="K1" s="142" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="L1" s="140" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="M1" s="143"/>
       <c r="N1" s="143"/>
@@ -13799,10 +14012,10 @@
     </row>
     <row r="2" spans="1:26" ht="38.25">
       <c r="A2" s="144" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B2" s="145" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C2" s="146"/>
       <c r="D2" s="146" t="s">
@@ -13829,7 +14042,7 @@
       </c>
       <c r="K2" s="149"/>
       <c r="L2" s="150" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="M2" s="143"/>
       <c r="N2" s="143"/>
@@ -13848,16 +14061,16 @@
     </row>
     <row r="3" spans="1:26" ht="51">
       <c r="A3" s="144" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B3" s="162" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C3" s="151" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="D3" s="146" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="E3" s="147">
         <v>45575</v>
@@ -13876,7 +14089,7 @@
       </c>
       <c r="K3" s="147"/>
       <c r="L3" s="150" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="M3" s="152"/>
       <c r="N3" s="143"/>
@@ -13895,14 +14108,14 @@
     </row>
     <row r="4" spans="1:26" ht="51">
       <c r="A4" s="144" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B4" s="160"/>
       <c r="C4" s="153" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="D4" s="146" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="E4" s="147">
         <v>45575</v>
@@ -13921,7 +14134,7 @@
       </c>
       <c r="K4" s="154"/>
       <c r="L4" s="157" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="M4" s="152"/>
       <c r="N4" s="143"/>
@@ -13940,16 +14153,16 @@
     </row>
     <row r="5" spans="1:26" ht="51">
       <c r="A5" s="144" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B5" s="140" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C5" s="146" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="D5" s="146" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="E5" s="147">
         <v>45575</v>
@@ -13968,7 +14181,7 @@
       </c>
       <c r="K5" s="147"/>
       <c r="L5" s="150" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="M5" s="152"/>
       <c r="N5" s="143"/>

--- a/Proteccion.xlsx
+++ b/Proteccion.xlsx
@@ -19,7 +19,7 @@
     <sheet name="pruebas i" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'EN PROCESO (Proteccíon)'!$A$1:$AN$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'EN PROCESO (Proteccíon)'!$A$1:$AN$115</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="519">
   <si>
     <t>Asignado a</t>
   </si>
@@ -1326,8 +1326,8 @@
     <t>EN PROCESO</t>
   </si>
   <si>
-    <t xml:space="preserve">26/05/2026 Identificación de recursos en donde se definen la mayor parte de gabinetes a migrar
-</t>
+    <t>26/05/2026 Identificación de recursos en donde se definen la mayor parte de gabinetes a migrar
+09/06/2026 Se comparte información relacionadaa los documentos que se esperan migrar. Se facilita 3 ejemplos para cada uno de los tipos documentales y la infromación relacionada a los gabinetes</t>
   </si>
   <si>
     <t>REQ-44</t>
@@ -1340,7 +1340,8 @@
   </si>
   <si>
     <t>27/05/2026 Se identifican las bandejas pero no los procesos en la aplicación para realizar el añadido en el código. Se comenta al proceso para poder identificarlos
-03/06/2026 Se recibió información para la gestión de la mitad de las bandejas y poder modificar el código añadiendo el étodo de tracking</t>
+03/06/2026 Se recibió información para la gestión de la mitad de las bandejas y poder modificar el código añadiendo el étodo de tracking
+05/06/2026 Se completa el envío de eventros para todas las bandejas que se indicaron</t>
   </si>
   <si>
     <t>REQ-45</t>
@@ -1350,10 +1351,87 @@
   </si>
   <si>
     <t>Actualización de glosas y configuración para la apertura de tareas</t>
+  </si>
+  <si>
+    <t>PAUSADO</t>
   </si>
   <si>
     <t>02/06/2026 Se analiza el código y la lógica del negocio y se encontró que para la maypria de casos solo es necesario una actualización en bases de datos, pero para otros si se necesitaría cambio en el cóidigo
 03/06/2026 Se indica que es necesario primero una reunión para medir los cambios, debido a que la actualización es para muchos tipos</t>
+  </si>
+  <si>
+    <t>REQ-46</t>
+  </si>
+  <si>
+    <t>Se presentaron problemas de configuración y acceso a la plataforma fileNEt desde IMAGINE y se necesita su corrección. Además, se crea funacionalidades para la verificación del cargue, el estado de documentos y envío de peticiones de reintentos de descargue documental</t>
+  </si>
+  <si>
+    <t>Creación de funcionalidades y corrección en las configuraciones de autenticación para el módulo de validaciones de fileNet</t>
+  </si>
+  <si>
+    <t>10/06/2026 Se entrega servicios re configurados y funcionalidades nuevas</t>
+  </si>
+  <si>
+    <t>REQ-47</t>
+  </si>
+  <si>
+    <t>Existe un problema al realizar cierre de una bandeja en donde esta coratndo la lógica e impidiendo el cierre y avance normal de la gestión, por lo que es necesario la revisión y la corrección tanto del código como de los casos</t>
+  </si>
+  <si>
+    <t>Correccion cierre Accion Legal</t>
+  </si>
+  <si>
+    <t>10/06/2026 Se nos indica los problemas y las situaciones generadas. Se realiza el primer sondeo y análisis pero no se encuentra la raíz del problema
+11/06/2026 Se construye en el código una herramienta para guardar la información de las gestiones y poder identificar mejor la situación
+17/06/2026 Se realiza una reunión en donde se identifica que las opciones problemáticas no es donde en princiío se había indicado, se realizan las correcciones y se está trabajando en los trámites con problemas</t>
+  </si>
+  <si>
+    <t>REQ-48</t>
+  </si>
+  <si>
+    <t>Aunque existe un desarrollo relativamente nuevo para tratar los casos que no envían eventos en esta etapa, solo se hace para casos actuales de este año por lo que cuando un caso viejo se actualiza y es necesario de dicho evento no es enviado automaticamente por lo que es necesario su procesamiento</t>
+  </si>
+  <si>
+    <t>Correccion trámites en normalización</t>
+  </si>
+  <si>
+    <t>17/06/2026 Se construye una solucion para tratar estos casos de una manera más rápida y automatizada</t>
+  </si>
+  <si>
+    <t>REQ-49</t>
+  </si>
+  <si>
+    <t>Existe un problema en el módulo de reconstrucción OBP automático que se creo junto con el consumo de fileNet y no esta cerrando gestiones, por lo que es necesario revisión y corrección</t>
+  </si>
+  <si>
+    <t>Correccion trámites en reconstrucción</t>
+  </si>
+  <si>
+    <t>EN TEST</t>
+  </si>
+  <si>
+    <t>19/06/2026 Se construye una solucion que identifique que trámites son los que se deben de gestionar, debido a que con cédula como filtro la función podía tomar un trámite indebido. Se soluciona para los casos pendientes de cerrar gestion y se esta pendiente la confirmación de si la solución aplica para todos los casos.</t>
+  </si>
+  <si>
+    <t>REQ-50</t>
+  </si>
+  <si>
+    <t>Actualización de servicio para deshabilitar la apertura de tareas en el proceso de fusión</t>
+  </si>
+  <si>
+    <t>Es necesario la modificación de la lógica al fusionar trámites para impedir la apertura de tareas</t>
+  </si>
+  <si>
+    <t>23/06/2026 Se construye una solucion que identifique el momento de la fusión y poder deshabilitar la apertura de tareas</t>
+  </si>
+  <si>
+    <t>REQ-51</t>
+  </si>
+  <si>
+    <t>Es necesario la corrección en el flujo para ciertos trámites  y la deshabilitación de un servicio que esta generando dicho problema de flujo. Dicho servicio no estará disponible hasta que un servicio externo pueda disponer la información que necesitamos para su funcionamiento</t>
+  </si>
+  <si>
+    <t>Deshabilitación de servicio</t>
   </si>
   <si>
     <t>dias estimados</t>
@@ -3181,7 +3259,7 @@
   <sheetPr>
     <tabColor rgb="FF93C47D"/>
   </sheetPr>
-  <dimension ref="A1:AN109"/>
+  <dimension ref="A1:AN115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.21875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3335,7 +3413,7 @@
         <v>23</v>
       </c>
       <c r="R2" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="3" spans="1:40" ht="29.25" customHeight="1">
@@ -3390,7 +3468,7 @@
         <v>26</v>
       </c>
       <c r="R3" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="4" spans="1:40" ht="29.25" customHeight="1">
@@ -3449,7 +3527,7 @@
         <v>30</v>
       </c>
       <c r="R4" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" spans="1:40" ht="29.25" customHeight="1">
@@ -3508,7 +3586,7 @@
         <v>33</v>
       </c>
       <c r="R5" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6" spans="1:40" ht="29.25" customHeight="1">
@@ -3567,7 +3645,7 @@
         <v>36</v>
       </c>
       <c r="R6" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="7" spans="1:40" ht="29.25" customHeight="1">
@@ -3626,7 +3704,7 @@
         <v>39</v>
       </c>
       <c r="R7" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8" spans="1:40" ht="29.25" customHeight="1">
@@ -3681,7 +3759,7 @@
         <v>43</v>
       </c>
       <c r="R8" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="9" spans="1:40" ht="29.25" customHeight="1">
@@ -3736,7 +3814,7 @@
         <v>46</v>
       </c>
       <c r="R9" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
       <c r="S9" s="55"/>
       <c r="T9" s="55"/>
@@ -3811,7 +3889,7 @@
         <v>49</v>
       </c>
       <c r="R10" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
       <c r="S10" s="59"/>
       <c r="T10" s="59"/>
@@ -3890,7 +3968,7 @@
         <v>52</v>
       </c>
       <c r="R11" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
       <c r="S11" s="55"/>
       <c r="T11" s="55"/>
@@ -3969,7 +4047,7 @@
         <v>56</v>
       </c>
       <c r="R12" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
       <c r="S12" s="59"/>
       <c r="T12" s="59"/>
@@ -4046,7 +4124,7 @@
         <v>60</v>
       </c>
       <c r="R13" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
       <c r="S13" s="55"/>
       <c r="T13" s="55"/>
@@ -4121,7 +4199,7 @@
         <v>63</v>
       </c>
       <c r="R14" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
       <c r="S14" s="59"/>
       <c r="T14" s="59"/>
@@ -4198,7 +4276,7 @@
         <v>66</v>
       </c>
       <c r="R15" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="16" spans="1:40" ht="40.5" customHeight="1">
@@ -4253,7 +4331,7 @@
         <v>69</v>
       </c>
       <c r="R16" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="48" customHeight="1">
@@ -4308,7 +4386,7 @@
         <v>72</v>
       </c>
       <c r="R17" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="42" customHeight="1">
@@ -4363,7 +4441,7 @@
         <v>75</v>
       </c>
       <c r="R18" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="29.25" customHeight="1">
@@ -4418,7 +4496,7 @@
         <v>78</v>
       </c>
       <c r="R19" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="52.5" customHeight="1">
@@ -4460,7 +4538,7 @@
       NETWORKDAYS(J20,L20,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="N20" s="51"/>
       <c r="O20" s="51"/>
@@ -4469,7 +4547,7 @@
         <v>81</v>
       </c>
       <c r="R20" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="67.5" customHeight="1">
@@ -4514,7 +4592,7 @@
         <v>85</v>
       </c>
       <c r="R21" s="159" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="129.75" customHeight="1">
@@ -4571,7 +4649,7 @@
         <v>88</v>
       </c>
       <c r="R22" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="69" customHeight="1">
@@ -4628,7 +4706,7 @@
         <v>92</v>
       </c>
       <c r="R23" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="78.75" customHeight="1">
@@ -4683,7 +4761,7 @@
         <v>95</v>
       </c>
       <c r="R24" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="63" customHeight="1">
@@ -4742,7 +4820,7 @@
         <v>99</v>
       </c>
       <c r="R25" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="67.5" customHeight="1">
@@ -4797,7 +4875,7 @@
         <v>103</v>
       </c>
       <c r="R26" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="55.5" customHeight="1">
@@ -4844,7 +4922,7 @@
         <v>107</v>
       </c>
       <c r="R27" s="159" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="138" customHeight="1">
@@ -4899,7 +4977,7 @@
         <v>110</v>
       </c>
       <c r="R28" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="67.5" customHeight="1">
@@ -4954,7 +5032,7 @@
       <c r="P29" s="54"/>
       <c r="Q29" s="42"/>
       <c r="R29" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="85.5">
@@ -5007,7 +5085,7 @@
       <c r="P30" s="51"/>
       <c r="Q30" s="75"/>
       <c r="R30" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="71.25">
@@ -5060,7 +5138,7 @@
       <c r="P31" s="54"/>
       <c r="Q31" s="76"/>
       <c r="R31" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="42.75">
@@ -5111,7 +5189,7 @@
       <c r="P32" s="51"/>
       <c r="Q32" s="75"/>
       <c r="R32" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="76.5" customHeight="1">
@@ -5166,7 +5244,7 @@
         <v>121</v>
       </c>
       <c r="R33" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="38.25">
@@ -5223,7 +5301,7 @@
         <v>125</v>
       </c>
       <c r="R34" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="42.75">
@@ -5280,7 +5358,7 @@
         <v>125</v>
       </c>
       <c r="R35" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="93" customHeight="1">
@@ -5337,7 +5415,7 @@
         <v>131</v>
       </c>
       <c r="R36" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="76.5" customHeight="1">
@@ -5394,7 +5472,7 @@
         <v>135</v>
       </c>
       <c r="R37" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="235.5" customHeight="1">
@@ -5438,7 +5516,7 @@
       NETWORKDAYS(J38,L38,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="N38" s="24"/>
       <c r="O38" s="24"/>
@@ -5447,7 +5525,7 @@
         <v>139</v>
       </c>
       <c r="R38" s="159" t="s">
-        <v>492</v>
+        <v>517</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="162" customHeight="1">
@@ -5504,7 +5582,7 @@
         <v>142</v>
       </c>
       <c r="R39" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="93" customHeight="1">
@@ -5563,7 +5641,7 @@
         <v>146</v>
       </c>
       <c r="R40" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="93" customHeight="1">
@@ -5620,7 +5698,7 @@
         <v>151</v>
       </c>
       <c r="R41" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="67.5" customHeight="1">
@@ -5679,7 +5757,7 @@
         <v>154</v>
       </c>
       <c r="R42" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="93" customHeight="1">
@@ -5738,7 +5816,7 @@
         <v>158</v>
       </c>
       <c r="R43" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="93" customHeight="1">
@@ -5797,7 +5875,7 @@
         <v>162</v>
       </c>
       <c r="R44" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="93" customHeight="1">
@@ -5856,7 +5934,7 @@
         <v>166</v>
       </c>
       <c r="R45" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="46" spans="1:18" ht="162" customHeight="1">
@@ -5915,7 +5993,7 @@
         <v>170</v>
       </c>
       <c r="R46" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="47" spans="1:18" ht="162" customHeight="1">
@@ -5974,7 +6052,7 @@
         <v>173</v>
       </c>
       <c r="R47" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="48" spans="1:18" ht="162" customHeight="1">
@@ -6033,7 +6111,7 @@
         <v>176</v>
       </c>
       <c r="R48" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="162" customHeight="1">
@@ -6092,7 +6170,7 @@
         <v>179</v>
       </c>
       <c r="R49" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="162" customHeight="1">
@@ -6151,7 +6229,7 @@
         <v>182</v>
       </c>
       <c r="R50" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="51" spans="1:18" ht="162" customHeight="1">
@@ -6210,7 +6288,7 @@
         <v>185</v>
       </c>
       <c r="R51" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="52" spans="1:18" ht="162" customHeight="1">
@@ -6267,7 +6345,7 @@
         <v>188</v>
       </c>
       <c r="R52" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="53" spans="1:18" ht="101.25" customHeight="1">
@@ -6324,7 +6402,7 @@
         <v>192</v>
       </c>
       <c r="R53" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="54" spans="1:18" ht="110.25" customHeight="1">
@@ -6381,7 +6459,7 @@
         <v>196</v>
       </c>
       <c r="R54" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="162" customHeight="1">
@@ -6440,7 +6518,7 @@
         <v>199</v>
       </c>
       <c r="R55" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="56" spans="1:18" ht="162" customHeight="1">
@@ -6499,7 +6577,7 @@
         <v>202</v>
       </c>
       <c r="R56" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="57" spans="1:18" ht="110.25" customHeight="1">
@@ -6558,7 +6636,7 @@
         <v>206</v>
       </c>
       <c r="R57" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="162" customHeight="1">
@@ -6617,7 +6695,7 @@
         <v>209</v>
       </c>
       <c r="R58" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="59" spans="1:18" ht="110.25" customHeight="1">
@@ -6676,7 +6754,7 @@
         <v>213</v>
       </c>
       <c r="R59" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="60" spans="1:18" ht="162" customHeight="1">
@@ -6735,7 +6813,7 @@
         <v>216</v>
       </c>
       <c r="R60" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="61" spans="1:18" ht="162" customHeight="1">
@@ -6794,7 +6872,7 @@
         <v>219</v>
       </c>
       <c r="R61" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="62" spans="1:18" ht="110.25" customHeight="1">
@@ -6853,7 +6931,7 @@
         <v>222</v>
       </c>
       <c r="R62" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="63" spans="1:18" ht="162" customHeight="1">
@@ -6912,7 +6990,7 @@
         <v>225</v>
       </c>
       <c r="R63" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="64" spans="1:18" ht="132.75" customHeight="1">
@@ -6971,7 +7049,7 @@
         <v>229</v>
       </c>
       <c r="R64" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="65" spans="1:18" ht="132.75" customHeight="1">
@@ -7030,7 +7108,7 @@
         <v>233</v>
       </c>
       <c r="R65" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="66" spans="1:18" ht="162" customHeight="1">
@@ -7089,7 +7167,7 @@
         <v>236</v>
       </c>
       <c r="R66" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="67" spans="1:18" ht="162" customHeight="1">
@@ -7148,7 +7226,7 @@
         <v>239</v>
       </c>
       <c r="R67" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="68" spans="1:18" ht="162" customHeight="1">
@@ -7207,7 +7285,7 @@
         <v>239</v>
       </c>
       <c r="R68" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="69" spans="1:18" ht="132.75" customHeight="1">
@@ -7265,7 +7343,7 @@
         <v>245</v>
       </c>
       <c r="R69" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="70" spans="1:18" ht="162" customHeight="1">
@@ -7324,7 +7402,7 @@
         <v>248</v>
       </c>
       <c r="R70" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="71" spans="1:18" ht="162" customHeight="1">
@@ -7382,7 +7460,7 @@
         <v>251</v>
       </c>
       <c r="R71" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="72" spans="1:18" ht="162" customHeight="1">
@@ -7441,7 +7519,7 @@
         <v>254</v>
       </c>
       <c r="R72" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="73" spans="1:18" ht="162" customHeight="1">
@@ -7500,7 +7578,7 @@
         <v>257</v>
       </c>
       <c r="R73" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="74" spans="1:18" ht="144" customHeight="1">
@@ -7559,7 +7637,7 @@
         <v>261</v>
       </c>
       <c r="R74" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="75" spans="1:18" ht="162" customHeight="1">
@@ -7618,7 +7696,7 @@
         <v>264</v>
       </c>
       <c r="R75" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="76" spans="1:18" ht="132.75" customHeight="1">
@@ -7677,7 +7755,7 @@
         <v>268</v>
       </c>
       <c r="R76" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="77" spans="1:18" ht="176.25" customHeight="1">
@@ -7736,7 +7814,7 @@
         <v>271</v>
       </c>
       <c r="R77" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="78" spans="1:18" ht="132.75" customHeight="1">
@@ -7795,7 +7873,7 @@
         <v>275</v>
       </c>
       <c r="R78" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="79" spans="1:18" ht="132.75" customHeight="1">
@@ -7854,7 +7932,7 @@
         <v>279</v>
       </c>
       <c r="R79" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="80" spans="1:18" ht="153" customHeight="1">
@@ -7915,7 +7993,7 @@
         <v>283</v>
       </c>
       <c r="R80" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="132.75" customHeight="1">
@@ -7974,7 +8052,7 @@
         <v>287</v>
       </c>
       <c r="R81" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="82" spans="1:18" ht="153" customHeight="1">
@@ -8033,7 +8111,7 @@
         <v>291</v>
       </c>
       <c r="R82" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="83" spans="1:18" ht="162" customHeight="1">
@@ -8092,7 +8170,7 @@
         <v>294</v>
       </c>
       <c r="R83" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="84" spans="1:18" ht="162" customHeight="1">
@@ -8147,7 +8225,7 @@
         <v>298</v>
       </c>
       <c r="R84" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="85" spans="1:18" ht="153" customHeight="1">
@@ -8206,7 +8284,7 @@
         <v>300</v>
       </c>
       <c r="R85" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="86" spans="1:18" ht="162" customHeight="1">
@@ -8265,7 +8343,7 @@
         <v>303</v>
       </c>
       <c r="R86" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="87" spans="1:18" ht="162" customHeight="1">
@@ -8324,7 +8402,7 @@
         <v>306</v>
       </c>
       <c r="R87" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="88" spans="1:18" ht="153" customHeight="1">
@@ -8383,7 +8461,7 @@
         <v>309</v>
       </c>
       <c r="R88" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="89" spans="1:18" ht="153" customHeight="1">
@@ -8442,7 +8520,7 @@
         <v>313</v>
       </c>
       <c r="R89" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="90" spans="1:18" ht="204">
@@ -8499,7 +8577,7 @@
         <v>317</v>
       </c>
       <c r="R90" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="91" spans="1:18" ht="153" customHeight="1">
@@ -8558,7 +8636,7 @@
         <v>321</v>
       </c>
       <c r="R91" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="92" spans="1:18" ht="153" customHeight="1">
@@ -8617,7 +8695,7 @@
         <v>324</v>
       </c>
       <c r="R92" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="93" spans="1:18" ht="162" customHeight="1">
@@ -8676,7 +8754,7 @@
         <v>327</v>
       </c>
       <c r="R93" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="94" spans="1:18" ht="153" customHeight="1">
@@ -8735,7 +8813,7 @@
         <v>324</v>
       </c>
       <c r="R94" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="95" spans="1:18" ht="258" customHeight="1">
@@ -8794,7 +8872,7 @@
         <v>334</v>
       </c>
       <c r="R95" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="96" spans="1:18" ht="168.75" customHeight="1">
@@ -8851,7 +8929,7 @@
       </c>
       <c r="Q96" s="75"/>
       <c r="R96" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="97" spans="1:18" ht="129.75" customHeight="1">
@@ -8908,7 +8986,7 @@
         <v>339</v>
       </c>
       <c r="R97" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="98" spans="1:18" ht="140.25" customHeight="1">
@@ -8967,7 +9045,7 @@
         <v>343</v>
       </c>
       <c r="R98" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="99" spans="1:18" ht="184.5" customHeight="1">
@@ -9026,7 +9104,7 @@
         <v>347</v>
       </c>
       <c r="R99" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="100" spans="1:18" ht="177" customHeight="1">
@@ -9083,7 +9161,7 @@
         <v>350</v>
       </c>
       <c r="R100" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="101" spans="1:18" ht="140.25" customHeight="1">
@@ -9142,7 +9220,7 @@
         <v>354</v>
       </c>
       <c r="R101" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="102" spans="1:18" ht="140.25" customHeight="1">
@@ -9201,7 +9279,7 @@
         <v>358</v>
       </c>
       <c r="R102" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="103" spans="1:18" ht="140.25" customHeight="1">
@@ -9260,7 +9338,7 @@
         <v>362</v>
       </c>
       <c r="R103" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="104" spans="1:18" ht="140.25" customHeight="1">
@@ -9319,7 +9397,7 @@
         <v>366</v>
       </c>
       <c r="R104" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="105" spans="1:18" ht="140.25" customHeight="1">
@@ -9378,7 +9456,7 @@
         <v>370</v>
       </c>
       <c r="R105" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="106" spans="1:18" ht="140.25" customHeight="1">
@@ -9437,7 +9515,7 @@
         <v>374</v>
       </c>
       <c r="R106" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="107" spans="1:18" ht="140.25" customHeight="1">
@@ -9458,7 +9536,7 @@
         <v>378</v>
       </c>
       <c r="G107" s="74">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H107" s="35">
         <f>IF(OR(J107="",K107="",K107&lt;J107),0,NETWORKDAYS(J107,K107,Hoja2!$A$2:$A$53))</f>
@@ -9481,7 +9559,7 @@
       NETWORKDAYS(J107,L107,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="N107" s="38"/>
       <c r="O107" s="38"/>
@@ -9490,7 +9568,7 @@
         <v>379</v>
       </c>
       <c r="R107" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="108" spans="1:18" ht="140.25" customHeight="1">
@@ -9508,10 +9586,10 @@
       </c>
       <c r="E108" s="19"/>
       <c r="F108" s="52" t="s">
-        <v>378</v>
+        <v>150</v>
       </c>
       <c r="G108" s="64">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="H108" s="22">
         <f>IF(OR(J108="",K108="",K108&lt;J108),0,NETWORKDAYS(J108,K108,Hoja2!$A$2:$A$53))</f>
@@ -9526,7 +9604,9 @@
       <c r="K108" s="24">
         <v>46174</v>
       </c>
-      <c r="L108" s="24"/>
+      <c r="L108" s="24">
+        <v>46178</v>
+      </c>
       <c r="M108" s="25">
         <f ca="1">IF(OR(J108="",AND(L108="",TODAY()&lt;J108),AND(L108&lt;&gt;"",L108&lt;J108)),0,
    IF(L108="",
@@ -9534,16 +9614,18 @@
       NETWORKDAYS(J108,L108,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N108" s="24"/>
-      <c r="O108" s="24"/>
+      <c r="O108" s="24">
+        <v>46178</v>
+      </c>
       <c r="P108" s="24"/>
       <c r="Q108" s="75" t="s">
         <v>383</v>
       </c>
       <c r="R108" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
     </row>
     <row r="109" spans="1:18" ht="140.25" customHeight="1">
@@ -9561,7 +9643,7 @@
       </c>
       <c r="E109" s="32"/>
       <c r="F109" s="70" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="G109" s="74">
         <v>5</v>
@@ -9587,30 +9669,380 @@
       NETWORKDAYS(J109,L109,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="N109" s="38"/>
       <c r="O109" s="38"/>
       <c r="P109" s="38"/>
       <c r="Q109" s="76" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="R109" s="160" t="s">
-        <v>493</v>
+        <v>518</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" ht="140.25" customHeight="1">
+      <c r="A110" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B110" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="C110" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="D110" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="E110" s="19"/>
+      <c r="F110" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="G110" s="64">
+        <v>100</v>
+      </c>
+      <c r="H110" s="22">
+        <f>IF(OR(J110="",K110="",K110&lt;J110),0,NETWORKDAYS(J110,K110,Hoja2!$A$2:$A$53))</f>
+        <v>2</v>
+      </c>
+      <c r="I110" s="43">
+        <v>46182</v>
+      </c>
+      <c r="J110" s="43">
+        <v>46182</v>
+      </c>
+      <c r="K110" s="24">
+        <v>46183</v>
+      </c>
+      <c r="L110" s="24">
+        <v>46183</v>
+      </c>
+      <c r="M110" s="25">
+        <f ca="1">IF(OR(J110="",AND(L110="",TODAY()&lt;J110),AND(L110&lt;&gt;"",L110&lt;J110)),0,
+   IF(L110="",
+      NETWORKDAYS(J110,TODAY(),Hoja2!$A$2:$A$53),
+      NETWORKDAYS(J110,L110,Hoja2!$A$2:$A$53)
+   )
+)</f>
+        <v>2</v>
+      </c>
+      <c r="N110" s="24"/>
+      <c r="O110" s="24">
+        <v>46183</v>
+      </c>
+      <c r="P110" s="24">
+        <v>46183</v>
+      </c>
+      <c r="Q110" s="75" t="s">
+        <v>392</v>
+      </c>
+      <c r="R110" s="160" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" ht="169.5" customHeight="1">
+      <c r="A111" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B111" s="30" t="s">
+        <v>393</v>
+      </c>
+      <c r="C111" s="31" t="s">
+        <v>394</v>
+      </c>
+      <c r="D111" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="E111" s="32"/>
+      <c r="F111" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="G111" s="74">
+        <v>100</v>
+      </c>
+      <c r="H111" s="35">
+        <f>IF(OR(J111="",K111="",K111&lt;J111),0,NETWORKDAYS(J111,K111,Hoja2!$A$2:$A$53))</f>
+        <v>3</v>
+      </c>
+      <c r="I111" s="37">
+        <v>46184</v>
+      </c>
+      <c r="J111" s="37">
+        <v>46185</v>
+      </c>
+      <c r="K111" s="38">
+        <v>46190</v>
+      </c>
+      <c r="L111" s="38">
+        <v>46191</v>
+      </c>
+      <c r="M111" s="39">
+        <f ca="1">IF(OR(J111="",AND(L111="",TODAY()&lt;J111),AND(L111&lt;&gt;"",L111&lt;J111)),0,
+   IF(L111="",
+      NETWORKDAYS(J111,TODAY(),Hoja2!$A$2:$A$53),
+      NETWORKDAYS(J111,L111,Hoja2!$A$2:$A$53)
+   )
+)</f>
+        <v>4</v>
+      </c>
+      <c r="N111" s="38"/>
+      <c r="O111" s="38">
+        <v>46190</v>
+      </c>
+      <c r="P111" s="38">
+        <v>46191</v>
+      </c>
+      <c r="Q111" s="76" t="s">
+        <v>396</v>
+      </c>
+      <c r="R111" s="160" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" ht="140.25" customHeight="1">
+      <c r="A112" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B112" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="C112" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="D112" s="19" t="s">
+        <v>399</v>
+      </c>
+      <c r="E112" s="19"/>
+      <c r="F112" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="G112" s="64">
+        <v>100</v>
+      </c>
+      <c r="H112" s="22">
+        <f>IF(OR(J112="",K112="",K112&lt;J112),0,NETWORKDAYS(J112,K112,Hoja2!$A$2:$A$53))</f>
+        <v>2</v>
+      </c>
+      <c r="I112" s="43">
+        <v>46189</v>
+      </c>
+      <c r="J112" s="43">
+        <v>46189</v>
+      </c>
+      <c r="K112" s="24">
+        <v>46190</v>
+      </c>
+      <c r="L112" s="24">
+        <v>46190</v>
+      </c>
+      <c r="M112" s="25">
+        <f ca="1">IF(OR(J112="",AND(L112="",TODAY()&lt;J112),AND(L112&lt;&gt;"",L112&lt;J112)),0,
+   IF(L112="",
+      NETWORKDAYS(J112,TODAY(),Hoja2!$A$2:$A$53),
+      NETWORKDAYS(J112,L112,Hoja2!$A$2:$A$53)
+   )
+)</f>
+        <v>2</v>
+      </c>
+      <c r="N112" s="24"/>
+      <c r="O112" s="24">
+        <v>46190</v>
+      </c>
+      <c r="P112" s="24">
+        <v>46190</v>
+      </c>
+      <c r="Q112" s="75" t="s">
+        <v>400</v>
+      </c>
+      <c r="R112" s="160" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" ht="140.25" customHeight="1">
+      <c r="A113" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B113" s="30" t="s">
+        <v>401</v>
+      </c>
+      <c r="C113" s="31" t="s">
+        <v>402</v>
+      </c>
+      <c r="D113" s="32" t="s">
+        <v>403</v>
+      </c>
+      <c r="E113" s="32"/>
+      <c r="F113" s="70" t="s">
+        <v>404</v>
+      </c>
+      <c r="G113" s="74">
+        <v>100</v>
+      </c>
+      <c r="H113" s="35">
+        <f>IF(OR(J113="",K113="",K113&lt;J113),0,NETWORKDAYS(J113,K113,Hoja2!$A$2:$A$53))</f>
+        <v>1</v>
+      </c>
+      <c r="I113" s="37">
+        <v>46192</v>
+      </c>
+      <c r="J113" s="37">
+        <v>46192</v>
+      </c>
+      <c r="K113" s="38">
+        <v>46192</v>
+      </c>
+      <c r="L113" s="38"/>
+      <c r="M113" s="39">
+        <f ca="1">IF(OR(J113="",AND(L113="",TODAY()&lt;J113),AND(L113&lt;&gt;"",L113&lt;J113)),0,
+   IF(L113="",
+      NETWORKDAYS(J113,TODAY(),Hoja2!$A$2:$A$53),
+      NETWORKDAYS(J113,L113,Hoja2!$A$2:$A$53)
+   )
+)</f>
+        <v>4</v>
+      </c>
+      <c r="N113" s="38"/>
+      <c r="O113" s="38">
+        <v>46192</v>
+      </c>
+      <c r="P113" s="38">
+        <v>46192</v>
+      </c>
+      <c r="Q113" s="76" t="s">
+        <v>405</v>
+      </c>
+      <c r="R113" s="160" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" ht="140.25" customHeight="1">
+      <c r="A114" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B114" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="C114" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="D114" s="19" t="s">
+        <v>408</v>
+      </c>
+      <c r="E114" s="19"/>
+      <c r="F114" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="G114" s="64">
+        <v>100</v>
+      </c>
+      <c r="H114" s="22">
+        <f>IF(OR(J114="",K114="",K114&lt;J114),0,NETWORKDAYS(J114,K114,Hoja2!$A$2:$A$53))</f>
+        <v>1</v>
+      </c>
+      <c r="I114" s="43">
+        <v>46196</v>
+      </c>
+      <c r="J114" s="43">
+        <v>46196</v>
+      </c>
+      <c r="K114" s="24">
+        <v>46196</v>
+      </c>
+      <c r="L114" s="24">
+        <v>46196</v>
+      </c>
+      <c r="M114" s="25">
+        <f ca="1">IF(OR(J114="",AND(L114="",TODAY()&lt;J114),AND(L114&lt;&gt;"",L114&lt;J114)),0,
+   IF(L114="",
+      NETWORKDAYS(J114,TODAY(),Hoja2!$A$2:$A$53),
+      NETWORKDAYS(J114,L114,Hoja2!$A$2:$A$53)
+   )
+)</f>
+        <v>1</v>
+      </c>
+      <c r="N114" s="24"/>
+      <c r="O114" s="24">
+        <v>46196</v>
+      </c>
+      <c r="P114" s="24">
+        <v>46196</v>
+      </c>
+      <c r="Q114" s="75" t="s">
+        <v>409</v>
+      </c>
+      <c r="R114" s="160" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" ht="140.25" customHeight="1">
+      <c r="A115" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B115" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="C115" s="31" t="s">
+        <v>411</v>
+      </c>
+      <c r="D115" s="32" t="s">
+        <v>412</v>
+      </c>
+      <c r="E115" s="32"/>
+      <c r="F115" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="G115" s="74">
+        <v>100</v>
+      </c>
+      <c r="H115" s="35">
+        <f>IF(OR(J115="",K115="",K115&lt;J115),0,NETWORKDAYS(J115,K115,Hoja2!$A$2:$A$53))</f>
+        <v>1</v>
+      </c>
+      <c r="I115" s="37">
+        <v>46192</v>
+      </c>
+      <c r="J115" s="37">
+        <v>46195</v>
+      </c>
+      <c r="K115" s="38">
+        <v>46195</v>
+      </c>
+      <c r="L115" s="38">
+        <v>46195</v>
+      </c>
+      <c r="M115" s="39">
+        <f ca="1">IF(OR(J115="",AND(L115="",TODAY()&lt;J115),AND(L115&lt;&gt;"",L115&lt;J115)),0,
+   IF(L115="",
+      NETWORKDAYS(J115,TODAY(),Hoja2!$A$2:$A$53),
+      NETWORKDAYS(J115,L115,Hoja2!$A$2:$A$53)
+   )
+)</f>
+        <v>1</v>
+      </c>
+      <c r="N115" s="38"/>
+      <c r="O115" s="38">
+        <v>46195</v>
+      </c>
+      <c r="P115" s="38">
+        <v>46195</v>
+      </c>
+      <c r="Q115" s="76"/>
+      <c r="R115" s="160" t="s">
+        <v>518</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN109"/>
-  <conditionalFormatting sqref="B1:B109">
+  <autoFilter ref="A1:AN115"/>
+  <conditionalFormatting sqref="B1:B115">
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>COUNTIF(B$1:B$109, B1)&gt;1</formula>
+      <formula>COUNTIF(B$1:B$115, B1)&gt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I2:L20 I21 K21:L21 I22:L109 N2:P109">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="I2:L20 I21 K21:L21 I22:L115 N2:P115">
       <formula1>OR(NOT(ISERROR(DATEVALUE(I2))), AND(ISNUMBER(I2), LEFT(CELL("format", I2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F109">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F115">
       <formula1>"FINALIZADO,EN PROCESO,PAUSADO,EN TEST,PENDIENTE,PRUEBAS CLIENTE,PRUEBAS IMAGINE,CANCELADO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9653,7 +10085,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="79" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="I1" s="80" t="s">
         <v>8</v>
@@ -9668,7 +10100,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="80" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="N1" s="82" t="s">
         <v>14</v>
@@ -9704,19 +10136,19 @@
     </row>
     <row r="2" spans="1:39" ht="29.25" customHeight="1">
       <c r="A2" s="83" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="B2" s="84" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="85" t="s">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="D2" s="84" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="84" t="s">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="F2" s="86" t="s">
         <v>22</v>
@@ -9751,19 +10183,19 @@
     </row>
     <row r="3" spans="1:39" ht="29.25" customHeight="1">
       <c r="A3" s="83" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="B3" s="84" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="85" t="s">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="D3" s="84" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="84" t="s">
-        <v>393</v>
+        <v>418</v>
       </c>
       <c r="F3" s="86" t="s">
         <v>22</v>
@@ -9798,19 +10230,19 @@
     </row>
     <row r="4" spans="1:39" ht="39" customHeight="1">
       <c r="A4" s="83" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="B4" s="84" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="85" t="s">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="D4" s="84" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="84" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="F4" s="86" t="s">
         <v>22</v>
@@ -9849,19 +10281,19 @@
     </row>
     <row r="5" spans="1:39" ht="127.5">
       <c r="A5" s="83" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="B5" s="84" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="85" t="s">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="D5" s="84" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="100" t="s">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="F5" s="86" t="s">
         <v>22</v>
@@ -9900,19 +10332,19 @@
     </row>
     <row r="6" spans="1:39" ht="29.25" customHeight="1">
       <c r="A6" s="83" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="B6" s="84" t="s">
         <v>34</v>
       </c>
       <c r="C6" s="85" t="s">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="D6" s="84" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="102" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="F6" s="103" t="s">
         <v>22</v>
@@ -9951,19 +10383,19 @@
     </row>
     <row r="7" spans="1:39" ht="29.25" customHeight="1">
       <c r="A7" s="83" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="B7" s="84" t="s">
         <v>37</v>
       </c>
       <c r="C7" s="85" t="s">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="D7" s="84" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="84" t="s">
-        <v>398</v>
+        <v>423</v>
       </c>
       <c r="F7" s="105" t="s">
         <v>22</v>
@@ -10002,19 +10434,19 @@
     </row>
     <row r="8" spans="1:39" ht="29.25" customHeight="1">
       <c r="A8" s="83" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="B8" s="84" t="s">
         <v>40</v>
       </c>
       <c r="C8" s="85" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="D8" s="84" t="s">
         <v>42</v>
       </c>
       <c r="E8" s="107" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="F8" s="86" t="s">
         <v>22</v>
@@ -10049,17 +10481,17 @@
     </row>
     <row r="9" spans="1:39" ht="29.25" customHeight="1">
       <c r="A9" s="83" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="B9" s="84" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="111" t="s">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="D9" s="112"/>
       <c r="E9" s="84" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="F9" s="105" t="s">
         <v>22</v>
@@ -10096,17 +10528,17 @@
     </row>
     <row r="10" spans="1:39" ht="93" customHeight="1">
       <c r="A10" s="83" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="B10" s="84" t="s">
         <v>47</v>
       </c>
       <c r="C10" s="111" t="s">
-        <v>403</v>
+        <v>428</v>
       </c>
       <c r="D10" s="112"/>
       <c r="E10" s="84" t="s">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="F10" s="105" t="s">
         <v>22</v>
@@ -10141,19 +10573,19 @@
     </row>
     <row r="11" spans="1:39" ht="409.5">
       <c r="A11" s="83" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="B11" s="84" t="s">
         <v>50</v>
       </c>
       <c r="C11" s="85" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="D11" s="84" t="s">
         <v>42</v>
       </c>
       <c r="E11" s="114" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="F11" s="105" t="s">
         <v>22</v>
@@ -10190,19 +10622,19 @@
     </row>
     <row r="12" spans="1:39" ht="29.25" customHeight="1">
       <c r="A12" s="83" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="B12" s="84" t="s">
         <v>53</v>
       </c>
       <c r="C12" s="115" t="s">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="D12" s="84" t="s">
         <v>55</v>
       </c>
       <c r="E12" s="84" t="s">
-        <v>407</v>
+        <v>432</v>
       </c>
       <c r="F12" s="105" t="s">
         <v>22</v>
@@ -10239,19 +10671,19 @@
     </row>
     <row r="13" spans="1:39" ht="29.25" customHeight="1">
       <c r="A13" s="83" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="B13" s="84" t="s">
         <v>57</v>
       </c>
       <c r="C13" s="111" t="s">
-        <v>408</v>
+        <v>433</v>
       </c>
       <c r="D13" s="84" t="s">
         <v>59</v>
       </c>
       <c r="E13" s="84" t="s">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="F13" s="105" t="s">
         <v>22</v>
@@ -10286,7 +10718,7 @@
     </row>
     <row r="14" spans="1:39" ht="29.25" customHeight="1">
       <c r="A14" s="83" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="B14" s="84" t="s">
         <v>61</v>
@@ -10296,7 +10728,7 @@
       </c>
       <c r="D14" s="116"/>
       <c r="E14" s="102" t="s">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="F14" s="110" t="s">
         <v>22</v>
@@ -10359,7 +10791,7 @@
         <v>45292</v>
       </c>
       <c r="B1" s="118" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17.25" customHeight="1">
@@ -10367,7 +10799,7 @@
         <v>45299</v>
       </c>
       <c r="B2" s="118" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.25" customHeight="1">
@@ -10375,7 +10807,7 @@
         <v>45376</v>
       </c>
       <c r="B3" s="118" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17.25" customHeight="1">
@@ -10383,7 +10815,7 @@
         <v>45379</v>
       </c>
       <c r="B4" s="118" t="s">
-        <v>414</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="17.25" customHeight="1">
@@ -10391,7 +10823,7 @@
         <v>45380</v>
       </c>
       <c r="B5" s="118" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="17.25" customHeight="1">
@@ -10399,7 +10831,7 @@
         <v>45413</v>
       </c>
       <c r="B6" s="118" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.25" customHeight="1">
@@ -10407,7 +10839,7 @@
         <v>45425</v>
       </c>
       <c r="B7" s="118" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17.25" customHeight="1">
@@ -10415,7 +10847,7 @@
         <v>45446</v>
       </c>
       <c r="B8" s="118" t="s">
-        <v>418</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17.25" customHeight="1">
@@ -10423,7 +10855,7 @@
         <v>45453</v>
       </c>
       <c r="B9" s="118" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="17.25" customHeight="1">
@@ -10431,7 +10863,7 @@
         <v>45474</v>
       </c>
       <c r="B10" s="118" t="s">
-        <v>420</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17.25" customHeight="1">
@@ -10439,7 +10871,7 @@
         <v>45493</v>
       </c>
       <c r="B11" s="118" t="s">
-        <v>421</v>
+        <v>446</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17.25" customHeight="1">
@@ -10447,7 +10879,7 @@
         <v>45511</v>
       </c>
       <c r="B12" s="118" t="s">
-        <v>422</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17.25" customHeight="1">
@@ -10455,7 +10887,7 @@
         <v>45523</v>
       </c>
       <c r="B13" s="118" t="s">
-        <v>423</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17.25" customHeight="1">
@@ -10463,7 +10895,7 @@
         <v>45579</v>
       </c>
       <c r="B14" s="118" t="s">
-        <v>424</v>
+        <v>449</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17.25" customHeight="1">
@@ -10471,7 +10903,7 @@
         <v>45600</v>
       </c>
       <c r="B15" s="118" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17.25" customHeight="1">
@@ -10479,7 +10911,7 @@
         <v>45607</v>
       </c>
       <c r="B16" s="118" t="s">
-        <v>426</v>
+        <v>451</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17.25" customHeight="1">
@@ -10487,7 +10919,7 @@
         <v>45634</v>
       </c>
       <c r="B17" s="118" t="s">
-        <v>427</v>
+        <v>452</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="17.25" customHeight="1">
@@ -10495,7 +10927,7 @@
         <v>45651</v>
       </c>
       <c r="B18" s="118" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="17.25" customHeight="1">
@@ -10503,7 +10935,7 @@
         <v>45658</v>
       </c>
       <c r="B19" s="119" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25" customHeight="1">
@@ -10511,7 +10943,7 @@
         <v>45663</v>
       </c>
       <c r="B20" s="119" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17.25" customHeight="1">
@@ -10519,7 +10951,7 @@
         <v>45740</v>
       </c>
       <c r="B21" s="119" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="17.25" customHeight="1">
@@ -10527,7 +10959,7 @@
         <v>45764</v>
       </c>
       <c r="B22" s="119" t="s">
-        <v>432</v>
+        <v>457</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17.25" customHeight="1">
@@ -10535,7 +10967,7 @@
         <v>45765</v>
       </c>
       <c r="B23" s="119" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="17.25" customHeight="1">
@@ -10543,7 +10975,7 @@
         <v>45778</v>
       </c>
       <c r="B24" s="119" t="s">
-        <v>434</v>
+        <v>459</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="17.25" customHeight="1">
@@ -10551,7 +10983,7 @@
         <v>45810</v>
       </c>
       <c r="B25" s="119" t="s">
-        <v>435</v>
+        <v>460</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17.25" customHeight="1">
@@ -10559,7 +10991,7 @@
         <v>45831</v>
       </c>
       <c r="B26" s="119" t="s">
-        <v>436</v>
+        <v>461</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="17.25" customHeight="1">
@@ -10567,7 +10999,7 @@
         <v>45838</v>
       </c>
       <c r="B27" s="119" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="17.25" customHeight="1">
@@ -10575,7 +11007,7 @@
         <v>45858</v>
       </c>
       <c r="B28" s="119" t="s">
-        <v>438</v>
+        <v>463</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="17.25" customHeight="1">
@@ -10583,7 +11015,7 @@
         <v>45876</v>
       </c>
       <c r="B29" s="119" t="s">
-        <v>439</v>
+        <v>464</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="17.25" customHeight="1">
@@ -10591,7 +11023,7 @@
         <v>45887</v>
       </c>
       <c r="B30" s="119" t="s">
-        <v>440</v>
+        <v>465</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="17.25" customHeight="1">
@@ -10599,7 +11031,7 @@
         <v>45943</v>
       </c>
       <c r="B31" s="119" t="s">
-        <v>441</v>
+        <v>466</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="17.25" customHeight="1">
@@ -10607,7 +11039,7 @@
         <v>45964</v>
       </c>
       <c r="B32" s="119" t="s">
-        <v>442</v>
+        <v>467</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="17.25" customHeight="1">
@@ -10615,7 +11047,7 @@
         <v>45978</v>
       </c>
       <c r="B33" s="119" t="s">
-        <v>443</v>
+        <v>468</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="17.25" customHeight="1">
@@ -10623,7 +11055,7 @@
         <v>45999</v>
       </c>
       <c r="B34" s="119" t="s">
-        <v>444</v>
+        <v>469</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17.25" customHeight="1">
@@ -10631,7 +11063,7 @@
         <v>46016</v>
       </c>
       <c r="B35" s="119" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17.25" customHeight="1">
@@ -10639,7 +11071,7 @@
         <v>46023</v>
       </c>
       <c r="B36" s="119" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="17.25" customHeight="1">
@@ -10647,7 +11079,7 @@
         <v>46034</v>
       </c>
       <c r="B37" s="119" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17.25" customHeight="1">
@@ -10655,7 +11087,7 @@
         <v>46104</v>
       </c>
       <c r="B38" s="119" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17.25" customHeight="1">
@@ -10663,7 +11095,7 @@
         <v>46114</v>
       </c>
       <c r="B39" s="119" t="s">
-        <v>432</v>
+        <v>457</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="17.25" customHeight="1">
@@ -10671,7 +11103,7 @@
         <v>46115</v>
       </c>
       <c r="B40" s="119" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17.25" customHeight="1">
@@ -10679,7 +11111,7 @@
         <v>46143</v>
       </c>
       <c r="B41" s="119" t="s">
-        <v>434</v>
+        <v>459</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="17.25" customHeight="1">
@@ -10687,7 +11119,7 @@
         <v>46160</v>
       </c>
       <c r="B42" s="119" t="s">
-        <v>435</v>
+        <v>460</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="17.25" customHeight="1">
@@ -10695,7 +11127,7 @@
         <v>46181</v>
       </c>
       <c r="B43" s="119" t="s">
-        <v>436</v>
+        <v>461</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="17.25" customHeight="1">
@@ -10703,7 +11135,7 @@
         <v>46188</v>
       </c>
       <c r="B44" s="119" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="17.25" customHeight="1">
@@ -10711,7 +11143,7 @@
         <v>46202</v>
       </c>
       <c r="B45" s="119" t="s">
-        <v>447</v>
+        <v>472</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="17.25" customHeight="1">
@@ -10719,7 +11151,7 @@
         <v>46223</v>
       </c>
       <c r="B46" s="119" t="s">
-        <v>438</v>
+        <v>463</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="17.25" customHeight="1">
@@ -10727,7 +11159,7 @@
         <v>46241</v>
       </c>
       <c r="B47" s="119" t="s">
-        <v>439</v>
+        <v>464</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="17.25" customHeight="1">
@@ -10735,7 +11167,7 @@
         <v>46251</v>
       </c>
       <c r="B48" s="119" t="s">
-        <v>440</v>
+        <v>465</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="17.25" customHeight="1">
@@ -10743,7 +11175,7 @@
         <v>46307</v>
       </c>
       <c r="B49" s="119" t="s">
-        <v>441</v>
+        <v>466</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="17.25" customHeight="1">
@@ -10751,7 +11183,7 @@
         <v>46328</v>
       </c>
       <c r="B50" s="119" t="s">
-        <v>442</v>
+        <v>467</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="17.25" customHeight="1">
@@ -10759,7 +11191,7 @@
         <v>46342</v>
       </c>
       <c r="B51" s="119" t="s">
-        <v>443</v>
+        <v>468</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="17.25" customHeight="1">
@@ -10767,7 +11199,7 @@
         <v>46364</v>
       </c>
       <c r="B52" s="119" t="s">
-        <v>444</v>
+        <v>469</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="17.25" customHeight="1">
@@ -10775,7 +11207,7 @@
         <v>46381</v>
       </c>
       <c r="B53" s="119" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="17.25" customHeight="1"/>
@@ -11744,7 +12176,7 @@
   <sheetData>
     <row r="1" spans="1:97" ht="15.75">
       <c r="A1" s="120" t="s">
-        <v>448</v>
+        <v>473</v>
       </c>
       <c r="B1" s="121"/>
       <c r="C1" s="121"/>
@@ -11802,7 +12234,7 @@
     </row>
     <row r="3" spans="1:97" ht="32.25" customHeight="1">
       <c r="A3" s="122" t="s">
-        <v>449</v>
+        <v>474</v>
       </c>
       <c r="B3" s="123">
         <v>45596</v>
@@ -12095,261 +12527,261 @@
     </row>
     <row r="4" spans="1:97" ht="30.75" customHeight="1">
       <c r="A4" s="126" t="s">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="B4" s="127" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="C4" s="128" t="s">
-        <v>452</v>
+        <v>477</v>
       </c>
       <c r="D4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="E4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="F4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="G4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="H4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="I4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="J4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="K4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="L4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="M4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="N4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="O4" s="129" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="P4" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Q4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="R4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="S4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="T4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="U4" s="130" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="V4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="W4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="X4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Y4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Z4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AA4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AB4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AC4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AD4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AE4" s="155" t="s">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="AF4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AG4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AH4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AI4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AJ4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AK4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AL4" s="155" t="s">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="AM4" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AN4" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AO4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AP4" s="155" t="s">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="AQ4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AR4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AS4" s="155" t="s">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="AT4" s="131" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AU4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AV4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AW4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AX4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AY4" s="155" t="s">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="AZ4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BA4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BB4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BC4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BD4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BE4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BF4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BG4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BH4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BI4" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BJ4" s="155" t="s">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="BK4" s="130" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="BL4" s="130" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="BM4" s="130" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="BN4" s="130" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="BO4" s="130" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="BP4" s="130" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="BQ4" s="130" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="BR4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BS4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BT4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BU4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BV4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BW4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BX4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BY4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BZ4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CA4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CB4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CC4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CD4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CE4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CF4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CG4" s="129"/>
       <c r="CH4" s="129"/>
       <c r="CI4" s="155" t="s">
-        <v>459</v>
+        <v>484</v>
       </c>
       <c r="CJ4" s="129"/>
       <c r="CK4" s="129"/>
@@ -12361,249 +12793,249 @@
       <c r="CQ4" s="129"/>
       <c r="CR4" s="129"/>
       <c r="CS4" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:97" ht="15.75" customHeight="1">
       <c r="A5" s="126" t="s">
-        <v>460</v>
+        <v>485</v>
       </c>
       <c r="B5" s="127" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="C5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="D5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="E5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="F5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="G5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="H5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="I5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="J5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="K5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="L5" s="129" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="M5" s="129" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="N5" s="129" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="O5" s="129" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="P5" s="130" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="Q5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="R5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="S5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="T5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="U5" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="V5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="W5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="X5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Y5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Z5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AA5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AB5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AC5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AD5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AE5" s="156"/>
       <c r="AF5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AG5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AH5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AI5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AJ5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AK5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AL5" s="156"/>
       <c r="AM5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AN5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AO5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AP5" s="156"/>
       <c r="AQ5" s="129" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="AR5" s="129" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="AS5" s="156"/>
       <c r="AT5" s="129" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="AU5" s="129" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="AV5" s="129" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="AW5" s="129" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="AX5" s="129" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="AY5" s="156"/>
       <c r="AZ5" s="129" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="BA5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BB5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BC5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BD5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BE5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BF5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BG5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BH5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BI5" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BJ5" s="156"/>
       <c r="BK5" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BL5" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BM5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BN5" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BO5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BP5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BQ5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BR5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BS5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BT5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BU5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BV5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BW5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BX5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BY5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BZ5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CA5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CB5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CC5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CD5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CE5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CF5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CG5" s="129"/>
       <c r="CH5" s="129"/>
@@ -12618,249 +13050,249 @@
       <c r="CQ5" s="129"/>
       <c r="CR5" s="129"/>
       <c r="CS5" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:97" ht="15.75">
       <c r="A6" s="126" t="s">
-        <v>461</v>
+        <v>486</v>
       </c>
       <c r="B6" s="127" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="C6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="D6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="E6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="F6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="G6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="H6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="I6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="J6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="K6" s="132" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="L6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="M6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="N6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="O6" s="129" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="P6" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Q6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="R6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="S6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="T6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="U6" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="V6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="W6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="X6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Y6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Z6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AA6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AB6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AC6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AD6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AE6" s="156"/>
       <c r="AF6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AG6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AH6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AI6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AJ6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AK6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AL6" s="156"/>
       <c r="AM6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AN6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AO6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AP6" s="156"/>
       <c r="AQ6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AR6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AS6" s="156"/>
       <c r="AT6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AU6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AV6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AW6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AX6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AY6" s="156"/>
       <c r="AZ6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BA6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BB6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BC6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BD6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BE6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BF6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BG6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BH6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BI6" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BJ6" s="156"/>
       <c r="BK6" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BL6" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BM6" s="129" t="s">
-        <v>463</v>
+        <v>488</v>
       </c>
       <c r="BN6" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BO6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BP6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BQ6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BR6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BS6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BT6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BU6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BV6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BW6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BX6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BY6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BZ6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CA6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CB6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CC6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CD6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CE6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CF6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CG6" s="129"/>
       <c r="CH6" s="129"/>
@@ -12875,198 +13307,198 @@
       <c r="CQ6" s="129"/>
       <c r="CR6" s="129"/>
       <c r="CS6" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" spans="1:97" ht="15.75" hidden="1" customHeight="1">
       <c r="A7" s="126" t="s">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="B7" s="127" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="C7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="D7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="E7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="F7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="G7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="H7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="I7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="J7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="K7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="L7" s="132" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="M7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="N7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="O7" s="129" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="P7" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Q7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="R7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="S7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="T7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="U7" s="130" t="s">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="V7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="W7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="X7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Y7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Z7" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AA7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AB7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AC7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AD7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AE7" s="156"/>
       <c r="AF7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AG7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AH7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AI7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AJ7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AK7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AL7" s="156"/>
       <c r="AM7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AN7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AO7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AP7" s="156"/>
       <c r="AQ7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AR7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AS7" s="156"/>
       <c r="AT7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AU7" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AV7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AW7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AX7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AY7" s="156"/>
       <c r="AZ7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BA7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BB7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BC7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BD7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BE7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BF7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BG7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BH7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BI7" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BJ7" s="156"/>
       <c r="BK7" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BL7" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BM7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BN7" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BO7" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BP7" s="129"/>
       <c r="BQ7" s="129"/>
@@ -13074,16 +13506,16 @@
       <c r="BS7" s="129"/>
       <c r="BT7" s="129"/>
       <c r="BU7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BV7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BW7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BX7" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BY7" s="129"/>
       <c r="BZ7" s="129"/>
@@ -13109,220 +13541,220 @@
     </row>
     <row r="8" spans="1:97" ht="15.75" hidden="1" customHeight="1">
       <c r="A8" s="126" t="s">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="B8" s="127" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="C8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="D8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="E8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="F8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="G8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="H8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="I8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="J8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="K8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="L8" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="M8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="N8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="O8" s="129" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="P8" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Q8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="R8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="S8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="T8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="U8" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="V8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="W8" s="129" t="s">
-        <v>467</v>
+        <v>492</v>
       </c>
       <c r="X8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Y8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Z8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AA8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AB8" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AC8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AD8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AE8" s="156"/>
       <c r="AF8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AG8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AH8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AI8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AJ8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AK8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AL8" s="156"/>
       <c r="AM8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AN8" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AO8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AP8" s="156"/>
       <c r="AQ8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AR8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AS8" s="156"/>
       <c r="AT8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AU8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AV8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AW8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AX8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AY8" s="156"/>
       <c r="AZ8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BA8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BB8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BC8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BD8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BE8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BF8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BG8" s="129" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="BH8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BI8" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BJ8" s="156"/>
       <c r="BK8" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BL8" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BM8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BN8" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BO8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BP8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BQ8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BR8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BS8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BT8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BU8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BV8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BW8" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BX8" s="129" t="s">
-        <v>469</v>
+        <v>494</v>
       </c>
       <c r="BY8" s="129"/>
       <c r="BZ8" s="129"/>
@@ -13348,244 +13780,244 @@
     </row>
     <row r="9" spans="1:97" ht="15.75">
       <c r="A9" s="126" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="B9" s="127" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="C9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="D9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="E9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="F9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="G9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="H9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="I9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="J9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="K9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="L9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="M9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="N9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="O9" s="132" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="P9" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Q9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="R9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="S9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="T9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="U9" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="V9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="W9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="X9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Y9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Z9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AA9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AB9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AC9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AD9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AE9" s="156"/>
       <c r="AF9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AG9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AH9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AI9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AJ9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AK9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AL9" s="156"/>
       <c r="AM9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AN9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AO9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AP9" s="156"/>
       <c r="AQ9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AR9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AS9" s="156"/>
       <c r="AT9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AU9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AV9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AW9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AX9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AY9" s="156"/>
       <c r="AZ9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BA9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BB9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BC9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BD9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BE9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BF9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BG9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BH9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BI9" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BJ9" s="156"/>
       <c r="BK9" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BL9" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BM9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BN9" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BO9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BP9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BQ9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BR9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BS9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BT9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BU9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BV9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BW9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BX9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BY9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BZ9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CA9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CB9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CC9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CD9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CE9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CF9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CG9" s="129"/>
       <c r="CH9" s="129"/>
@@ -13600,249 +14032,249 @@
       <c r="CQ9" s="129"/>
       <c r="CR9" s="129"/>
       <c r="CS9" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10" spans="1:97" ht="15.75">
       <c r="A10" s="126" t="s">
-        <v>471</v>
+        <v>496</v>
       </c>
       <c r="B10" s="127" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="C10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="D10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="E10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="F10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="G10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="H10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="I10" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="J10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="K10" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="L10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="M10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="N10" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="O10" s="129" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="P10" s="130" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="Q10" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="R10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="S10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="T10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="U10" s="130" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="V10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="W10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="X10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Y10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Z10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AA10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AB10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AC10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AD10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AE10" s="156"/>
       <c r="AF10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AG10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AH10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AI10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AJ10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AK10" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AL10" s="156"/>
       <c r="AM10" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AN10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AO10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AP10" s="156"/>
       <c r="AQ10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AR10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AS10" s="156"/>
       <c r="AT10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AU10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AV10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AW10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AX10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AY10" s="156"/>
       <c r="AZ10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BA10" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BB10" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BC10" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BD10" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BE10" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BF10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BG10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BH10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BI10" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BJ10" s="156"/>
       <c r="BK10" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BL10" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BM10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BN10" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BO10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BP10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BQ10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BR10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BS10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BT10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BU10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BV10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BW10" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BX10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BY10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BZ10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CA10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CB10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CC10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CD10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CE10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CF10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CG10" s="129"/>
       <c r="CH10" s="129"/>
@@ -13857,249 +14289,249 @@
       <c r="CQ10" s="129"/>
       <c r="CR10" s="129"/>
       <c r="CS10" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" spans="1:97" ht="15.75">
       <c r="A11" s="126" t="s">
-        <v>472</v>
+        <v>497</v>
       </c>
       <c r="B11" s="127" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="C11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="D11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="E11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="F11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="G11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="H11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="I11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="J11" s="129" t="s">
-        <v>473</v>
+        <v>498</v>
       </c>
       <c r="K11" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="L11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="M11" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="N11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="O11" s="129" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="P11" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Q11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="R11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="S11" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="T11" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="U11" s="130" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="V11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="W11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="X11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Y11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Z11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AA11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AB11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AC11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AD11" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AE11" s="156"/>
       <c r="AF11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AG11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AH11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AI11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AJ11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AK11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AL11" s="156"/>
       <c r="AM11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AN11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AO11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AP11" s="156"/>
       <c r="AQ11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AR11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AS11" s="156"/>
       <c r="AT11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AU11" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AV11" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AW11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AX11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AY11" s="156"/>
       <c r="AZ11" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BA11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BB11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BC11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BD11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BE11" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BF11" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BG11" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BH11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BI11" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BJ11" s="156"/>
       <c r="BK11" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BL11" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BM11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BN11" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BO11" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BP11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BQ11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BR11" s="129" t="s">
-        <v>474</v>
+        <v>499</v>
       </c>
       <c r="BS11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BT11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BU11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BV11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BW11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BX11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BY11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BZ11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CA11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CB11" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="CC11" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="CD11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CE11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CF11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CG11" s="129"/>
       <c r="CH11" s="129"/>
@@ -14114,249 +14546,249 @@
       <c r="CQ11" s="129"/>
       <c r="CR11" s="129"/>
       <c r="CS11" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
     </row>
     <row r="12" spans="1:97" ht="15.75">
       <c r="A12" s="126" t="s">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="B12" s="127" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="C12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="D12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="E12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="F12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="G12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="H12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="I12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="J12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="K12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="L12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="M12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="N12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="O12" s="129" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="P12" s="130" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="Q12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="R12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="S12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="T12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="U12" s="130" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="V12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="W12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="X12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="Y12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="Z12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AA12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AB12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AC12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AD12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AE12" s="156"/>
       <c r="AF12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AG12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AH12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AI12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AJ12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AK12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AL12" s="156"/>
       <c r="AM12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AN12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AO12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AP12" s="156"/>
       <c r="AQ12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AR12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AS12" s="156"/>
       <c r="AT12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AU12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AV12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AW12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AX12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AY12" s="156"/>
       <c r="AZ12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BA12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BB12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BC12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BD12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BE12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BF12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BG12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BH12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BI12" s="130" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BJ12" s="156"/>
       <c r="BK12" s="130" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BL12" s="130" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BM12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BN12" s="130" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BO12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BP12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BQ12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BR12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BS12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BT12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BU12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BV12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BW12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BX12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BY12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="BZ12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="CA12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="CB12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CC12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="CD12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="CE12" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CF12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="CG12" s="129"/>
       <c r="CH12" s="129"/>
@@ -14371,249 +14803,249 @@
       <c r="CQ12" s="129"/>
       <c r="CR12" s="129"/>
       <c r="CS12" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
     </row>
     <row r="13" spans="1:97" ht="15.75">
       <c r="A13" s="126" t="s">
-        <v>476</v>
+        <v>501</v>
       </c>
       <c r="B13" s="127" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="C13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="D13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="E13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="F13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="G13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="H13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="I13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="J13" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="K13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="L13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="M13" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="N13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="O13" s="129" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="P13" s="130" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="Q13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="R13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="S13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="T13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="U13" s="130" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="V13" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="W13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="X13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="Y13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="Z13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AA13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AB13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AC13" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AD13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AE13" s="157"/>
       <c r="AF13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AG13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AH13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AI13" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="AJ13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AK13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AL13" s="157"/>
       <c r="AM13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AN13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AO13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AP13" s="157"/>
       <c r="AQ13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AR13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AS13" s="157"/>
       <c r="AT13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AU13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AV13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AW13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AX13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="AY13" s="157"/>
       <c r="AZ13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BA13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BB13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BC13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BD13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BE13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BF13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BG13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BH13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BI13" s="130" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BJ13" s="157"/>
       <c r="BK13" s="130" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BL13" s="130" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BM13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BN13" s="130" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BO13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BP13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BQ13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BR13" s="129" t="s">
-        <v>474</v>
+        <v>499</v>
       </c>
       <c r="BS13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BT13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BU13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BV13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BW13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BX13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BY13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="BZ13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="CA13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="CB13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="CC13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="CD13" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CE13" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CF13" s="129" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="CG13" s="129"/>
       <c r="CH13" s="129"/>
@@ -14628,7 +15060,7 @@
       <c r="CQ13" s="129"/>
       <c r="CR13" s="129"/>
       <c r="CS13" s="129" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -15647,7 +16079,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="25.5">
       <c r="A1" s="133" t="s">
-        <v>477</v>
+        <v>502</v>
       </c>
       <c r="B1" s="133" t="s">
         <v>2</v>
@@ -15671,16 +16103,16 @@
         <v>11</v>
       </c>
       <c r="I1" s="136" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="J1" s="137" t="s">
-        <v>478</v>
+        <v>503</v>
       </c>
       <c r="K1" s="138" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="L1" s="136" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="M1" s="139"/>
       <c r="N1" s="139"/>
@@ -15699,10 +16131,10 @@
     </row>
     <row r="2" spans="1:26" ht="38.25">
       <c r="A2" s="140" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="B2" s="141" t="s">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="C2" s="142"/>
       <c r="D2" s="142" t="s">
@@ -15729,7 +16161,7 @@
       </c>
       <c r="K2" s="145"/>
       <c r="L2" s="146" t="s">
-        <v>483</v>
+        <v>508</v>
       </c>
       <c r="M2" s="139"/>
       <c r="N2" s="139"/>
@@ -15748,16 +16180,16 @@
     </row>
     <row r="3" spans="1:26" ht="51">
       <c r="A3" s="140" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="B3" s="158" t="s">
-        <v>484</v>
+        <v>509</v>
       </c>
       <c r="C3" s="147" t="s">
-        <v>485</v>
+        <v>510</v>
       </c>
       <c r="D3" s="142" t="s">
-        <v>486</v>
+        <v>511</v>
       </c>
       <c r="E3" s="143">
         <v>45575</v>
@@ -15776,7 +16208,7 @@
       </c>
       <c r="K3" s="143"/>
       <c r="L3" s="146" t="s">
-        <v>487</v>
+        <v>512</v>
       </c>
       <c r="M3" s="148"/>
       <c r="N3" s="139"/>
@@ -15795,14 +16227,14 @@
     </row>
     <row r="4" spans="1:26" ht="51">
       <c r="A4" s="140" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="B4" s="156"/>
       <c r="C4" s="149" t="s">
-        <v>488</v>
+        <v>513</v>
       </c>
       <c r="D4" s="142" t="s">
-        <v>486</v>
+        <v>511</v>
       </c>
       <c r="E4" s="143">
         <v>45575</v>
@@ -15821,7 +16253,7 @@
       </c>
       <c r="K4" s="150"/>
       <c r="L4" s="153" t="s">
-        <v>489</v>
+        <v>514</v>
       </c>
       <c r="M4" s="148"/>
       <c r="N4" s="139"/>
@@ -15840,16 +16272,16 @@
     </row>
     <row r="5" spans="1:26" ht="51">
       <c r="A5" s="140" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="B5" s="136" t="s">
-        <v>490</v>
+        <v>515</v>
       </c>
       <c r="C5" s="142" t="s">
-        <v>491</v>
+        <v>516</v>
       </c>
       <c r="D5" s="142" t="s">
-        <v>486</v>
+        <v>511</v>
       </c>
       <c r="E5" s="143">
         <v>45575</v>
@@ -15868,7 +16300,7 @@
       </c>
       <c r="K5" s="143"/>
       <c r="L5" s="146" t="s">
-        <v>489</v>
+        <v>514</v>
       </c>
       <c r="M5" s="148"/>
       <c r="N5" s="139"/>
